--- a/hardness_profile.xlsx
+++ b/hardness_profile.xlsx
@@ -64,15 +64,30 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">E6018_SD</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">E7018_HV</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E7018_SD</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">E9018_HV</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E9018_SD</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Zone</t>
         </is>
@@ -86,12 +101,21 @@
         <v>212.3</v>
       </c>
       <c r="C2">
+        <v>10.62</v>
+      </c>
+      <c r="D2">
         <v>208.8</v>
       </c>
-      <c r="D2">
+      <c r="E2">
+        <v>10.44</v>
+      </c>
+      <c r="F2">
         <v>214.1</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2">
+        <v>10.71</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -105,12 +129,21 @@
         <v>213.8</v>
       </c>
       <c r="C3">
+        <v>10.69</v>
+      </c>
+      <c r="D3">
         <v>211.1</v>
       </c>
-      <c r="D3">
+      <c r="E3">
+        <v>10.55</v>
+      </c>
+      <c r="F3">
         <v>214.4</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3">
+        <v>10.72</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -124,12 +157,21 @@
         <v>211.1</v>
       </c>
       <c r="C4">
+        <v>10.55</v>
+      </c>
+      <c r="D4">
         <v>211.2</v>
       </c>
-      <c r="D4">
+      <c r="E4">
+        <v>10.56</v>
+      </c>
+      <c r="F4">
         <v>214.4</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4">
+        <v>10.72</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -143,12 +185,21 @@
         <v>211.8</v>
       </c>
       <c r="C5">
+        <v>10.59</v>
+      </c>
+      <c r="D5">
         <v>212.6</v>
       </c>
-      <c r="D5">
+      <c r="E5">
+        <v>10.63</v>
+      </c>
+      <c r="F5">
         <v>214.7</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5">
+        <v>10.73</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -162,12 +213,21 @@
         <v>213.5</v>
       </c>
       <c r="C6">
+        <v>10.68</v>
+      </c>
+      <c r="D6">
         <v>212.7</v>
       </c>
-      <c r="D6">
+      <c r="E6">
+        <v>10.63</v>
+      </c>
+      <c r="F6">
         <v>215.3</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6">
+        <v>10.77</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -181,12 +241,21 @@
         <v>214.3</v>
       </c>
       <c r="C7">
+        <v>10.72</v>
+      </c>
+      <c r="D7">
         <v>214.0</v>
       </c>
-      <c r="D7">
+      <c r="E7">
+        <v>10.7</v>
+      </c>
+      <c r="F7">
         <v>215.9</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7">
+        <v>10.8</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -200,12 +269,21 @@
         <v>213.3</v>
       </c>
       <c r="C8">
+        <v>10.67</v>
+      </c>
+      <c r="D8">
         <v>213.3</v>
       </c>
-      <c r="D8">
+      <c r="E8">
+        <v>10.67</v>
+      </c>
+      <c r="F8">
         <v>214.9</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8">
+        <v>10.75</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -219,12 +297,21 @@
         <v>213.9</v>
       </c>
       <c r="C9">
+        <v>10.7</v>
+      </c>
+      <c r="D9">
         <v>214.2</v>
       </c>
-      <c r="D9">
+      <c r="E9">
+        <v>10.71</v>
+      </c>
+      <c r="F9">
         <v>215.8</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9">
+        <v>10.79</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -238,12 +325,21 @@
         <v>214.4</v>
       </c>
       <c r="C10">
+        <v>10.72</v>
+      </c>
+      <c r="D10">
         <v>214.6</v>
       </c>
-      <c r="D10">
+      <c r="E10">
+        <v>10.73</v>
+      </c>
+      <c r="F10">
         <v>216.3</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10">
+        <v>10.82</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -257,12 +353,21 @@
         <v>213.4</v>
       </c>
       <c r="C11">
+        <v>10.67</v>
+      </c>
+      <c r="D11">
         <v>214.6</v>
       </c>
-      <c r="D11">
+      <c r="E11">
+        <v>10.73</v>
+      </c>
+      <c r="F11">
         <v>214.7</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11">
+        <v>10.73</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -276,12 +381,21 @@
         <v>215.0</v>
       </c>
       <c r="C12">
+        <v>10.75</v>
+      </c>
+      <c r="D12">
         <v>213.2</v>
       </c>
-      <c r="D12">
+      <c r="E12">
+        <v>10.66</v>
+      </c>
+      <c r="F12">
         <v>214.3</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12">
+        <v>10.72</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -295,12 +409,21 @@
         <v>216.4</v>
       </c>
       <c r="C13">
+        <v>10.82</v>
+      </c>
+      <c r="D13">
         <v>213.8</v>
       </c>
-      <c r="D13">
+      <c r="E13">
+        <v>10.69</v>
+      </c>
+      <c r="F13">
         <v>215.9</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13">
+        <v>10.8</v>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -314,12 +437,21 @@
         <v>214.0</v>
       </c>
       <c r="C14">
+        <v>10.7</v>
+      </c>
+      <c r="D14">
         <v>213.2</v>
       </c>
-      <c r="D14">
+      <c r="E14">
+        <v>10.66</v>
+      </c>
+      <c r="F14">
         <v>214.5</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14">
+        <v>10.73</v>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -333,12 +465,21 @@
         <v>214.0</v>
       </c>
       <c r="C15">
+        <v>10.7</v>
+      </c>
+      <c r="D15">
         <v>212.4</v>
       </c>
-      <c r="D15">
+      <c r="E15">
+        <v>10.62</v>
+      </c>
+      <c r="F15">
         <v>213.9</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15">
+        <v>10.7</v>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -352,12 +493,21 @@
         <v>213.5</v>
       </c>
       <c r="C16">
+        <v>10.68</v>
+      </c>
+      <c r="D16">
         <v>213.1</v>
       </c>
-      <c r="D16">
+      <c r="E16">
+        <v>10.66</v>
+      </c>
+      <c r="F16">
         <v>213.3</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16">
+        <v>10.67</v>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -371,12 +521,21 @@
         <v>215.1</v>
       </c>
       <c r="C17">
+        <v>10.76</v>
+      </c>
+      <c r="D17">
         <v>213.2</v>
       </c>
-      <c r="D17">
+      <c r="E17">
+        <v>10.66</v>
+      </c>
+      <c r="F17">
         <v>215.5</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17">
+        <v>10.78</v>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -390,12 +549,21 @@
         <v>212.8</v>
       </c>
       <c r="C18">
+        <v>10.64</v>
+      </c>
+      <c r="D18">
         <v>213.1</v>
       </c>
-      <c r="D18">
+      <c r="E18">
+        <v>10.66</v>
+      </c>
+      <c r="F18">
         <v>215.6</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18">
+        <v>10.78</v>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -409,12 +577,21 @@
         <v>216.6</v>
       </c>
       <c r="C19">
+        <v>10.83</v>
+      </c>
+      <c r="D19">
         <v>212.8</v>
       </c>
-      <c r="D19">
+      <c r="E19">
+        <v>10.64</v>
+      </c>
+      <c r="F19">
         <v>215.2</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19">
+        <v>10.76</v>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -428,12 +605,21 @@
         <v>213.4</v>
       </c>
       <c r="C20">
+        <v>10.67</v>
+      </c>
+      <c r="D20">
         <v>213.4</v>
       </c>
-      <c r="D20">
+      <c r="E20">
+        <v>10.67</v>
+      </c>
+      <c r="F20">
         <v>216.2</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20">
+        <v>10.81</v>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -447,12 +633,21 @@
         <v>215.0</v>
       </c>
       <c r="C21">
+        <v>10.75</v>
+      </c>
+      <c r="D21">
         <v>213.6</v>
       </c>
-      <c r="D21">
+      <c r="E21">
+        <v>10.68</v>
+      </c>
+      <c r="F21">
         <v>214.7</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21">
+        <v>10.73</v>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -466,12 +661,21 @@
         <v>214.8</v>
       </c>
       <c r="C22">
-        <v>215.7</v>
+        <v>10.74</v>
       </c>
       <c r="D22">
         <v>215.7</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22">
+        <v>10.79</v>
+      </c>
+      <c r="F22">
+        <v>215.7</v>
+      </c>
+      <c r="G22">
+        <v>10.79</v>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -485,12 +689,21 @@
         <v>215.6</v>
       </c>
       <c r="C23">
+        <v>10.78</v>
+      </c>
+      <c r="D23">
         <v>215.7</v>
       </c>
-      <c r="D23">
+      <c r="E23">
+        <v>10.79</v>
+      </c>
+      <c r="F23">
         <v>215.2</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23">
+        <v>10.76</v>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -504,12 +717,21 @@
         <v>216.6</v>
       </c>
       <c r="C24">
+        <v>10.83</v>
+      </c>
+      <c r="D24">
         <v>215.6</v>
       </c>
-      <c r="D24">
+      <c r="E24">
+        <v>10.78</v>
+      </c>
+      <c r="F24">
         <v>216.2</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24">
+        <v>10.81</v>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -523,12 +745,21 @@
         <v>217.2</v>
       </c>
       <c r="C25">
+        <v>10.86</v>
+      </c>
+      <c r="D25">
         <v>217.1</v>
       </c>
-      <c r="D25">
+      <c r="E25">
+        <v>10.86</v>
+      </c>
+      <c r="F25">
         <v>218.3</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25">
+        <v>10.92</v>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -542,12 +773,21 @@
         <v>217.4</v>
       </c>
       <c r="C26">
+        <v>10.87</v>
+      </c>
+      <c r="D26">
         <v>217.3</v>
       </c>
-      <c r="D26">
+      <c r="E26">
+        <v>10.87</v>
+      </c>
+      <c r="F26">
         <v>219.4</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26">
+        <v>10.97</v>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -561,12 +801,21 @@
         <v>217.9</v>
       </c>
       <c r="C27">
+        <v>10.9</v>
+      </c>
+      <c r="D27">
         <v>219.4</v>
       </c>
-      <c r="D27">
+      <c r="E27">
+        <v>10.97</v>
+      </c>
+      <c r="F27">
         <v>222.0</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27">
+        <v>11.1</v>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -580,12 +829,21 @@
         <v>218.2</v>
       </c>
       <c r="C28">
+        <v>10.91</v>
+      </c>
+      <c r="D28">
         <v>219.9</v>
       </c>
-      <c r="D28">
+      <c r="E28">
+        <v>11.0</v>
+      </c>
+      <c r="F28">
         <v>222.4</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28">
+        <v>11.12</v>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -599,12 +857,21 @@
         <v>221.0</v>
       </c>
       <c r="C29">
+        <v>11.05</v>
+      </c>
+      <c r="D29">
         <v>222.5</v>
       </c>
-      <c r="D29">
+      <c r="E29">
+        <v>11.12</v>
+      </c>
+      <c r="F29">
         <v>222.6</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29">
+        <v>11.13</v>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -618,12 +885,21 @@
         <v>220.1</v>
       </c>
       <c r="C30">
+        <v>11.01</v>
+      </c>
+      <c r="D30">
         <v>223.5</v>
       </c>
-      <c r="D30">
+      <c r="E30">
+        <v>11.18</v>
+      </c>
+      <c r="F30">
         <v>227.0</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30">
+        <v>11.35</v>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -637,12 +913,21 @@
         <v>220.0</v>
       </c>
       <c r="C31">
+        <v>11.0</v>
+      </c>
+      <c r="D31">
         <v>223.3</v>
       </c>
-      <c r="D31">
+      <c r="E31">
+        <v>11.17</v>
+      </c>
+      <c r="F31">
         <v>229.2</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31">
+        <v>11.46</v>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -656,12 +941,21 @@
         <v>218.6</v>
       </c>
       <c r="C32">
+        <v>10.93</v>
+      </c>
+      <c r="D32">
         <v>226.2</v>
       </c>
-      <c r="D32">
+      <c r="E32">
+        <v>11.31</v>
+      </c>
+      <c r="F32">
         <v>231.8</v>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32">
+        <v>11.59</v>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -675,12 +969,21 @@
         <v>220.7</v>
       </c>
       <c r="C33">
+        <v>11.04</v>
+      </c>
+      <c r="D33">
         <v>224.8</v>
       </c>
-      <c r="D33">
+      <c r="E33">
+        <v>11.24</v>
+      </c>
+      <c r="F33">
         <v>233.1</v>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33">
+        <v>11.66</v>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -694,12 +997,21 @@
         <v>219.8</v>
       </c>
       <c r="C34">
+        <v>10.99</v>
+      </c>
+      <c r="D34">
         <v>226.3</v>
       </c>
-      <c r="D34">
+      <c r="E34">
+        <v>11.32</v>
+      </c>
+      <c r="F34">
         <v>235.6</v>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34">
+        <v>11.78</v>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -713,12 +1025,21 @@
         <v>221.5</v>
       </c>
       <c r="C35">
+        <v>11.08</v>
+      </c>
+      <c r="D35">
         <v>229.1</v>
       </c>
-      <c r="D35">
+      <c r="E35">
+        <v>11.46</v>
+      </c>
+      <c r="F35">
         <v>238.3</v>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35">
+        <v>11.92</v>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -732,12 +1053,21 @@
         <v>221.6</v>
       </c>
       <c r="C36">
+        <v>11.08</v>
+      </c>
+      <c r="D36">
         <v>231.5</v>
       </c>
-      <c r="D36">
+      <c r="E36">
+        <v>11.58</v>
+      </c>
+      <c r="F36">
         <v>237.8</v>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36">
+        <v>11.89</v>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -751,12 +1081,21 @@
         <v>223.3</v>
       </c>
       <c r="C37">
+        <v>11.17</v>
+      </c>
+      <c r="D37">
         <v>232.1</v>
       </c>
-      <c r="D37">
+      <c r="E37">
+        <v>11.61</v>
+      </c>
+      <c r="F37">
         <v>239.9</v>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37">
+        <v>12.0</v>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -770,12 +1109,21 @@
         <v>224.5</v>
       </c>
       <c r="C38">
+        <v>11.23</v>
+      </c>
+      <c r="D38">
         <v>232.3</v>
       </c>
-      <c r="D38">
+      <c r="E38">
+        <v>11.62</v>
+      </c>
+      <c r="F38">
         <v>242.1</v>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38">
+        <v>12.11</v>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -789,12 +1137,21 @@
         <v>226.9</v>
       </c>
       <c r="C39">
+        <v>11.35</v>
+      </c>
+      <c r="D39">
         <v>233.7</v>
       </c>
-      <c r="D39">
+      <c r="E39">
+        <v>11.69</v>
+      </c>
+      <c r="F39">
         <v>243.8</v>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39">
+        <v>12.19</v>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -808,12 +1165,21 @@
         <v>228.4</v>
       </c>
       <c r="C40">
+        <v>11.42</v>
+      </c>
+      <c r="D40">
         <v>236.9</v>
       </c>
-      <c r="D40">
+      <c r="E40">
+        <v>11.85</v>
+      </c>
+      <c r="F40">
         <v>246.3</v>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40">
+        <v>12.32</v>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -827,12 +1193,21 @@
         <v>230.7</v>
       </c>
       <c r="C41">
+        <v>11.54</v>
+      </c>
+      <c r="D41">
         <v>237.9</v>
       </c>
-      <c r="D41">
+      <c r="E41">
+        <v>11.9</v>
+      </c>
+      <c r="F41">
         <v>248.5</v>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41">
+        <v>12.43</v>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -846,12 +1221,21 @@
         <v>231.2</v>
       </c>
       <c r="C42">
+        <v>11.56</v>
+      </c>
+      <c r="D42">
         <v>240.7</v>
       </c>
-      <c r="D42">
+      <c r="E42">
+        <v>12.04</v>
+      </c>
+      <c r="F42">
         <v>248.6</v>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42">
+        <v>12.43</v>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -865,12 +1249,21 @@
         <v>231.9</v>
       </c>
       <c r="C43">
+        <v>11.6</v>
+      </c>
+      <c r="D43">
         <v>239.0</v>
       </c>
-      <c r="D43">
+      <c r="E43">
+        <v>11.95</v>
+      </c>
+      <c r="F43">
         <v>251.8</v>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43">
+        <v>12.59</v>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -884,12 +1277,21 @@
         <v>234.6</v>
       </c>
       <c r="C44">
+        <v>11.73</v>
+      </c>
+      <c r="D44">
         <v>239.7</v>
       </c>
-      <c r="D44">
+      <c r="E44">
+        <v>11.98</v>
+      </c>
+      <c r="F44">
         <v>251.0</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44">
+        <v>12.55</v>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -903,12 +1305,21 @@
         <v>236.5</v>
       </c>
       <c r="C45">
+        <v>11.83</v>
+      </c>
+      <c r="D45">
         <v>242.7</v>
       </c>
-      <c r="D45">
+      <c r="E45">
+        <v>12.13</v>
+      </c>
+      <c r="F45">
         <v>256.3</v>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45">
+        <v>12.82</v>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -922,12 +1333,21 @@
         <v>236.9</v>
       </c>
       <c r="C46">
+        <v>11.85</v>
+      </c>
+      <c r="D46">
         <v>243.5</v>
       </c>
-      <c r="D46">
+      <c r="E46">
+        <v>12.18</v>
+      </c>
+      <c r="F46">
         <v>255.0</v>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46">
+        <v>12.75</v>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -941,12 +1361,21 @@
         <v>237.8</v>
       </c>
       <c r="C47">
+        <v>11.89</v>
+      </c>
+      <c r="D47">
         <v>243.9</v>
       </c>
-      <c r="D47">
+      <c r="E47">
+        <v>12.2</v>
+      </c>
+      <c r="F47">
         <v>257.1</v>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47">
+        <v>12.86</v>
+      </c>
+      <c r="H47" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -960,12 +1389,21 @@
         <v>240.6</v>
       </c>
       <c r="C48">
+        <v>12.03</v>
+      </c>
+      <c r="D48">
         <v>242.9</v>
       </c>
-      <c r="D48">
+      <c r="E48">
+        <v>12.15</v>
+      </c>
+      <c r="F48">
         <v>258.1</v>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48">
+        <v>12.91</v>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -979,12 +1417,21 @@
         <v>240.0</v>
       </c>
       <c r="C49">
+        <v>12.0</v>
+      </c>
+      <c r="D49">
         <v>245.3</v>
       </c>
-      <c r="D49">
+      <c r="E49">
+        <v>12.27</v>
+      </c>
+      <c r="F49">
         <v>261.0</v>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49">
+        <v>13.05</v>
+      </c>
+      <c r="H49" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -998,12 +1445,21 @@
         <v>243.1</v>
       </c>
       <c r="C50">
+        <v>12.16</v>
+      </c>
+      <c r="D50">
         <v>247.7</v>
       </c>
-      <c r="D50">
+      <c r="E50">
+        <v>12.38</v>
+      </c>
+      <c r="F50">
         <v>262.7</v>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50">
+        <v>13.13</v>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -1017,12 +1473,21 @@
         <v>243.3</v>
       </c>
       <c r="C51">
+        <v>12.17</v>
+      </c>
+      <c r="D51">
         <v>248.9</v>
       </c>
-      <c r="D51">
+      <c r="E51">
+        <v>12.45</v>
+      </c>
+      <c r="F51">
         <v>263.0</v>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51">
+        <v>13.15</v>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -1036,12 +1501,21 @@
         <v>244.6</v>
       </c>
       <c r="C52">
+        <v>12.23</v>
+      </c>
+      <c r="D52">
         <v>249.8</v>
       </c>
-      <c r="D52">
+      <c r="E52">
+        <v>12.49</v>
+      </c>
+      <c r="F52">
         <v>265.3</v>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52">
+        <v>13.27</v>
+      </c>
+      <c r="H52" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -1055,12 +1529,21 @@
         <v>247.4</v>
       </c>
       <c r="C53">
+        <v>12.37</v>
+      </c>
+      <c r="D53">
         <v>251.0</v>
       </c>
-      <c r="D53">
+      <c r="E53">
+        <v>12.55</v>
+      </c>
+      <c r="F53">
         <v>265.8</v>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53">
+        <v>13.29</v>
+      </c>
+      <c r="H53" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -1074,12 +1557,21 @@
         <v>248.1</v>
       </c>
       <c r="C54">
+        <v>12.41</v>
+      </c>
+      <c r="D54">
         <v>251.7</v>
       </c>
-      <c r="D54">
+      <c r="E54">
+        <v>12.59</v>
+      </c>
+      <c r="F54">
         <v>269.3</v>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54">
+        <v>13.47</v>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -1093,12 +1585,21 @@
         <v>249.1</v>
       </c>
       <c r="C55">
+        <v>12.46</v>
+      </c>
+      <c r="D55">
         <v>253.7</v>
       </c>
-      <c r="D55">
+      <c r="E55">
+        <v>12.69</v>
+      </c>
+      <c r="F55">
         <v>271.6</v>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55">
+        <v>13.58</v>
+      </c>
+      <c r="H55" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -1112,12 +1613,21 @@
         <v>249.8</v>
       </c>
       <c r="C56">
+        <v>12.49</v>
+      </c>
+      <c r="D56">
         <v>255.6</v>
       </c>
-      <c r="D56">
+      <c r="E56">
+        <v>12.78</v>
+      </c>
+      <c r="F56">
         <v>272.9</v>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56">
+        <v>13.64</v>
+      </c>
+      <c r="H56" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -1131,12 +1641,21 @@
         <v>250.5</v>
       </c>
       <c r="C57">
+        <v>12.53</v>
+      </c>
+      <c r="D57">
         <v>256.7</v>
       </c>
-      <c r="D57">
+      <c r="E57">
+        <v>12.84</v>
+      </c>
+      <c r="F57">
         <v>276.6</v>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57">
+        <v>13.83</v>
+      </c>
+      <c r="H57" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -1150,12 +1669,21 @@
         <v>248.6</v>
       </c>
       <c r="C58">
+        <v>12.43</v>
+      </c>
+      <c r="D58">
         <v>255.7</v>
       </c>
-      <c r="D58">
+      <c r="E58">
+        <v>12.79</v>
+      </c>
+      <c r="F58">
         <v>274.7</v>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58">
+        <v>13.73</v>
+      </c>
+      <c r="H58" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -1169,12 +1697,21 @@
         <v>245.4</v>
       </c>
       <c r="C59">
+        <v>12.27</v>
+      </c>
+      <c r="D59">
         <v>253.5</v>
       </c>
-      <c r="D59">
+      <c r="E59">
+        <v>12.68</v>
+      </c>
+      <c r="F59">
         <v>272.8</v>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59">
+        <v>13.64</v>
+      </c>
+      <c r="H59" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -1188,12 +1725,21 @@
         <v>243.1</v>
       </c>
       <c r="C60">
+        <v>12.16</v>
+      </c>
+      <c r="D60">
         <v>251.8</v>
       </c>
-      <c r="D60">
+      <c r="E60">
+        <v>12.59</v>
+      </c>
+      <c r="F60">
         <v>272.4</v>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60">
+        <v>13.62</v>
+      </c>
+      <c r="H60" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -1207,12 +1753,21 @@
         <v>235.4</v>
       </c>
       <c r="C61">
+        <v>11.77</v>
+      </c>
+      <c r="D61">
         <v>246.8</v>
       </c>
-      <c r="D61">
+      <c r="E61">
+        <v>12.34</v>
+      </c>
+      <c r="F61">
         <v>270.2</v>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61">
+        <v>13.51</v>
+      </c>
+      <c r="H61" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -1226,12 +1781,21 @@
         <v>227.0</v>
       </c>
       <c r="C62">
+        <v>11.35</v>
+      </c>
+      <c r="D62">
         <v>241.7</v>
       </c>
-      <c r="D62">
+      <c r="E62">
+        <v>12.09</v>
+      </c>
+      <c r="F62">
         <v>266.6</v>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62">
+        <v>13.33</v>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -1245,12 +1809,21 @@
         <v>218.5</v>
       </c>
       <c r="C63">
+        <v>10.93</v>
+      </c>
+      <c r="D63">
         <v>238.4</v>
       </c>
-      <c r="D63">
+      <c r="E63">
+        <v>11.92</v>
+      </c>
+      <c r="F63">
         <v>265.2</v>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63">
+        <v>13.26</v>
+      </c>
+      <c r="H63" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1264,12 +1837,21 @@
         <v>210.2</v>
       </c>
       <c r="C64">
+        <v>10.51</v>
+      </c>
+      <c r="D64">
         <v>232.2</v>
       </c>
-      <c r="D64">
+      <c r="E64">
+        <v>11.61</v>
+      </c>
+      <c r="F64">
         <v>262.5</v>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64">
+        <v>13.12</v>
+      </c>
+      <c r="H64" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1283,12 +1865,21 @@
         <v>207.8</v>
       </c>
       <c r="C65">
+        <v>10.39</v>
+      </c>
+      <c r="D65">
         <v>232.5</v>
       </c>
-      <c r="D65">
+      <c r="E65">
+        <v>11.62</v>
+      </c>
+      <c r="F65">
         <v>264.3</v>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65">
+        <v>13.22</v>
+      </c>
+      <c r="H65" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1302,12 +1893,21 @@
         <v>207.0</v>
       </c>
       <c r="C66">
+        <v>10.35</v>
+      </c>
+      <c r="D66">
         <v>231.0</v>
       </c>
-      <c r="D66">
+      <c r="E66">
+        <v>11.55</v>
+      </c>
+      <c r="F66">
         <v>264.5</v>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66">
+        <v>13.23</v>
+      </c>
+      <c r="H66" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1321,12 +1921,21 @@
         <v>206.5</v>
       </c>
       <c r="C67">
+        <v>10.33</v>
+      </c>
+      <c r="D67">
         <v>230.1</v>
       </c>
-      <c r="D67">
+      <c r="E67">
+        <v>11.51</v>
+      </c>
+      <c r="F67">
         <v>262.7</v>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67">
+        <v>13.13</v>
+      </c>
+      <c r="H67" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1340,12 +1949,21 @@
         <v>206.4</v>
       </c>
       <c r="C68">
+        <v>10.32</v>
+      </c>
+      <c r="D68">
         <v>230.0</v>
       </c>
-      <c r="D68">
+      <c r="E68">
+        <v>11.5</v>
+      </c>
+      <c r="F68">
         <v>263.3</v>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68">
+        <v>13.17</v>
+      </c>
+      <c r="H68" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1359,12 +1977,21 @@
         <v>205.1</v>
       </c>
       <c r="C69">
+        <v>10.26</v>
+      </c>
+      <c r="D69">
         <v>229.1</v>
       </c>
-      <c r="D69">
+      <c r="E69">
+        <v>11.46</v>
+      </c>
+      <c r="F69">
         <v>264.2</v>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69">
+        <v>13.21</v>
+      </c>
+      <c r="H69" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1378,12 +2005,21 @@
         <v>205.6</v>
       </c>
       <c r="C70">
+        <v>10.28</v>
+      </c>
+      <c r="D70">
         <v>228.4</v>
       </c>
-      <c r="D70">
+      <c r="E70">
+        <v>11.42</v>
+      </c>
+      <c r="F70">
         <v>262.2</v>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70">
+        <v>13.11</v>
+      </c>
+      <c r="H70" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1397,12 +2033,21 @@
         <v>204.9</v>
       </c>
       <c r="C71">
+        <v>10.25</v>
+      </c>
+      <c r="D71">
         <v>227.6</v>
       </c>
-      <c r="D71">
+      <c r="E71">
+        <v>11.38</v>
+      </c>
+      <c r="F71">
         <v>262.8</v>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="G71">
+        <v>13.14</v>
+      </c>
+      <c r="H71" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1416,12 +2061,21 @@
         <v>206.0</v>
       </c>
       <c r="C72">
+        <v>10.3</v>
+      </c>
+      <c r="D72">
         <v>225.9</v>
       </c>
-      <c r="D72">
+      <c r="E72">
+        <v>11.3</v>
+      </c>
+      <c r="F72">
         <v>260.5</v>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="G72">
+        <v>13.03</v>
+      </c>
+      <c r="H72" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1435,12 +2089,21 @@
         <v>205.1</v>
       </c>
       <c r="C73">
+        <v>10.26</v>
+      </c>
+      <c r="D73">
         <v>226.2</v>
       </c>
-      <c r="D73">
+      <c r="E73">
+        <v>11.31</v>
+      </c>
+      <c r="F73">
         <v>261.4</v>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73">
+        <v>13.07</v>
+      </c>
+      <c r="H73" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1454,12 +2117,21 @@
         <v>204.9</v>
       </c>
       <c r="C74">
+        <v>10.25</v>
+      </c>
+      <c r="D74">
         <v>224.8</v>
       </c>
-      <c r="D74">
+      <c r="E74">
+        <v>11.24</v>
+      </c>
+      <c r="F74">
         <v>262.5</v>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="G74">
+        <v>13.12</v>
+      </c>
+      <c r="H74" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1473,12 +2145,21 @@
         <v>204.9</v>
       </c>
       <c r="C75">
+        <v>10.25</v>
+      </c>
+      <c r="D75">
         <v>227.0</v>
       </c>
-      <c r="D75">
+      <c r="E75">
+        <v>11.35</v>
+      </c>
+      <c r="F75">
         <v>260.8</v>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="G75">
+        <v>13.04</v>
+      </c>
+      <c r="H75" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1492,12 +2173,21 @@
         <v>205.2</v>
       </c>
       <c r="C76">
+        <v>10.26</v>
+      </c>
+      <c r="D76">
         <v>225.6</v>
       </c>
-      <c r="D76">
+      <c r="E76">
+        <v>11.28</v>
+      </c>
+      <c r="F76">
         <v>262.0</v>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="G76">
+        <v>13.1</v>
+      </c>
+      <c r="H76" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1511,12 +2201,21 @@
         <v>203.6</v>
       </c>
       <c r="C77">
+        <v>10.18</v>
+      </c>
+      <c r="D77">
         <v>226.6</v>
       </c>
-      <c r="D77">
+      <c r="E77">
+        <v>11.33</v>
+      </c>
+      <c r="F77">
         <v>260.8</v>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77">
+        <v>13.04</v>
+      </c>
+      <c r="H77" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1530,12 +2229,21 @@
         <v>205.3</v>
       </c>
       <c r="C78">
+        <v>10.27</v>
+      </c>
+      <c r="D78">
         <v>228.9</v>
       </c>
-      <c r="D78">
+      <c r="E78">
+        <v>11.45</v>
+      </c>
+      <c r="F78">
         <v>260.6</v>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="G78">
+        <v>13.03</v>
+      </c>
+      <c r="H78" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1549,12 +2257,21 @@
         <v>206.2</v>
       </c>
       <c r="C79">
+        <v>10.31</v>
+      </c>
+      <c r="D79">
         <v>229.0</v>
       </c>
-      <c r="D79">
+      <c r="E79">
+        <v>11.45</v>
+      </c>
+      <c r="F79">
         <v>259.2</v>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="G79">
+        <v>12.96</v>
+      </c>
+      <c r="H79" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1568,12 +2285,21 @@
         <v>207.2</v>
       </c>
       <c r="C80">
+        <v>10.36</v>
+      </c>
+      <c r="D80">
         <v>228.8</v>
       </c>
-      <c r="D80">
+      <c r="E80">
+        <v>11.44</v>
+      </c>
+      <c r="F80">
         <v>258.3</v>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="G80">
+        <v>12.92</v>
+      </c>
+      <c r="H80" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1587,12 +2313,21 @@
         <v>206.6</v>
       </c>
       <c r="C81">
+        <v>10.33</v>
+      </c>
+      <c r="D81">
         <v>230.5</v>
       </c>
-      <c r="D81">
+      <c r="E81">
+        <v>11.53</v>
+      </c>
+      <c r="F81">
         <v>258.8</v>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="G81">
+        <v>12.94</v>
+      </c>
+      <c r="H81" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1606,12 +2341,21 @@
         <v>207.1</v>
       </c>
       <c r="C82">
+        <v>10.36</v>
+      </c>
+      <c r="D82">
         <v>231.7</v>
       </c>
-      <c r="D82">
+      <c r="E82">
+        <v>11.59</v>
+      </c>
+      <c r="F82">
         <v>259.6</v>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="G82">
+        <v>12.98</v>
+      </c>
+      <c r="H82" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1625,12 +2369,21 @@
         <v>206.6</v>
       </c>
       <c r="C83">
+        <v>10.33</v>
+      </c>
+      <c r="D83">
         <v>231.5</v>
       </c>
-      <c r="D83">
+      <c r="E83">
+        <v>11.58</v>
+      </c>
+      <c r="F83">
         <v>259.4</v>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="G83">
+        <v>12.97</v>
+      </c>
+      <c r="H83" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1644,12 +2397,21 @@
         <v>209.0</v>
       </c>
       <c r="C84">
+        <v>10.45</v>
+      </c>
+      <c r="D84">
         <v>232.9</v>
       </c>
-      <c r="D84">
+      <c r="E84">
+        <v>11.65</v>
+      </c>
+      <c r="F84">
         <v>257.6</v>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="G84">
+        <v>12.88</v>
+      </c>
+      <c r="H84" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1663,12 +2425,21 @@
         <v>208.0</v>
       </c>
       <c r="C85">
+        <v>10.4</v>
+      </c>
+      <c r="D85">
         <v>232.1</v>
       </c>
-      <c r="D85">
+      <c r="E85">
+        <v>11.61</v>
+      </c>
+      <c r="F85">
         <v>260.0</v>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="G85">
+        <v>13.0</v>
+      </c>
+      <c r="H85" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1682,12 +2453,21 @@
         <v>208.6</v>
       </c>
       <c r="C86">
+        <v>10.43</v>
+      </c>
+      <c r="D86">
         <v>233.5</v>
       </c>
-      <c r="D86">
+      <c r="E86">
+        <v>11.68</v>
+      </c>
+      <c r="F86">
         <v>260.8</v>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="G86">
+        <v>13.04</v>
+      </c>
+      <c r="H86" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1701,12 +2481,21 @@
         <v>209.2</v>
       </c>
       <c r="C87">
+        <v>10.46</v>
+      </c>
+      <c r="D87">
         <v>233.7</v>
       </c>
-      <c r="D87">
+      <c r="E87">
+        <v>11.69</v>
+      </c>
+      <c r="F87">
         <v>261.9</v>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="G87">
+        <v>13.09</v>
+      </c>
+      <c r="H87" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1720,12 +2509,21 @@
         <v>209.8</v>
       </c>
       <c r="C88">
+        <v>10.49</v>
+      </c>
+      <c r="D88">
         <v>232.9</v>
       </c>
-      <c r="D88">
+      <c r="E88">
+        <v>11.65</v>
+      </c>
+      <c r="F88">
         <v>261.3</v>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="G88">
+        <v>13.07</v>
+      </c>
+      <c r="H88" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1739,12 +2537,21 @@
         <v>210.5</v>
       </c>
       <c r="C89">
+        <v>10.53</v>
+      </c>
+      <c r="D89">
         <v>233.2</v>
       </c>
-      <c r="D89">
+      <c r="E89">
+        <v>11.66</v>
+      </c>
+      <c r="F89">
         <v>262.6</v>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="G89">
+        <v>13.13</v>
+      </c>
+      <c r="H89" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1758,12 +2565,21 @@
         <v>212.0</v>
       </c>
       <c r="C90">
+        <v>10.6</v>
+      </c>
+      <c r="D90">
         <v>234.6</v>
       </c>
-      <c r="D90">
+      <c r="E90">
+        <v>11.73</v>
+      </c>
+      <c r="F90">
         <v>263.5</v>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="G90">
+        <v>13.18</v>
+      </c>
+      <c r="H90" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1777,12 +2593,21 @@
         <v>211.6</v>
       </c>
       <c r="C91">
+        <v>10.58</v>
+      </c>
+      <c r="D91">
         <v>233.3</v>
       </c>
-      <c r="D91">
+      <c r="E91">
+        <v>11.67</v>
+      </c>
+      <c r="F91">
         <v>263.5</v>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="G91">
+        <v>13.18</v>
+      </c>
+      <c r="H91" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1796,12 +2621,21 @@
         <v>214.6</v>
       </c>
       <c r="C92">
+        <v>10.73</v>
+      </c>
+      <c r="D92">
         <v>231.8</v>
       </c>
-      <c r="D92">
+      <c r="E92">
+        <v>11.59</v>
+      </c>
+      <c r="F92">
         <v>260.9</v>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="G92">
+        <v>13.04</v>
+      </c>
+      <c r="H92" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1815,12 +2649,21 @@
         <v>212.8</v>
       </c>
       <c r="C93">
+        <v>10.64</v>
+      </c>
+      <c r="D93">
         <v>233.4</v>
       </c>
-      <c r="D93">
+      <c r="E93">
+        <v>11.67</v>
+      </c>
+      <c r="F93">
         <v>264.6</v>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="G93">
+        <v>13.23</v>
+      </c>
+      <c r="H93" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1834,12 +2677,21 @@
         <v>213.0</v>
       </c>
       <c r="C94">
+        <v>10.65</v>
+      </c>
+      <c r="D94">
         <v>231.8</v>
       </c>
-      <c r="D94">
+      <c r="E94">
+        <v>11.59</v>
+      </c>
+      <c r="F94">
         <v>263.1</v>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="G94">
+        <v>13.16</v>
+      </c>
+      <c r="H94" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1853,12 +2705,21 @@
         <v>213.8</v>
       </c>
       <c r="C95">
+        <v>10.69</v>
+      </c>
+      <c r="D95">
         <v>232.6</v>
       </c>
-      <c r="D95">
+      <c r="E95">
+        <v>11.63</v>
+      </c>
+      <c r="F95">
         <v>263.2</v>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="G95">
+        <v>13.16</v>
+      </c>
+      <c r="H95" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1872,12 +2733,21 @@
         <v>212.8</v>
       </c>
       <c r="C96">
+        <v>10.64</v>
+      </c>
+      <c r="D96">
         <v>231.4</v>
       </c>
-      <c r="D96">
+      <c r="E96">
+        <v>11.57</v>
+      </c>
+      <c r="F96">
         <v>262.2</v>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="G96">
+        <v>13.11</v>
+      </c>
+      <c r="H96" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1891,12 +2761,21 @@
         <v>213.4</v>
       </c>
       <c r="C97">
+        <v>10.67</v>
+      </c>
+      <c r="D97">
         <v>230.4</v>
       </c>
-      <c r="D97">
+      <c r="E97">
+        <v>11.52</v>
+      </c>
+      <c r="F97">
         <v>261.6</v>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="G97">
+        <v>13.08</v>
+      </c>
+      <c r="H97" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1910,12 +2789,21 @@
         <v>213.3</v>
       </c>
       <c r="C98">
+        <v>10.67</v>
+      </c>
+      <c r="D98">
         <v>228.9</v>
       </c>
-      <c r="D98">
+      <c r="E98">
+        <v>11.45</v>
+      </c>
+      <c r="F98">
         <v>261.5</v>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="G98">
+        <v>13.08</v>
+      </c>
+      <c r="H98" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1929,12 +2817,21 @@
         <v>213.0</v>
       </c>
       <c r="C99">
+        <v>10.65</v>
+      </c>
+      <c r="D99">
         <v>229.1</v>
       </c>
-      <c r="D99">
+      <c r="E99">
+        <v>11.46</v>
+      </c>
+      <c r="F99">
         <v>261.7</v>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="G99">
+        <v>13.09</v>
+      </c>
+      <c r="H99" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1948,12 +2845,21 @@
         <v>211.2</v>
       </c>
       <c r="C100">
+        <v>10.56</v>
+      </c>
+      <c r="D100">
         <v>229.1</v>
       </c>
-      <c r="D100">
+      <c r="E100">
+        <v>11.46</v>
+      </c>
+      <c r="F100">
         <v>259.6</v>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="G100">
+        <v>12.98</v>
+      </c>
+      <c r="H100" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1967,12 +2873,21 @@
         <v>209.6</v>
       </c>
       <c r="C101">
+        <v>10.48</v>
+      </c>
+      <c r="D101">
         <v>230.1</v>
       </c>
-      <c r="D101">
+      <c r="E101">
+        <v>11.51</v>
+      </c>
+      <c r="F101">
         <v>256.5</v>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="G101">
+        <v>12.83</v>
+      </c>
+      <c r="H101" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -1986,12 +2901,21 @@
         <v>207.1</v>
       </c>
       <c r="C102">
+        <v>10.36</v>
+      </c>
+      <c r="D102">
         <v>228.9</v>
       </c>
-      <c r="D102">
+      <c r="E102">
+        <v>11.45</v>
+      </c>
+      <c r="F102">
         <v>257.5</v>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="G102">
+        <v>12.88</v>
+      </c>
+      <c r="H102" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2005,12 +2929,21 @@
         <v>207.8</v>
       </c>
       <c r="C103">
+        <v>10.39</v>
+      </c>
+      <c r="D103">
         <v>229.4</v>
       </c>
-      <c r="D103">
+      <c r="E103">
+        <v>11.47</v>
+      </c>
+      <c r="F103">
         <v>257.1</v>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="G103">
+        <v>12.86</v>
+      </c>
+      <c r="H103" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2024,12 +2957,21 @@
         <v>207.2</v>
       </c>
       <c r="C104">
+        <v>10.36</v>
+      </c>
+      <c r="D104">
         <v>227.9</v>
       </c>
-      <c r="D104">
+      <c r="E104">
+        <v>11.4</v>
+      </c>
+      <c r="F104">
         <v>255.2</v>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="G104">
+        <v>12.76</v>
+      </c>
+      <c r="H104" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2043,12 +2985,21 @@
         <v>206.9</v>
       </c>
       <c r="C105">
+        <v>10.35</v>
+      </c>
+      <c r="D105">
         <v>230.8</v>
       </c>
-      <c r="D105">
+      <c r="E105">
+        <v>11.54</v>
+      </c>
+      <c r="F105">
         <v>254.2</v>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="G105">
+        <v>12.71</v>
+      </c>
+      <c r="H105" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2062,12 +3013,21 @@
         <v>205.5</v>
       </c>
       <c r="C106">
+        <v>10.28</v>
+      </c>
+      <c r="D106">
         <v>228.1</v>
       </c>
-      <c r="D106">
+      <c r="E106">
+        <v>11.41</v>
+      </c>
+      <c r="F106">
         <v>252.3</v>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="G106">
+        <v>12.62</v>
+      </c>
+      <c r="H106" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2081,12 +3041,21 @@
         <v>206.1</v>
       </c>
       <c r="C107">
+        <v>10.3</v>
+      </c>
+      <c r="D107">
         <v>227.3</v>
       </c>
-      <c r="D107">
+      <c r="E107">
+        <v>11.37</v>
+      </c>
+      <c r="F107">
         <v>250.4</v>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="G107">
+        <v>12.52</v>
+      </c>
+      <c r="H107" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2100,12 +3069,21 @@
         <v>205.7</v>
       </c>
       <c r="C108">
+        <v>10.29</v>
+      </c>
+      <c r="D108">
         <v>226.8</v>
       </c>
-      <c r="D108">
+      <c r="E108">
+        <v>11.34</v>
+      </c>
+      <c r="F108">
         <v>251.4</v>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="G108">
+        <v>12.57</v>
+      </c>
+      <c r="H108" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2119,12 +3097,21 @@
         <v>207.3</v>
       </c>
       <c r="C109">
+        <v>10.37</v>
+      </c>
+      <c r="D109">
         <v>226.6</v>
       </c>
-      <c r="D109">
+      <c r="E109">
+        <v>11.33</v>
+      </c>
+      <c r="F109">
         <v>250.2</v>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="G109">
+        <v>12.51</v>
+      </c>
+      <c r="H109" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2138,12 +3125,21 @@
         <v>207.0</v>
       </c>
       <c r="C110">
+        <v>10.35</v>
+      </c>
+      <c r="D110">
         <v>226.2</v>
       </c>
-      <c r="D110">
+      <c r="E110">
+        <v>11.31</v>
+      </c>
+      <c r="F110">
         <v>250.2</v>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="G110">
+        <v>12.51</v>
+      </c>
+      <c r="H110" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2157,12 +3153,21 @@
         <v>206.5</v>
       </c>
       <c r="C111">
+        <v>10.33</v>
+      </c>
+      <c r="D111">
         <v>224.0</v>
       </c>
-      <c r="D111">
+      <c r="E111">
+        <v>11.2</v>
+      </c>
+      <c r="F111">
         <v>249.2</v>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="G111">
+        <v>12.46</v>
+      </c>
+      <c r="H111" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2176,12 +3181,21 @@
         <v>206.4</v>
       </c>
       <c r="C112">
+        <v>10.32</v>
+      </c>
+      <c r="D112">
         <v>224.3</v>
       </c>
-      <c r="D112">
+      <c r="E112">
+        <v>11.22</v>
+      </c>
+      <c r="F112">
         <v>251.0</v>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="G112">
+        <v>12.55</v>
+      </c>
+      <c r="H112" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2195,12 +3209,21 @@
         <v>206.7</v>
       </c>
       <c r="C113">
+        <v>10.34</v>
+      </c>
+      <c r="D113">
         <v>224.2</v>
       </c>
-      <c r="D113">
+      <c r="E113">
+        <v>11.21</v>
+      </c>
+      <c r="F113">
         <v>251.1</v>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="G113">
+        <v>12.55</v>
+      </c>
+      <c r="H113" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2214,12 +3237,21 @@
         <v>207.4</v>
       </c>
       <c r="C114">
+        <v>10.37</v>
+      </c>
+      <c r="D114">
         <v>226.4</v>
       </c>
-      <c r="D114">
+      <c r="E114">
+        <v>11.32</v>
+      </c>
+      <c r="F114">
         <v>252.3</v>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="G114">
+        <v>12.62</v>
+      </c>
+      <c r="H114" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2233,12 +3265,21 @@
         <v>206.8</v>
       </c>
       <c r="C115">
+        <v>10.34</v>
+      </c>
+      <c r="D115">
         <v>226.4</v>
       </c>
-      <c r="D115">
+      <c r="E115">
+        <v>11.32</v>
+      </c>
+      <c r="F115">
         <v>254.3</v>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="G115">
+        <v>12.72</v>
+      </c>
+      <c r="H115" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2252,12 +3293,21 @@
         <v>206.8</v>
       </c>
       <c r="C116">
+        <v>10.34</v>
+      </c>
+      <c r="D116">
         <v>227.6</v>
       </c>
-      <c r="D116">
+      <c r="E116">
+        <v>11.38</v>
+      </c>
+      <c r="F116">
         <v>254.4</v>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="G116">
+        <v>12.72</v>
+      </c>
+      <c r="H116" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2271,12 +3321,21 @@
         <v>208.8</v>
       </c>
       <c r="C117">
+        <v>10.44</v>
+      </c>
+      <c r="D117">
         <v>228.9</v>
       </c>
-      <c r="D117">
+      <c r="E117">
+        <v>11.45</v>
+      </c>
+      <c r="F117">
         <v>254.3</v>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="G117">
+        <v>12.72</v>
+      </c>
+      <c r="H117" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2290,12 +3349,21 @@
         <v>206.2</v>
       </c>
       <c r="C118">
+        <v>10.31</v>
+      </c>
+      <c r="D118">
         <v>230.1</v>
       </c>
-      <c r="D118">
+      <c r="E118">
+        <v>11.51</v>
+      </c>
+      <c r="F118">
         <v>256.8</v>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="G118">
+        <v>12.84</v>
+      </c>
+      <c r="H118" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2309,12 +3377,21 @@
         <v>208.2</v>
       </c>
       <c r="C119">
+        <v>10.41</v>
+      </c>
+      <c r="D119">
         <v>230.7</v>
       </c>
-      <c r="D119">
+      <c r="E119">
+        <v>11.54</v>
+      </c>
+      <c r="F119">
         <v>257.9</v>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="G119">
+        <v>12.89</v>
+      </c>
+      <c r="H119" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2328,12 +3405,21 @@
         <v>207.9</v>
       </c>
       <c r="C120">
+        <v>10.4</v>
+      </c>
+      <c r="D120">
         <v>231.4</v>
       </c>
-      <c r="D120">
+      <c r="E120">
+        <v>11.57</v>
+      </c>
+      <c r="F120">
         <v>257.2</v>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="G120">
+        <v>12.86</v>
+      </c>
+      <c r="H120" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2347,12 +3433,21 @@
         <v>207.1</v>
       </c>
       <c r="C121">
+        <v>10.36</v>
+      </c>
+      <c r="D121">
         <v>233.7</v>
       </c>
-      <c r="D121">
+      <c r="E121">
+        <v>11.69</v>
+      </c>
+      <c r="F121">
         <v>258.0</v>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="G121">
+        <v>12.9</v>
+      </c>
+      <c r="H121" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2366,12 +3461,21 @@
         <v>208.3</v>
       </c>
       <c r="C122">
+        <v>10.42</v>
+      </c>
+      <c r="D122">
         <v>234.0</v>
       </c>
-      <c r="D122">
+      <c r="E122">
+        <v>11.7</v>
+      </c>
+      <c r="F122">
         <v>257.4</v>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="G122">
+        <v>12.87</v>
+      </c>
+      <c r="H122" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2385,12 +3489,21 @@
         <v>206.0</v>
       </c>
       <c r="C123">
+        <v>10.3</v>
+      </c>
+      <c r="D123">
         <v>234.4</v>
       </c>
-      <c r="D123">
+      <c r="E123">
+        <v>11.72</v>
+      </c>
+      <c r="F123">
         <v>259.5</v>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="G123">
+        <v>12.98</v>
+      </c>
+      <c r="H123" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2404,12 +3517,21 @@
         <v>206.8</v>
       </c>
       <c r="C124">
+        <v>10.34</v>
+      </c>
+      <c r="D124">
         <v>234.9</v>
       </c>
-      <c r="D124">
+      <c r="E124">
+        <v>11.75</v>
+      </c>
+      <c r="F124">
         <v>259.7</v>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="G124">
+        <v>12.98</v>
+      </c>
+      <c r="H124" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2423,12 +3545,21 @@
         <v>207.1</v>
       </c>
       <c r="C125">
+        <v>10.36</v>
+      </c>
+      <c r="D125">
         <v>235.3</v>
       </c>
-      <c r="D125">
+      <c r="E125">
+        <v>11.77</v>
+      </c>
+      <c r="F125">
         <v>258.0</v>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="G125">
+        <v>12.9</v>
+      </c>
+      <c r="H125" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2442,12 +3573,21 @@
         <v>209.6</v>
       </c>
       <c r="C126">
+        <v>10.48</v>
+      </c>
+      <c r="D126">
         <v>234.8</v>
       </c>
-      <c r="D126">
+      <c r="E126">
+        <v>11.74</v>
+      </c>
+      <c r="F126">
         <v>259.7</v>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="G126">
+        <v>12.98</v>
+      </c>
+      <c r="H126" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2461,12 +3601,21 @@
         <v>206.5</v>
       </c>
       <c r="C127">
+        <v>10.33</v>
+      </c>
+      <c r="D127">
         <v>233.3</v>
       </c>
-      <c r="D127">
+      <c r="E127">
+        <v>11.67</v>
+      </c>
+      <c r="F127">
         <v>260.6</v>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="G127">
+        <v>13.03</v>
+      </c>
+      <c r="H127" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2480,12 +3629,21 @@
         <v>209.9</v>
       </c>
       <c r="C128">
+        <v>10.5</v>
+      </c>
+      <c r="D128">
         <v>234.7</v>
       </c>
-      <c r="D128">
+      <c r="E128">
+        <v>11.73</v>
+      </c>
+      <c r="F128">
         <v>259.3</v>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="G128">
+        <v>12.97</v>
+      </c>
+      <c r="H128" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2499,12 +3657,21 @@
         <v>210.2</v>
       </c>
       <c r="C129">
+        <v>10.51</v>
+      </c>
+      <c r="D129">
         <v>234.6</v>
       </c>
-      <c r="D129">
+      <c r="E129">
+        <v>11.73</v>
+      </c>
+      <c r="F129">
         <v>261.7</v>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="G129">
+        <v>13.09</v>
+      </c>
+      <c r="H129" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2518,12 +3685,21 @@
         <v>209.5</v>
       </c>
       <c r="C130">
+        <v>10.48</v>
+      </c>
+      <c r="D130">
         <v>233.6</v>
       </c>
-      <c r="D130">
+      <c r="E130">
+        <v>11.68</v>
+      </c>
+      <c r="F130">
         <v>261.2</v>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="G130">
+        <v>13.06</v>
+      </c>
+      <c r="H130" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2537,12 +3713,21 @@
         <v>209.8</v>
       </c>
       <c r="C131">
+        <v>10.49</v>
+      </c>
+      <c r="D131">
         <v>234.6</v>
       </c>
-      <c r="D131">
+      <c r="E131">
+        <v>11.73</v>
+      </c>
+      <c r="F131">
         <v>262.3</v>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="G131">
+        <v>13.12</v>
+      </c>
+      <c r="H131" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2556,12 +3741,21 @@
         <v>211.9</v>
       </c>
       <c r="C132">
+        <v>10.6</v>
+      </c>
+      <c r="D132">
         <v>236.1</v>
       </c>
-      <c r="D132">
+      <c r="E132">
+        <v>11.8</v>
+      </c>
+      <c r="F132">
         <v>262.5</v>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="G132">
+        <v>13.12</v>
+      </c>
+      <c r="H132" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2575,12 +3769,21 @@
         <v>211.6</v>
       </c>
       <c r="C133">
+        <v>10.58</v>
+      </c>
+      <c r="D133">
         <v>236.9</v>
       </c>
-      <c r="D133">
+      <c r="E133">
+        <v>11.85</v>
+      </c>
+      <c r="F133">
         <v>261.9</v>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="G133">
+        <v>13.09</v>
+      </c>
+      <c r="H133" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2594,12 +3797,21 @@
         <v>213.1</v>
       </c>
       <c r="C134">
+        <v>10.66</v>
+      </c>
+      <c r="D134">
         <v>236.5</v>
       </c>
-      <c r="D134">
+      <c r="E134">
+        <v>11.83</v>
+      </c>
+      <c r="F134">
         <v>262.1</v>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="G134">
+        <v>13.11</v>
+      </c>
+      <c r="H134" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2613,12 +3825,21 @@
         <v>211.8</v>
       </c>
       <c r="C135">
+        <v>10.59</v>
+      </c>
+      <c r="D135">
         <v>236.4</v>
       </c>
-      <c r="D135">
+      <c r="E135">
+        <v>11.82</v>
+      </c>
+      <c r="F135">
         <v>261.0</v>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="G135">
+        <v>13.05</v>
+      </c>
+      <c r="H135" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2632,12 +3853,21 @@
         <v>211.5</v>
       </c>
       <c r="C136">
+        <v>10.58</v>
+      </c>
+      <c r="D136">
         <v>237.7</v>
       </c>
-      <c r="D136">
+      <c r="E136">
+        <v>11.88</v>
+      </c>
+      <c r="F136">
         <v>261.0</v>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="G136">
+        <v>13.05</v>
+      </c>
+      <c r="H136" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2651,12 +3881,21 @@
         <v>211.3</v>
       </c>
       <c r="C137">
+        <v>10.57</v>
+      </c>
+      <c r="D137">
         <v>238.3</v>
       </c>
-      <c r="D137">
+      <c r="E137">
+        <v>11.92</v>
+      </c>
+      <c r="F137">
         <v>259.8</v>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="G137">
+        <v>12.99</v>
+      </c>
+      <c r="H137" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2670,12 +3909,21 @@
         <v>209.9</v>
       </c>
       <c r="C138">
+        <v>10.5</v>
+      </c>
+      <c r="D138">
         <v>238.5</v>
       </c>
-      <c r="D138">
+      <c r="E138">
+        <v>11.93</v>
+      </c>
+      <c r="F138">
         <v>259.4</v>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="G138">
+        <v>12.97</v>
+      </c>
+      <c r="H138" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2689,12 +3937,21 @@
         <v>211.4</v>
       </c>
       <c r="C139">
+        <v>10.57</v>
+      </c>
+      <c r="D139">
         <v>238.3</v>
       </c>
-      <c r="D139">
+      <c r="E139">
+        <v>11.92</v>
+      </c>
+      <c r="F139">
         <v>257.9</v>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="G139">
+        <v>12.89</v>
+      </c>
+      <c r="H139" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2708,12 +3965,21 @@
         <v>208.8</v>
       </c>
       <c r="C140">
+        <v>10.44</v>
+      </c>
+      <c r="D140">
         <v>238.9</v>
       </c>
-      <c r="D140">
+      <c r="E140">
+        <v>11.95</v>
+      </c>
+      <c r="F140">
         <v>257.8</v>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="G140">
+        <v>12.89</v>
+      </c>
+      <c r="H140" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2727,12 +3993,21 @@
         <v>210.0</v>
       </c>
       <c r="C141">
+        <v>10.5</v>
+      </c>
+      <c r="D141">
         <v>237.3</v>
       </c>
-      <c r="D141">
+      <c r="E141">
+        <v>11.87</v>
+      </c>
+      <c r="F141">
         <v>257.0</v>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="G141">
+        <v>12.85</v>
+      </c>
+      <c r="H141" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2746,12 +4021,21 @@
         <v>210.4</v>
       </c>
       <c r="C142">
+        <v>10.52</v>
+      </c>
+      <c r="D142">
         <v>240.4</v>
       </c>
-      <c r="D142">
+      <c r="E142">
+        <v>12.02</v>
+      </c>
+      <c r="F142">
         <v>256.8</v>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="G142">
+        <v>12.84</v>
+      </c>
+      <c r="H142" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2765,12 +4049,21 @@
         <v>209.2</v>
       </c>
       <c r="C143">
+        <v>10.46</v>
+      </c>
+      <c r="D143">
         <v>237.9</v>
       </c>
-      <c r="D143">
+      <c r="E143">
+        <v>11.9</v>
+      </c>
+      <c r="F143">
         <v>257.2</v>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="G143">
+        <v>12.86</v>
+      </c>
+      <c r="H143" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2784,12 +4077,21 @@
         <v>210.9</v>
       </c>
       <c r="C144">
+        <v>10.55</v>
+      </c>
+      <c r="D144">
         <v>237.6</v>
       </c>
-      <c r="D144">
+      <c r="E144">
+        <v>11.88</v>
+      </c>
+      <c r="F144">
         <v>254.9</v>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="G144">
+        <v>12.75</v>
+      </c>
+      <c r="H144" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2803,12 +4105,21 @@
         <v>209.4</v>
       </c>
       <c r="C145">
+        <v>10.47</v>
+      </c>
+      <c r="D145">
         <v>237.7</v>
       </c>
-      <c r="D145">
+      <c r="E145">
+        <v>11.88</v>
+      </c>
+      <c r="F145">
         <v>255.3</v>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="G145">
+        <v>12.77</v>
+      </c>
+      <c r="H145" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2822,12 +4133,21 @@
         <v>209.0</v>
       </c>
       <c r="C146">
+        <v>10.45</v>
+      </c>
+      <c r="D146">
         <v>238.6</v>
       </c>
-      <c r="D146">
+      <c r="E146">
+        <v>11.93</v>
+      </c>
+      <c r="F146">
         <v>254.5</v>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="G146">
+        <v>12.73</v>
+      </c>
+      <c r="H146" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2841,12 +4161,21 @@
         <v>210.2</v>
       </c>
       <c r="C147">
+        <v>10.51</v>
+      </c>
+      <c r="D147">
         <v>238.1</v>
       </c>
-      <c r="D147">
+      <c r="E147">
+        <v>11.91</v>
+      </c>
+      <c r="F147">
         <v>256.4</v>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="G147">
+        <v>12.82</v>
+      </c>
+      <c r="H147" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2860,12 +4189,21 @@
         <v>209.9</v>
       </c>
       <c r="C148">
+        <v>10.5</v>
+      </c>
+      <c r="D148">
         <v>235.2</v>
       </c>
-      <c r="D148">
+      <c r="E148">
+        <v>11.76</v>
+      </c>
+      <c r="F148">
         <v>254.6</v>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="G148">
+        <v>12.73</v>
+      </c>
+      <c r="H148" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2879,12 +4217,21 @@
         <v>210.2</v>
       </c>
       <c r="C149">
+        <v>10.51</v>
+      </c>
+      <c r="D149">
         <v>236.2</v>
       </c>
-      <c r="D149">
+      <c r="E149">
+        <v>11.81</v>
+      </c>
+      <c r="F149">
         <v>256.0</v>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="G149">
+        <v>12.8</v>
+      </c>
+      <c r="H149" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2898,12 +4245,21 @@
         <v>209.5</v>
       </c>
       <c r="C150">
+        <v>10.48</v>
+      </c>
+      <c r="D150">
         <v>235.5</v>
       </c>
-      <c r="D150">
+      <c r="E150">
+        <v>11.78</v>
+      </c>
+      <c r="F150">
         <v>254.1</v>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="G150">
+        <v>12.71</v>
+      </c>
+      <c r="H150" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2917,12 +4273,21 @@
         <v>210.7</v>
       </c>
       <c r="C151">
+        <v>10.54</v>
+      </c>
+      <c r="D151">
         <v>235.6</v>
       </c>
-      <c r="D151">
+      <c r="E151">
+        <v>11.78</v>
+      </c>
+      <c r="F151">
         <v>255.2</v>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="G151">
+        <v>12.76</v>
+      </c>
+      <c r="H151" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2936,12 +4301,21 @@
         <v>210.8</v>
       </c>
       <c r="C152">
+        <v>10.54</v>
+      </c>
+      <c r="D152">
         <v>233.8</v>
       </c>
-      <c r="D152">
+      <c r="E152">
+        <v>11.69</v>
+      </c>
+      <c r="F152">
         <v>257.7</v>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="G152">
+        <v>12.88</v>
+      </c>
+      <c r="H152" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2955,12 +4329,21 @@
         <v>209.3</v>
       </c>
       <c r="C153">
+        <v>10.47</v>
+      </c>
+      <c r="D153">
         <v>233.5</v>
       </c>
-      <c r="D153">
+      <c r="E153">
+        <v>11.68</v>
+      </c>
+      <c r="F153">
         <v>255.8</v>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="G153">
+        <v>12.79</v>
+      </c>
+      <c r="H153" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2974,12 +4357,21 @@
         <v>209.6</v>
       </c>
       <c r="C154">
+        <v>10.48</v>
+      </c>
+      <c r="D154">
         <v>232.8</v>
       </c>
-      <c r="D154">
+      <c r="E154">
+        <v>11.64</v>
+      </c>
+      <c r="F154">
         <v>255.8</v>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="G154">
+        <v>12.79</v>
+      </c>
+      <c r="H154" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -2993,12 +4385,21 @@
         <v>208.9</v>
       </c>
       <c r="C155">
+        <v>10.45</v>
+      </c>
+      <c r="D155">
         <v>232.9</v>
       </c>
-      <c r="D155">
+      <c r="E155">
+        <v>11.65</v>
+      </c>
+      <c r="F155">
         <v>255.5</v>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="G155">
+        <v>12.78</v>
+      </c>
+      <c r="H155" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3012,12 +4413,21 @@
         <v>211.2</v>
       </c>
       <c r="C156">
+        <v>10.56</v>
+      </c>
+      <c r="D156">
         <v>231.8</v>
       </c>
-      <c r="D156">
+      <c r="E156">
+        <v>11.59</v>
+      </c>
+      <c r="F156">
         <v>255.4</v>
       </c>
-      <c r="E156" t="inlineStr">
+      <c r="G156">
+        <v>12.77</v>
+      </c>
+      <c r="H156" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3031,12 +4441,21 @@
         <v>210.9</v>
       </c>
       <c r="C157">
+        <v>10.55</v>
+      </c>
+      <c r="D157">
         <v>231.5</v>
       </c>
-      <c r="D157">
+      <c r="E157">
+        <v>11.58</v>
+      </c>
+      <c r="F157">
         <v>256.6</v>
       </c>
-      <c r="E157" t="inlineStr">
+      <c r="G157">
+        <v>12.83</v>
+      </c>
+      <c r="H157" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3050,12 +4469,21 @@
         <v>209.8</v>
       </c>
       <c r="C158">
+        <v>10.49</v>
+      </c>
+      <c r="D158">
         <v>231.0</v>
       </c>
-      <c r="D158">
+      <c r="E158">
+        <v>11.55</v>
+      </c>
+      <c r="F158">
         <v>256.1</v>
       </c>
-      <c r="E158" t="inlineStr">
+      <c r="G158">
+        <v>12.81</v>
+      </c>
+      <c r="H158" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3069,12 +4497,21 @@
         <v>212.9</v>
       </c>
       <c r="C159">
+        <v>10.65</v>
+      </c>
+      <c r="D159">
         <v>230.2</v>
       </c>
-      <c r="D159">
+      <c r="E159">
+        <v>11.51</v>
+      </c>
+      <c r="F159">
         <v>258.3</v>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="G159">
+        <v>12.92</v>
+      </c>
+      <c r="H159" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3088,12 +4525,21 @@
         <v>212.0</v>
       </c>
       <c r="C160">
+        <v>10.6</v>
+      </c>
+      <c r="D160">
         <v>230.8</v>
       </c>
-      <c r="D160">
+      <c r="E160">
+        <v>11.54</v>
+      </c>
+      <c r="F160">
         <v>258.2</v>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="G160">
+        <v>12.91</v>
+      </c>
+      <c r="H160" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3107,12 +4553,21 @@
         <v>211.2</v>
       </c>
       <c r="C161">
+        <v>10.56</v>
+      </c>
+      <c r="D161">
         <v>229.6</v>
       </c>
-      <c r="D161">
+      <c r="E161">
+        <v>11.48</v>
+      </c>
+      <c r="F161">
         <v>258.4</v>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="G161">
+        <v>12.92</v>
+      </c>
+      <c r="H161" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3126,12 +4581,21 @@
         <v>211.8</v>
       </c>
       <c r="C162">
+        <v>10.59</v>
+      </c>
+      <c r="D162">
         <v>229.8</v>
       </c>
-      <c r="D162">
+      <c r="E162">
+        <v>11.49</v>
+      </c>
+      <c r="F162">
         <v>257.3</v>
       </c>
-      <c r="E162" t="inlineStr">
+      <c r="G162">
+        <v>12.87</v>
+      </c>
+      <c r="H162" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3145,12 +4609,21 @@
         <v>212.1</v>
       </c>
       <c r="C163">
+        <v>10.61</v>
+      </c>
+      <c r="D163">
         <v>229.4</v>
       </c>
-      <c r="D163">
+      <c r="E163">
+        <v>11.47</v>
+      </c>
+      <c r="F163">
         <v>258.0</v>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="G163">
+        <v>12.9</v>
+      </c>
+      <c r="H163" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3164,12 +4637,21 @@
         <v>211.5</v>
       </c>
       <c r="C164">
+        <v>10.58</v>
+      </c>
+      <c r="D164">
         <v>229.6</v>
       </c>
-      <c r="D164">
+      <c r="E164">
+        <v>11.48</v>
+      </c>
+      <c r="F164">
         <v>257.4</v>
       </c>
-      <c r="E164" t="inlineStr">
+      <c r="G164">
+        <v>12.87</v>
+      </c>
+      <c r="H164" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3183,12 +4665,21 @@
         <v>210.5</v>
       </c>
       <c r="C165">
+        <v>10.53</v>
+      </c>
+      <c r="D165">
         <v>229.8</v>
       </c>
-      <c r="D165">
+      <c r="E165">
+        <v>11.49</v>
+      </c>
+      <c r="F165">
         <v>260.2</v>
       </c>
-      <c r="E165" t="inlineStr">
+      <c r="G165">
+        <v>13.01</v>
+      </c>
+      <c r="H165" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3202,12 +4693,21 @@
         <v>210.5</v>
       </c>
       <c r="C166">
+        <v>10.53</v>
+      </c>
+      <c r="D166">
         <v>229.4</v>
       </c>
-      <c r="D166">
+      <c r="E166">
+        <v>11.47</v>
+      </c>
+      <c r="F166">
         <v>258.5</v>
       </c>
-      <c r="E166" t="inlineStr">
+      <c r="G166">
+        <v>12.93</v>
+      </c>
+      <c r="H166" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3221,12 +4721,21 @@
         <v>208.8</v>
       </c>
       <c r="C167">
+        <v>10.44</v>
+      </c>
+      <c r="D167">
         <v>230.9</v>
       </c>
-      <c r="D167">
+      <c r="E167">
+        <v>11.55</v>
+      </c>
+      <c r="F167">
         <v>260.8</v>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="G167">
+        <v>13.04</v>
+      </c>
+      <c r="H167" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3240,12 +4749,21 @@
         <v>207.5</v>
       </c>
       <c r="C168">
+        <v>10.38</v>
+      </c>
+      <c r="D168">
         <v>231.7</v>
       </c>
-      <c r="D168">
+      <c r="E168">
+        <v>11.59</v>
+      </c>
+      <c r="F168">
         <v>259.9</v>
       </c>
-      <c r="E168" t="inlineStr">
+      <c r="G168">
+        <v>12.99</v>
+      </c>
+      <c r="H168" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3259,12 +4777,21 @@
         <v>205.3</v>
       </c>
       <c r="C169">
+        <v>10.27</v>
+      </c>
+      <c r="D169">
         <v>232.0</v>
       </c>
-      <c r="D169">
+      <c r="E169">
+        <v>11.6</v>
+      </c>
+      <c r="F169">
         <v>259.5</v>
       </c>
-      <c r="E169" t="inlineStr">
+      <c r="G169">
+        <v>12.98</v>
+      </c>
+      <c r="H169" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3278,12 +4805,21 @@
         <v>205.4</v>
       </c>
       <c r="C170">
+        <v>10.27</v>
+      </c>
+      <c r="D170">
         <v>231.5</v>
       </c>
-      <c r="D170">
+      <c r="E170">
+        <v>11.58</v>
+      </c>
+      <c r="F170">
         <v>259.8</v>
       </c>
-      <c r="E170" t="inlineStr">
+      <c r="G170">
+        <v>12.99</v>
+      </c>
+      <c r="H170" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3297,12 +4833,21 @@
         <v>204.7</v>
       </c>
       <c r="C171">
+        <v>10.23</v>
+      </c>
+      <c r="D171">
         <v>231.4</v>
       </c>
-      <c r="D171">
+      <c r="E171">
+        <v>11.57</v>
+      </c>
+      <c r="F171">
         <v>259.8</v>
       </c>
-      <c r="E171" t="inlineStr">
+      <c r="G171">
+        <v>12.99</v>
+      </c>
+      <c r="H171" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3316,12 +4861,21 @@
         <v>204.9</v>
       </c>
       <c r="C172">
+        <v>10.25</v>
+      </c>
+      <c r="D172">
         <v>232.3</v>
       </c>
-      <c r="D172">
+      <c r="E172">
+        <v>11.62</v>
+      </c>
+      <c r="F172">
         <v>258.4</v>
       </c>
-      <c r="E172" t="inlineStr">
+      <c r="G172">
+        <v>12.92</v>
+      </c>
+      <c r="H172" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3335,12 +4889,21 @@
         <v>203.7</v>
       </c>
       <c r="C173">
+        <v>10.19</v>
+      </c>
+      <c r="D173">
         <v>232.4</v>
       </c>
-      <c r="D173">
+      <c r="E173">
+        <v>11.62</v>
+      </c>
+      <c r="F173">
         <v>257.5</v>
       </c>
-      <c r="E173" t="inlineStr">
+      <c r="G173">
+        <v>12.88</v>
+      </c>
+      <c r="H173" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3354,12 +4917,21 @@
         <v>205.4</v>
       </c>
       <c r="C174">
+        <v>10.27</v>
+      </c>
+      <c r="D174">
         <v>233.1</v>
       </c>
-      <c r="D174">
+      <c r="E174">
+        <v>11.66</v>
+      </c>
+      <c r="F174">
         <v>258.4</v>
       </c>
-      <c r="E174" t="inlineStr">
+      <c r="G174">
+        <v>12.92</v>
+      </c>
+      <c r="H174" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3373,12 +4945,21 @@
         <v>206.5</v>
       </c>
       <c r="C175">
+        <v>10.33</v>
+      </c>
+      <c r="D175">
         <v>233.8</v>
       </c>
-      <c r="D175">
+      <c r="E175">
+        <v>11.69</v>
+      </c>
+      <c r="F175">
         <v>258.6</v>
       </c>
-      <c r="E175" t="inlineStr">
+      <c r="G175">
+        <v>12.93</v>
+      </c>
+      <c r="H175" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3392,12 +4973,21 @@
         <v>204.4</v>
       </c>
       <c r="C176">
+        <v>10.22</v>
+      </c>
+      <c r="D176">
         <v>233.2</v>
       </c>
-      <c r="D176">
+      <c r="E176">
+        <v>11.66</v>
+      </c>
+      <c r="F176">
         <v>258.4</v>
       </c>
-      <c r="E176" t="inlineStr">
+      <c r="G176">
+        <v>12.92</v>
+      </c>
+      <c r="H176" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3411,12 +5001,21 @@
         <v>205.8</v>
       </c>
       <c r="C177">
+        <v>10.29</v>
+      </c>
+      <c r="D177">
         <v>235.0</v>
       </c>
-      <c r="D177">
+      <c r="E177">
+        <v>11.75</v>
+      </c>
+      <c r="F177">
         <v>257.9</v>
       </c>
-      <c r="E177" t="inlineStr">
+      <c r="G177">
+        <v>12.89</v>
+      </c>
+      <c r="H177" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3430,12 +5029,21 @@
         <v>205.5</v>
       </c>
       <c r="C178">
+        <v>10.28</v>
+      </c>
+      <c r="D178">
         <v>234.1</v>
       </c>
-      <c r="D178">
+      <c r="E178">
+        <v>11.71</v>
+      </c>
+      <c r="F178">
         <v>260.1</v>
       </c>
-      <c r="E178" t="inlineStr">
+      <c r="G178">
+        <v>13.01</v>
+      </c>
+      <c r="H178" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3449,12 +5057,21 @@
         <v>206.5</v>
       </c>
       <c r="C179">
+        <v>10.33</v>
+      </c>
+      <c r="D179">
         <v>232.4</v>
       </c>
-      <c r="D179">
+      <c r="E179">
+        <v>11.62</v>
+      </c>
+      <c r="F179">
         <v>260.8</v>
       </c>
-      <c r="E179" t="inlineStr">
+      <c r="G179">
+        <v>13.04</v>
+      </c>
+      <c r="H179" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3468,12 +5085,21 @@
         <v>207.4</v>
       </c>
       <c r="C180">
+        <v>10.37</v>
+      </c>
+      <c r="D180">
         <v>235.0</v>
       </c>
-      <c r="D180">
+      <c r="E180">
+        <v>11.75</v>
+      </c>
+      <c r="F180">
         <v>260.6</v>
       </c>
-      <c r="E180" t="inlineStr">
+      <c r="G180">
+        <v>13.03</v>
+      </c>
+      <c r="H180" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3487,12 +5113,21 @@
         <v>205.8</v>
       </c>
       <c r="C181">
+        <v>10.29</v>
+      </c>
+      <c r="D181">
         <v>233.8</v>
       </c>
-      <c r="D181">
+      <c r="E181">
+        <v>11.69</v>
+      </c>
+      <c r="F181">
         <v>258.6</v>
       </c>
-      <c r="E181" t="inlineStr">
+      <c r="G181">
+        <v>12.93</v>
+      </c>
+      <c r="H181" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3506,12 +5141,21 @@
         <v>205.8</v>
       </c>
       <c r="C182">
+        <v>10.29</v>
+      </c>
+      <c r="D182">
         <v>233.5</v>
       </c>
-      <c r="D182">
+      <c r="E182">
+        <v>11.68</v>
+      </c>
+      <c r="F182">
         <v>259.2</v>
       </c>
-      <c r="E182" t="inlineStr">
+      <c r="G182">
+        <v>12.96</v>
+      </c>
+      <c r="H182" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3525,12 +5169,21 @@
         <v>206.1</v>
       </c>
       <c r="C183">
+        <v>10.3</v>
+      </c>
+      <c r="D183">
         <v>231.5</v>
       </c>
-      <c r="D183">
+      <c r="E183">
+        <v>11.58</v>
+      </c>
+      <c r="F183">
         <v>259.3</v>
       </c>
-      <c r="E183" t="inlineStr">
+      <c r="G183">
+        <v>12.97</v>
+      </c>
+      <c r="H183" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3544,12 +5197,21 @@
         <v>205.8</v>
       </c>
       <c r="C184">
+        <v>10.29</v>
+      </c>
+      <c r="D184">
         <v>232.6</v>
       </c>
-      <c r="D184">
+      <c r="E184">
+        <v>11.63</v>
+      </c>
+      <c r="F184">
         <v>260.8</v>
       </c>
-      <c r="E184" t="inlineStr">
+      <c r="G184">
+        <v>13.04</v>
+      </c>
+      <c r="H184" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3563,12 +5225,21 @@
         <v>204.3</v>
       </c>
       <c r="C185">
+        <v>10.22</v>
+      </c>
+      <c r="D185">
         <v>231.6</v>
       </c>
-      <c r="D185">
+      <c r="E185">
+        <v>11.58</v>
+      </c>
+      <c r="F185">
         <v>261.7</v>
       </c>
-      <c r="E185" t="inlineStr">
+      <c r="G185">
+        <v>13.09</v>
+      </c>
+      <c r="H185" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3582,12 +5253,21 @@
         <v>204.3</v>
       </c>
       <c r="C186">
+        <v>10.22</v>
+      </c>
+      <c r="D186">
         <v>229.1</v>
       </c>
-      <c r="D186">
+      <c r="E186">
+        <v>11.46</v>
+      </c>
+      <c r="F186">
         <v>261.5</v>
       </c>
-      <c r="E186" t="inlineStr">
+      <c r="G186">
+        <v>13.08</v>
+      </c>
+      <c r="H186" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3601,12 +5281,21 @@
         <v>205.6</v>
       </c>
       <c r="C187">
+        <v>10.28</v>
+      </c>
+      <c r="D187">
         <v>229.7</v>
       </c>
-      <c r="D187">
+      <c r="E187">
+        <v>11.48</v>
+      </c>
+      <c r="F187">
         <v>259.7</v>
       </c>
-      <c r="E187" t="inlineStr">
+      <c r="G187">
+        <v>12.98</v>
+      </c>
+      <c r="H187" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3620,12 +5309,21 @@
         <v>205.2</v>
       </c>
       <c r="C188">
+        <v>10.26</v>
+      </c>
+      <c r="D188">
         <v>226.9</v>
       </c>
-      <c r="D188">
+      <c r="E188">
+        <v>11.35</v>
+      </c>
+      <c r="F188">
         <v>260.4</v>
       </c>
-      <c r="E188" t="inlineStr">
+      <c r="G188">
+        <v>13.02</v>
+      </c>
+      <c r="H188" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3639,12 +5337,21 @@
         <v>204.8</v>
       </c>
       <c r="C189">
+        <v>10.24</v>
+      </c>
+      <c r="D189">
         <v>228.9</v>
       </c>
-      <c r="D189">
+      <c r="E189">
+        <v>11.45</v>
+      </c>
+      <c r="F189">
         <v>260.5</v>
       </c>
-      <c r="E189" t="inlineStr">
+      <c r="G189">
+        <v>13.03</v>
+      </c>
+      <c r="H189" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3658,12 +5365,21 @@
         <v>204.9</v>
       </c>
       <c r="C190">
+        <v>10.25</v>
+      </c>
+      <c r="D190">
         <v>227.4</v>
       </c>
-      <c r="D190">
+      <c r="E190">
+        <v>11.37</v>
+      </c>
+      <c r="F190">
         <v>260.7</v>
       </c>
-      <c r="E190" t="inlineStr">
+      <c r="G190">
+        <v>13.04</v>
+      </c>
+      <c r="H190" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3677,12 +5393,21 @@
         <v>204.7</v>
       </c>
       <c r="C191">
+        <v>10.23</v>
+      </c>
+      <c r="D191">
         <v>226.9</v>
       </c>
-      <c r="D191">
+      <c r="E191">
+        <v>11.35</v>
+      </c>
+      <c r="F191">
         <v>260.3</v>
       </c>
-      <c r="E191" t="inlineStr">
+      <c r="G191">
+        <v>13.02</v>
+      </c>
+      <c r="H191" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3696,12 +5421,21 @@
         <v>205.0</v>
       </c>
       <c r="C192">
+        <v>10.25</v>
+      </c>
+      <c r="D192">
         <v>227.1</v>
       </c>
-      <c r="D192">
+      <c r="E192">
+        <v>11.36</v>
+      </c>
+      <c r="F192">
         <v>260.8</v>
       </c>
-      <c r="E192" t="inlineStr">
+      <c r="G192">
+        <v>13.04</v>
+      </c>
+      <c r="H192" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3715,12 +5449,21 @@
         <v>203.7</v>
       </c>
       <c r="C193">
+        <v>10.19</v>
+      </c>
+      <c r="D193">
         <v>226.7</v>
       </c>
-      <c r="D193">
+      <c r="E193">
+        <v>11.34</v>
+      </c>
+      <c r="F193">
         <v>260.9</v>
       </c>
-      <c r="E193" t="inlineStr">
+      <c r="G193">
+        <v>13.04</v>
+      </c>
+      <c r="H193" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3734,12 +5477,21 @@
         <v>205.6</v>
       </c>
       <c r="C194">
+        <v>10.28</v>
+      </c>
+      <c r="D194">
         <v>225.0</v>
       </c>
-      <c r="D194">
+      <c r="E194">
+        <v>11.25</v>
+      </c>
+      <c r="F194">
         <v>258.9</v>
       </c>
-      <c r="E194" t="inlineStr">
+      <c r="G194">
+        <v>12.95</v>
+      </c>
+      <c r="H194" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3753,12 +5505,21 @@
         <v>203.7</v>
       </c>
       <c r="C195">
+        <v>10.19</v>
+      </c>
+      <c r="D195">
         <v>225.9</v>
       </c>
-      <c r="D195">
+      <c r="E195">
+        <v>11.3</v>
+      </c>
+      <c r="F195">
         <v>257.3</v>
       </c>
-      <c r="E195" t="inlineStr">
+      <c r="G195">
+        <v>12.87</v>
+      </c>
+      <c r="H195" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3772,12 +5533,21 @@
         <v>202.9</v>
       </c>
       <c r="C196">
+        <v>10.15</v>
+      </c>
+      <c r="D196">
         <v>227.2</v>
       </c>
-      <c r="D196">
+      <c r="E196">
+        <v>11.36</v>
+      </c>
+      <c r="F196">
         <v>256.8</v>
       </c>
-      <c r="E196" t="inlineStr">
+      <c r="G196">
+        <v>12.84</v>
+      </c>
+      <c r="H196" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3791,12 +5561,21 @@
         <v>201.7</v>
       </c>
       <c r="C197">
+        <v>10.09</v>
+      </c>
+      <c r="D197">
         <v>228.1</v>
       </c>
-      <c r="D197">
+      <c r="E197">
+        <v>11.41</v>
+      </c>
+      <c r="F197">
         <v>255.8</v>
       </c>
-      <c r="E197" t="inlineStr">
+      <c r="G197">
+        <v>12.79</v>
+      </c>
+      <c r="H197" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3810,12 +5589,21 @@
         <v>204.4</v>
       </c>
       <c r="C198">
+        <v>10.22</v>
+      </c>
+      <c r="D198">
         <v>227.5</v>
       </c>
-      <c r="D198">
+      <c r="E198">
+        <v>11.38</v>
+      </c>
+      <c r="F198">
         <v>254.8</v>
       </c>
-      <c r="E198" t="inlineStr">
+      <c r="G198">
+        <v>12.74</v>
+      </c>
+      <c r="H198" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3829,12 +5617,21 @@
         <v>203.7</v>
       </c>
       <c r="C199">
+        <v>10.19</v>
+      </c>
+      <c r="D199">
         <v>227.9</v>
       </c>
-      <c r="D199">
+      <c r="E199">
+        <v>11.4</v>
+      </c>
+      <c r="F199">
         <v>251.5</v>
       </c>
-      <c r="E199" t="inlineStr">
+      <c r="G199">
+        <v>12.58</v>
+      </c>
+      <c r="H199" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3848,12 +5645,21 @@
         <v>202.8</v>
       </c>
       <c r="C200">
+        <v>10.14</v>
+      </c>
+      <c r="D200">
         <v>229.3</v>
       </c>
-      <c r="D200">
+      <c r="E200">
+        <v>11.47</v>
+      </c>
+      <c r="F200">
         <v>252.7</v>
       </c>
-      <c r="E200" t="inlineStr">
+      <c r="G200">
+        <v>12.63</v>
+      </c>
+      <c r="H200" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3867,12 +5673,21 @@
         <v>203.9</v>
       </c>
       <c r="C201">
+        <v>10.2</v>
+      </c>
+      <c r="D201">
         <v>230.8</v>
       </c>
-      <c r="D201">
+      <c r="E201">
+        <v>11.54</v>
+      </c>
+      <c r="F201">
         <v>250.7</v>
       </c>
-      <c r="E201" t="inlineStr">
+      <c r="G201">
+        <v>12.54</v>
+      </c>
+      <c r="H201" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3886,12 +5701,21 @@
         <v>203.2</v>
       </c>
       <c r="C202">
+        <v>10.16</v>
+      </c>
+      <c r="D202">
         <v>231.0</v>
       </c>
-      <c r="D202">
+      <c r="E202">
+        <v>11.55</v>
+      </c>
+      <c r="F202">
         <v>251.0</v>
       </c>
-      <c r="E202" t="inlineStr">
+      <c r="G202">
+        <v>12.55</v>
+      </c>
+      <c r="H202" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3905,12 +5729,21 @@
         <v>202.8</v>
       </c>
       <c r="C203">
+        <v>10.14</v>
+      </c>
+      <c r="D203">
         <v>231.0</v>
       </c>
-      <c r="D203">
+      <c r="E203">
+        <v>11.55</v>
+      </c>
+      <c r="F203">
         <v>251.3</v>
       </c>
-      <c r="E203" t="inlineStr">
+      <c r="G203">
+        <v>12.57</v>
+      </c>
+      <c r="H203" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3924,12 +5757,21 @@
         <v>204.1</v>
       </c>
       <c r="C204">
+        <v>10.21</v>
+      </c>
+      <c r="D204">
         <v>229.2</v>
       </c>
-      <c r="D204">
+      <c r="E204">
+        <v>11.46</v>
+      </c>
+      <c r="F204">
         <v>251.9</v>
       </c>
-      <c r="E204" t="inlineStr">
+      <c r="G204">
+        <v>12.6</v>
+      </c>
+      <c r="H204" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3943,12 +5785,21 @@
         <v>204.1</v>
       </c>
       <c r="C205">
+        <v>10.21</v>
+      </c>
+      <c r="D205">
         <v>229.3</v>
       </c>
-      <c r="D205">
+      <c r="E205">
+        <v>11.47</v>
+      </c>
+      <c r="F205">
         <v>253.5</v>
       </c>
-      <c r="E205" t="inlineStr">
+      <c r="G205">
+        <v>12.68</v>
+      </c>
+      <c r="H205" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3962,12 +5813,21 @@
         <v>205.6</v>
       </c>
       <c r="C206">
+        <v>10.28</v>
+      </c>
+      <c r="D206">
         <v>227.9</v>
       </c>
-      <c r="D206">
+      <c r="E206">
+        <v>11.4</v>
+      </c>
+      <c r="F206">
         <v>254.4</v>
       </c>
-      <c r="E206" t="inlineStr">
+      <c r="G206">
+        <v>12.72</v>
+      </c>
+      <c r="H206" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -3981,12 +5841,21 @@
         <v>204.7</v>
       </c>
       <c r="C207">
+        <v>10.23</v>
+      </c>
+      <c r="D207">
         <v>229.5</v>
       </c>
-      <c r="D207">
+      <c r="E207">
+        <v>11.48</v>
+      </c>
+      <c r="F207">
         <v>254.3</v>
       </c>
-      <c r="E207" t="inlineStr">
+      <c r="G207">
+        <v>12.72</v>
+      </c>
+      <c r="H207" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4000,12 +5869,21 @@
         <v>202.8</v>
       </c>
       <c r="C208">
+        <v>10.14</v>
+      </c>
+      <c r="D208">
         <v>227.1</v>
       </c>
-      <c r="D208">
+      <c r="E208">
+        <v>11.36</v>
+      </c>
+      <c r="F208">
         <v>253.3</v>
       </c>
-      <c r="E208" t="inlineStr">
+      <c r="G208">
+        <v>12.67</v>
+      </c>
+      <c r="H208" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4019,12 +5897,21 @@
         <v>205.6</v>
       </c>
       <c r="C209">
+        <v>10.28</v>
+      </c>
+      <c r="D209">
         <v>227.6</v>
       </c>
-      <c r="D209">
+      <c r="E209">
+        <v>11.38</v>
+      </c>
+      <c r="F209">
         <v>254.7</v>
       </c>
-      <c r="E209" t="inlineStr">
+      <c r="G209">
+        <v>12.73</v>
+      </c>
+      <c r="H209" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4038,12 +5925,21 @@
         <v>204.8</v>
       </c>
       <c r="C210">
+        <v>10.24</v>
+      </c>
+      <c r="D210">
         <v>226.1</v>
       </c>
-      <c r="D210">
+      <c r="E210">
+        <v>11.3</v>
+      </c>
+      <c r="F210">
         <v>253.4</v>
       </c>
-      <c r="E210" t="inlineStr">
+      <c r="G210">
+        <v>12.67</v>
+      </c>
+      <c r="H210" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4057,12 +5953,21 @@
         <v>205.9</v>
       </c>
       <c r="C211">
+        <v>10.3</v>
+      </c>
+      <c r="D211">
         <v>225.6</v>
       </c>
-      <c r="D211">
+      <c r="E211">
+        <v>11.28</v>
+      </c>
+      <c r="F211">
         <v>253.8</v>
       </c>
-      <c r="E211" t="inlineStr">
+      <c r="G211">
+        <v>12.69</v>
+      </c>
+      <c r="H211" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4076,12 +5981,21 @@
         <v>205.2</v>
       </c>
       <c r="C212">
+        <v>10.26</v>
+      </c>
+      <c r="D212">
         <v>225.6</v>
       </c>
-      <c r="D212">
+      <c r="E212">
+        <v>11.28</v>
+      </c>
+      <c r="F212">
         <v>254.4</v>
       </c>
-      <c r="E212" t="inlineStr">
+      <c r="G212">
+        <v>12.72</v>
+      </c>
+      <c r="H212" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4095,12 +6009,21 @@
         <v>206.1</v>
       </c>
       <c r="C213">
+        <v>10.3</v>
+      </c>
+      <c r="D213">
         <v>226.1</v>
       </c>
-      <c r="D213">
+      <c r="E213">
+        <v>11.3</v>
+      </c>
+      <c r="F213">
         <v>254.8</v>
       </c>
-      <c r="E213" t="inlineStr">
+      <c r="G213">
+        <v>12.74</v>
+      </c>
+      <c r="H213" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4114,12 +6037,21 @@
         <v>206.5</v>
       </c>
       <c r="C214">
+        <v>10.33</v>
+      </c>
+      <c r="D214">
         <v>227.0</v>
       </c>
-      <c r="D214">
+      <c r="E214">
+        <v>11.35</v>
+      </c>
+      <c r="F214">
         <v>255.1</v>
       </c>
-      <c r="E214" t="inlineStr">
+      <c r="G214">
+        <v>12.76</v>
+      </c>
+      <c r="H214" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4133,12 +6065,21 @@
         <v>207.5</v>
       </c>
       <c r="C215">
+        <v>10.38</v>
+      </c>
+      <c r="D215">
         <v>227.2</v>
       </c>
-      <c r="D215">
+      <c r="E215">
+        <v>11.36</v>
+      </c>
+      <c r="F215">
         <v>254.7</v>
       </c>
-      <c r="E215" t="inlineStr">
+      <c r="G215">
+        <v>12.73</v>
+      </c>
+      <c r="H215" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4152,12 +6093,21 @@
         <v>207.3</v>
       </c>
       <c r="C216">
+        <v>10.37</v>
+      </c>
+      <c r="D216">
         <v>227.6</v>
       </c>
-      <c r="D216">
+      <c r="E216">
+        <v>11.38</v>
+      </c>
+      <c r="F216">
         <v>256.0</v>
       </c>
-      <c r="E216" t="inlineStr">
+      <c r="G216">
+        <v>12.8</v>
+      </c>
+      <c r="H216" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4171,12 +6121,21 @@
         <v>207.1</v>
       </c>
       <c r="C217">
+        <v>10.36</v>
+      </c>
+      <c r="D217">
         <v>228.2</v>
       </c>
-      <c r="D217">
+      <c r="E217">
+        <v>11.41</v>
+      </c>
+      <c r="F217">
         <v>256.2</v>
       </c>
-      <c r="E217" t="inlineStr">
+      <c r="G217">
+        <v>12.81</v>
+      </c>
+      <c r="H217" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4190,12 +6149,21 @@
         <v>207.9</v>
       </c>
       <c r="C218">
+        <v>10.4</v>
+      </c>
+      <c r="D218">
         <v>227.6</v>
       </c>
-      <c r="D218">
+      <c r="E218">
+        <v>11.38</v>
+      </c>
+      <c r="F218">
         <v>254.8</v>
       </c>
-      <c r="E218" t="inlineStr">
+      <c r="G218">
+        <v>12.74</v>
+      </c>
+      <c r="H218" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4209,12 +6177,21 @@
         <v>208.0</v>
       </c>
       <c r="C219">
+        <v>10.4</v>
+      </c>
+      <c r="D219">
         <v>226.8</v>
       </c>
-      <c r="D219">
+      <c r="E219">
+        <v>11.34</v>
+      </c>
+      <c r="F219">
         <v>254.8</v>
       </c>
-      <c r="E219" t="inlineStr">
+      <c r="G219">
+        <v>12.74</v>
+      </c>
+      <c r="H219" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4228,12 +6205,21 @@
         <v>207.7</v>
       </c>
       <c r="C220">
+        <v>10.38</v>
+      </c>
+      <c r="D220">
         <v>228.7</v>
       </c>
-      <c r="D220">
+      <c r="E220">
+        <v>11.44</v>
+      </c>
+      <c r="F220">
         <v>256.7</v>
       </c>
-      <c r="E220" t="inlineStr">
+      <c r="G220">
+        <v>12.84</v>
+      </c>
+      <c r="H220" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4247,12 +6233,21 @@
         <v>208.1</v>
       </c>
       <c r="C221">
+        <v>10.41</v>
+      </c>
+      <c r="D221">
         <v>228.4</v>
       </c>
-      <c r="D221">
+      <c r="E221">
+        <v>11.42</v>
+      </c>
+      <c r="F221">
         <v>258.2</v>
       </c>
-      <c r="E221" t="inlineStr">
+      <c r="G221">
+        <v>12.91</v>
+      </c>
+      <c r="H221" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4266,12 +6261,21 @@
         <v>208.2</v>
       </c>
       <c r="C222">
+        <v>10.41</v>
+      </c>
+      <c r="D222">
         <v>228.3</v>
       </c>
-      <c r="D222">
+      <c r="E222">
+        <v>11.42</v>
+      </c>
+      <c r="F222">
         <v>257.7</v>
       </c>
-      <c r="E222" t="inlineStr">
+      <c r="G222">
+        <v>12.88</v>
+      </c>
+      <c r="H222" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4285,12 +6289,21 @@
         <v>206.3</v>
       </c>
       <c r="C223">
+        <v>10.32</v>
+      </c>
+      <c r="D223">
         <v>230.0</v>
       </c>
-      <c r="D223">
+      <c r="E223">
+        <v>11.5</v>
+      </c>
+      <c r="F223">
         <v>257.8</v>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="G223">
+        <v>12.89</v>
+      </c>
+      <c r="H223" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4304,12 +6317,21 @@
         <v>207.1</v>
       </c>
       <c r="C224">
+        <v>10.36</v>
+      </c>
+      <c r="D224">
         <v>229.8</v>
       </c>
-      <c r="D224">
+      <c r="E224">
+        <v>11.49</v>
+      </c>
+      <c r="F224">
         <v>259.2</v>
       </c>
-      <c r="E224" t="inlineStr">
+      <c r="G224">
+        <v>12.96</v>
+      </c>
+      <c r="H224" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4323,12 +6345,21 @@
         <v>207.7</v>
       </c>
       <c r="C225">
+        <v>10.38</v>
+      </c>
+      <c r="D225">
         <v>229.9</v>
       </c>
-      <c r="D225">
+      <c r="E225">
+        <v>11.5</v>
+      </c>
+      <c r="F225">
         <v>259.0</v>
       </c>
-      <c r="E225" t="inlineStr">
+      <c r="G225">
+        <v>12.95</v>
+      </c>
+      <c r="H225" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4342,12 +6373,21 @@
         <v>207.5</v>
       </c>
       <c r="C226">
+        <v>10.38</v>
+      </c>
+      <c r="D226">
         <v>231.6</v>
       </c>
-      <c r="D226">
+      <c r="E226">
+        <v>11.58</v>
+      </c>
+      <c r="F226">
         <v>261.3</v>
       </c>
-      <c r="E226" t="inlineStr">
+      <c r="G226">
+        <v>13.07</v>
+      </c>
+      <c r="H226" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4361,12 +6401,21 @@
         <v>207.9</v>
       </c>
       <c r="C227">
+        <v>10.4</v>
+      </c>
+      <c r="D227">
         <v>232.2</v>
       </c>
-      <c r="D227">
+      <c r="E227">
+        <v>11.61</v>
+      </c>
+      <c r="F227">
         <v>260.9</v>
       </c>
-      <c r="E227" t="inlineStr">
+      <c r="G227">
+        <v>13.04</v>
+      </c>
+      <c r="H227" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4380,12 +6429,21 @@
         <v>209.0</v>
       </c>
       <c r="C228">
+        <v>10.45</v>
+      </c>
+      <c r="D228">
         <v>233.7</v>
       </c>
-      <c r="D228">
+      <c r="E228">
+        <v>11.69</v>
+      </c>
+      <c r="F228">
         <v>261.6</v>
       </c>
-      <c r="E228" t="inlineStr">
+      <c r="G228">
+        <v>13.08</v>
+      </c>
+      <c r="H228" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4399,12 +6457,21 @@
         <v>209.1</v>
       </c>
       <c r="C229">
+        <v>10.46</v>
+      </c>
+      <c r="D229">
         <v>235.7</v>
       </c>
-      <c r="D229">
+      <c r="E229">
+        <v>11.79</v>
+      </c>
+      <c r="F229">
         <v>263.0</v>
       </c>
-      <c r="E229" t="inlineStr">
+      <c r="G229">
+        <v>13.15</v>
+      </c>
+      <c r="H229" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4418,12 +6485,21 @@
         <v>209.7</v>
       </c>
       <c r="C230">
+        <v>10.48</v>
+      </c>
+      <c r="D230">
         <v>234.9</v>
       </c>
-      <c r="D230">
+      <c r="E230">
+        <v>11.75</v>
+      </c>
+      <c r="F230">
         <v>263.8</v>
       </c>
-      <c r="E230" t="inlineStr">
+      <c r="G230">
+        <v>13.19</v>
+      </c>
+      <c r="H230" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4437,12 +6513,21 @@
         <v>210.9</v>
       </c>
       <c r="C231">
+        <v>10.55</v>
+      </c>
+      <c r="D231">
         <v>235.8</v>
       </c>
-      <c r="D231">
+      <c r="E231">
+        <v>11.79</v>
+      </c>
+      <c r="F231">
         <v>264.2</v>
       </c>
-      <c r="E231" t="inlineStr">
+      <c r="G231">
+        <v>13.21</v>
+      </c>
+      <c r="H231" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4456,12 +6541,21 @@
         <v>211.4</v>
       </c>
       <c r="C232">
+        <v>10.57</v>
+      </c>
+      <c r="D232">
         <v>236.9</v>
       </c>
-      <c r="D232">
+      <c r="E232">
+        <v>11.85</v>
+      </c>
+      <c r="F232">
         <v>265.2</v>
       </c>
-      <c r="E232" t="inlineStr">
+      <c r="G232">
+        <v>13.26</v>
+      </c>
+      <c r="H232" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4475,12 +6569,21 @@
         <v>210.2</v>
       </c>
       <c r="C233">
+        <v>10.51</v>
+      </c>
+      <c r="D233">
         <v>237.0</v>
       </c>
-      <c r="D233">
+      <c r="E233">
+        <v>11.85</v>
+      </c>
+      <c r="F233">
         <v>264.1</v>
       </c>
-      <c r="E233" t="inlineStr">
+      <c r="G233">
+        <v>13.21</v>
+      </c>
+      <c r="H233" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4494,12 +6597,21 @@
         <v>210.5</v>
       </c>
       <c r="C234">
+        <v>10.53</v>
+      </c>
+      <c r="D234">
         <v>235.5</v>
       </c>
-      <c r="D234">
+      <c r="E234">
+        <v>11.78</v>
+      </c>
+      <c r="F234">
         <v>265.1</v>
       </c>
-      <c r="E234" t="inlineStr">
+      <c r="G234">
+        <v>13.26</v>
+      </c>
+      <c r="H234" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4513,12 +6625,21 @@
         <v>208.8</v>
       </c>
       <c r="C235">
+        <v>10.44</v>
+      </c>
+      <c r="D235">
         <v>234.4</v>
       </c>
-      <c r="D235">
+      <c r="E235">
+        <v>11.72</v>
+      </c>
+      <c r="F235">
         <v>263.5</v>
       </c>
-      <c r="E235" t="inlineStr">
+      <c r="G235">
+        <v>13.18</v>
+      </c>
+      <c r="H235" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4532,12 +6653,21 @@
         <v>209.8</v>
       </c>
       <c r="C236">
+        <v>10.49</v>
+      </c>
+      <c r="D236">
         <v>234.6</v>
       </c>
-      <c r="D236">
+      <c r="E236">
+        <v>11.73</v>
+      </c>
+      <c r="F236">
         <v>262.8</v>
       </c>
-      <c r="E236" t="inlineStr">
+      <c r="G236">
+        <v>13.14</v>
+      </c>
+      <c r="H236" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4551,12 +6681,21 @@
         <v>209.1</v>
       </c>
       <c r="C237">
+        <v>10.46</v>
+      </c>
+      <c r="D237">
         <v>233.8</v>
       </c>
-      <c r="D237">
+      <c r="E237">
+        <v>11.69</v>
+      </c>
+      <c r="F237">
         <v>262.3</v>
       </c>
-      <c r="E237" t="inlineStr">
+      <c r="G237">
+        <v>13.12</v>
+      </c>
+      <c r="H237" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4570,12 +6709,21 @@
         <v>209.2</v>
       </c>
       <c r="C238">
+        <v>10.46</v>
+      </c>
+      <c r="D238">
         <v>232.9</v>
       </c>
-      <c r="D238">
+      <c r="E238">
+        <v>11.65</v>
+      </c>
+      <c r="F238">
         <v>261.9</v>
       </c>
-      <c r="E238" t="inlineStr">
+      <c r="G238">
+        <v>13.09</v>
+      </c>
+      <c r="H238" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4589,12 +6737,21 @@
         <v>209.6</v>
       </c>
       <c r="C239">
+        <v>10.48</v>
+      </c>
+      <c r="D239">
         <v>231.5</v>
       </c>
-      <c r="D239">
+      <c r="E239">
+        <v>11.58</v>
+      </c>
+      <c r="F239">
         <v>261.7</v>
       </c>
-      <c r="E239" t="inlineStr">
+      <c r="G239">
+        <v>13.09</v>
+      </c>
+      <c r="H239" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4608,12 +6765,21 @@
         <v>210.0</v>
       </c>
       <c r="C240">
+        <v>10.5</v>
+      </c>
+      <c r="D240">
         <v>233.0</v>
       </c>
-      <c r="D240">
+      <c r="E240">
+        <v>11.65</v>
+      </c>
+      <c r="F240">
         <v>260.9</v>
       </c>
-      <c r="E240" t="inlineStr">
+      <c r="G240">
+        <v>13.04</v>
+      </c>
+      <c r="H240" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4627,12 +6793,21 @@
         <v>208.9</v>
       </c>
       <c r="C241">
+        <v>10.45</v>
+      </c>
+      <c r="D241">
         <v>233.8</v>
       </c>
-      <c r="D241">
+      <c r="E241">
+        <v>11.69</v>
+      </c>
+      <c r="F241">
         <v>261.9</v>
       </c>
-      <c r="E241" t="inlineStr">
+      <c r="G241">
+        <v>13.09</v>
+      </c>
+      <c r="H241" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4646,12 +6821,21 @@
         <v>210.5</v>
       </c>
       <c r="C242">
+        <v>10.53</v>
+      </c>
+      <c r="D242">
         <v>231.4</v>
       </c>
-      <c r="D242">
+      <c r="E242">
+        <v>11.57</v>
+      </c>
+      <c r="F242">
         <v>259.0</v>
       </c>
-      <c r="E242" t="inlineStr">
+      <c r="G242">
+        <v>12.95</v>
+      </c>
+      <c r="H242" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4665,12 +6849,21 @@
         <v>208.8</v>
       </c>
       <c r="C243">
+        <v>10.44</v>
+      </c>
+      <c r="D243">
         <v>230.8</v>
       </c>
-      <c r="D243">
+      <c r="E243">
+        <v>11.54</v>
+      </c>
+      <c r="F243">
         <v>259.3</v>
       </c>
-      <c r="E243" t="inlineStr">
+      <c r="G243">
+        <v>12.97</v>
+      </c>
+      <c r="H243" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4684,12 +6877,21 @@
         <v>208.6</v>
       </c>
       <c r="C244">
+        <v>10.43</v>
+      </c>
+      <c r="D244">
         <v>230.6</v>
       </c>
-      <c r="D244">
+      <c r="E244">
+        <v>11.53</v>
+      </c>
+      <c r="F244">
         <v>257.8</v>
       </c>
-      <c r="E244" t="inlineStr">
+      <c r="G244">
+        <v>12.89</v>
+      </c>
+      <c r="H244" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4703,12 +6905,21 @@
         <v>209.7</v>
       </c>
       <c r="C245">
+        <v>10.48</v>
+      </c>
+      <c r="D245">
         <v>230.1</v>
       </c>
-      <c r="D245">
+      <c r="E245">
+        <v>11.51</v>
+      </c>
+      <c r="F245">
         <v>256.5</v>
       </c>
-      <c r="E245" t="inlineStr">
+      <c r="G245">
+        <v>12.83</v>
+      </c>
+      <c r="H245" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4722,12 +6933,21 @@
         <v>208.9</v>
       </c>
       <c r="C246">
+        <v>10.45</v>
+      </c>
+      <c r="D246">
         <v>231.2</v>
       </c>
-      <c r="D246">
+      <c r="E246">
+        <v>11.56</v>
+      </c>
+      <c r="F246">
         <v>256.2</v>
       </c>
-      <c r="E246" t="inlineStr">
+      <c r="G246">
+        <v>12.81</v>
+      </c>
+      <c r="H246" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4741,12 +6961,21 @@
         <v>207.7</v>
       </c>
       <c r="C247">
+        <v>10.38</v>
+      </c>
+      <c r="D247">
         <v>229.8</v>
       </c>
-      <c r="D247">
+      <c r="E247">
+        <v>11.49</v>
+      </c>
+      <c r="F247">
         <v>256.6</v>
       </c>
-      <c r="E247" t="inlineStr">
+      <c r="G247">
+        <v>12.83</v>
+      </c>
+      <c r="H247" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4760,12 +6989,21 @@
         <v>209.3</v>
       </c>
       <c r="C248">
+        <v>10.47</v>
+      </c>
+      <c r="D248">
         <v>229.9</v>
       </c>
-      <c r="D248">
+      <c r="E248">
+        <v>11.5</v>
+      </c>
+      <c r="F248">
         <v>256.7</v>
       </c>
-      <c r="E248" t="inlineStr">
+      <c r="G248">
+        <v>12.84</v>
+      </c>
+      <c r="H248" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4779,12 +7017,21 @@
         <v>209.8</v>
       </c>
       <c r="C249">
+        <v>10.49</v>
+      </c>
+      <c r="D249">
         <v>230.3</v>
       </c>
-      <c r="D249">
+      <c r="E249">
+        <v>11.52</v>
+      </c>
+      <c r="F249">
         <v>256.4</v>
       </c>
-      <c r="E249" t="inlineStr">
+      <c r="G249">
+        <v>12.82</v>
+      </c>
+      <c r="H249" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4798,12 +7045,21 @@
         <v>207.6</v>
       </c>
       <c r="C250">
+        <v>10.38</v>
+      </c>
+      <c r="D250">
         <v>230.8</v>
       </c>
-      <c r="D250">
+      <c r="E250">
+        <v>11.54</v>
+      </c>
+      <c r="F250">
         <v>254.6</v>
       </c>
-      <c r="E250" t="inlineStr">
+      <c r="G250">
+        <v>12.73</v>
+      </c>
+      <c r="H250" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4817,12 +7073,21 @@
         <v>209.1</v>
       </c>
       <c r="C251">
+        <v>10.46</v>
+      </c>
+      <c r="D251">
         <v>230.0</v>
       </c>
-      <c r="D251">
+      <c r="E251">
+        <v>11.5</v>
+      </c>
+      <c r="F251">
         <v>256.4</v>
       </c>
-      <c r="E251" t="inlineStr">
+      <c r="G251">
+        <v>12.82</v>
+      </c>
+      <c r="H251" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4836,12 +7101,21 @@
         <v>208.2</v>
       </c>
       <c r="C252">
+        <v>10.41</v>
+      </c>
+      <c r="D252">
         <v>231.1</v>
       </c>
-      <c r="D252">
+      <c r="E252">
+        <v>11.55</v>
+      </c>
+      <c r="F252">
         <v>256.4</v>
       </c>
-      <c r="E252" t="inlineStr">
+      <c r="G252">
+        <v>12.82</v>
+      </c>
+      <c r="H252" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4855,12 +7129,21 @@
         <v>207.6</v>
       </c>
       <c r="C253">
+        <v>10.38</v>
+      </c>
+      <c r="D253">
         <v>230.3</v>
       </c>
-      <c r="D253">
+      <c r="E253">
+        <v>11.52</v>
+      </c>
+      <c r="F253">
         <v>255.9</v>
       </c>
-      <c r="E253" t="inlineStr">
+      <c r="G253">
+        <v>12.8</v>
+      </c>
+      <c r="H253" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4874,12 +7157,21 @@
         <v>208.5</v>
       </c>
       <c r="C254">
+        <v>10.43</v>
+      </c>
+      <c r="D254">
         <v>230.8</v>
       </c>
-      <c r="D254">
+      <c r="E254">
+        <v>11.54</v>
+      </c>
+      <c r="F254">
         <v>257.5</v>
       </c>
-      <c r="E254" t="inlineStr">
+      <c r="G254">
+        <v>12.88</v>
+      </c>
+      <c r="H254" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4893,12 +7185,21 @@
         <v>208.8</v>
       </c>
       <c r="C255">
+        <v>10.44</v>
+      </c>
+      <c r="D255">
         <v>231.8</v>
       </c>
-      <c r="D255">
+      <c r="E255">
+        <v>11.59</v>
+      </c>
+      <c r="F255">
         <v>257.7</v>
       </c>
-      <c r="E255" t="inlineStr">
+      <c r="G255">
+        <v>12.88</v>
+      </c>
+      <c r="H255" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4912,12 +7213,21 @@
         <v>208.6</v>
       </c>
       <c r="C256">
+        <v>10.43</v>
+      </c>
+      <c r="D256">
         <v>232.4</v>
       </c>
-      <c r="D256">
+      <c r="E256">
+        <v>11.62</v>
+      </c>
+      <c r="F256">
         <v>258.2</v>
       </c>
-      <c r="E256" t="inlineStr">
+      <c r="G256">
+        <v>12.91</v>
+      </c>
+      <c r="H256" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4931,12 +7241,21 @@
         <v>209.8</v>
       </c>
       <c r="C257">
+        <v>10.49</v>
+      </c>
+      <c r="D257">
         <v>234.5</v>
       </c>
-      <c r="D257">
+      <c r="E257">
+        <v>11.73</v>
+      </c>
+      <c r="F257">
         <v>260.6</v>
       </c>
-      <c r="E257" t="inlineStr">
+      <c r="G257">
+        <v>13.03</v>
+      </c>
+      <c r="H257" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4950,12 +7269,21 @@
         <v>209.7</v>
       </c>
       <c r="C258">
+        <v>10.48</v>
+      </c>
+      <c r="D258">
         <v>234.9</v>
       </c>
-      <c r="D258">
+      <c r="E258">
+        <v>11.75</v>
+      </c>
+      <c r="F258">
         <v>259.6</v>
       </c>
-      <c r="E258" t="inlineStr">
+      <c r="G258">
+        <v>12.98</v>
+      </c>
+      <c r="H258" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4969,12 +7297,21 @@
         <v>207.7</v>
       </c>
       <c r="C259">
+        <v>10.38</v>
+      </c>
+      <c r="D259">
         <v>235.3</v>
       </c>
-      <c r="D259">
+      <c r="E259">
+        <v>11.77</v>
+      </c>
+      <c r="F259">
         <v>260.4</v>
       </c>
-      <c r="E259" t="inlineStr">
+      <c r="G259">
+        <v>13.02</v>
+      </c>
+      <c r="H259" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -4988,12 +7325,21 @@
         <v>207.7</v>
       </c>
       <c r="C260">
+        <v>10.38</v>
+      </c>
+      <c r="D260">
         <v>233.8</v>
       </c>
-      <c r="D260">
+      <c r="E260">
+        <v>11.69</v>
+      </c>
+      <c r="F260">
         <v>261.8</v>
       </c>
-      <c r="E260" t="inlineStr">
+      <c r="G260">
+        <v>13.09</v>
+      </c>
+      <c r="H260" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -5007,12 +7353,21 @@
         <v>215.9</v>
       </c>
       <c r="C261">
+        <v>10.8</v>
+      </c>
+      <c r="D261">
         <v>240.0</v>
       </c>
-      <c r="D261">
+      <c r="E261">
+        <v>12.0</v>
+      </c>
+      <c r="F261">
         <v>262.9</v>
       </c>
-      <c r="E261" t="inlineStr">
+      <c r="G261">
+        <v>13.14</v>
+      </c>
+      <c r="H261" t="inlineStr">
         <is>
           <t xml:space="preserve">FZ</t>
         </is>
@@ -5026,12 +7381,21 @@
         <v>222.8</v>
       </c>
       <c r="C262">
+        <v>11.14</v>
+      </c>
+      <c r="D262">
         <v>243.9</v>
       </c>
-      <c r="D262">
+      <c r="E262">
+        <v>12.2</v>
+      </c>
+      <c r="F262">
         <v>265.6</v>
       </c>
-      <c r="E262" t="inlineStr">
+      <c r="G262">
+        <v>13.28</v>
+      </c>
+      <c r="H262" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5045,12 +7409,21 @@
         <v>230.1</v>
       </c>
       <c r="C263">
+        <v>11.51</v>
+      </c>
+      <c r="D263">
         <v>249.9</v>
       </c>
-      <c r="D263">
+      <c r="E263">
+        <v>12.5</v>
+      </c>
+      <c r="F263">
         <v>266.2</v>
       </c>
-      <c r="E263" t="inlineStr">
+      <c r="G263">
+        <v>13.31</v>
+      </c>
+      <c r="H263" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5064,12 +7437,21 @@
         <v>237.7</v>
       </c>
       <c r="C264">
+        <v>11.88</v>
+      </c>
+      <c r="D264">
         <v>254.3</v>
       </c>
-      <c r="D264">
+      <c r="E264">
+        <v>12.72</v>
+      </c>
+      <c r="F264">
         <v>268.9</v>
       </c>
-      <c r="E264" t="inlineStr">
+      <c r="G264">
+        <v>13.45</v>
+      </c>
+      <c r="H264" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5083,12 +7465,21 @@
         <v>239.2</v>
       </c>
       <c r="C265">
+        <v>11.96</v>
+      </c>
+      <c r="D265">
         <v>255.6</v>
       </c>
-      <c r="D265">
+      <c r="E265">
+        <v>12.78</v>
+      </c>
+      <c r="F265">
         <v>269.5</v>
       </c>
-      <c r="E265" t="inlineStr">
+      <c r="G265">
+        <v>13.48</v>
+      </c>
+      <c r="H265" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5102,12 +7493,21 @@
         <v>240.6</v>
       </c>
       <c r="C266">
+        <v>12.03</v>
+      </c>
+      <c r="D266">
         <v>257.0</v>
       </c>
-      <c r="D266">
+      <c r="E266">
+        <v>12.85</v>
+      </c>
+      <c r="F266">
         <v>271.4</v>
       </c>
-      <c r="E266" t="inlineStr">
+      <c r="G266">
+        <v>13.57</v>
+      </c>
+      <c r="H266" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5121,12 +7521,21 @@
         <v>243.1</v>
       </c>
       <c r="C267">
+        <v>12.16</v>
+      </c>
+      <c r="D267">
         <v>261.2</v>
       </c>
-      <c r="D267">
+      <c r="E267">
+        <v>13.06</v>
+      </c>
+      <c r="F267">
         <v>271.0</v>
       </c>
-      <c r="E267" t="inlineStr">
+      <c r="G267">
+        <v>13.55</v>
+      </c>
+      <c r="H267" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5140,12 +7549,21 @@
         <v>241.1</v>
       </c>
       <c r="C268">
+        <v>12.05</v>
+      </c>
+      <c r="D268">
         <v>258.7</v>
       </c>
-      <c r="D268">
+      <c r="E268">
+        <v>12.94</v>
+      </c>
+      <c r="F268">
         <v>268.0</v>
       </c>
-      <c r="E268" t="inlineStr">
+      <c r="G268">
+        <v>13.4</v>
+      </c>
+      <c r="H268" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5159,12 +7577,21 @@
         <v>240.8</v>
       </c>
       <c r="C269">
+        <v>12.04</v>
+      </c>
+      <c r="D269">
         <v>256.5</v>
       </c>
-      <c r="D269">
+      <c r="E269">
+        <v>12.83</v>
+      </c>
+      <c r="F269">
         <v>266.5</v>
       </c>
-      <c r="E269" t="inlineStr">
+      <c r="G269">
+        <v>13.33</v>
+      </c>
+      <c r="H269" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5178,12 +7605,21 @@
         <v>239.3</v>
       </c>
       <c r="C270">
+        <v>11.97</v>
+      </c>
+      <c r="D270">
         <v>255.0</v>
       </c>
-      <c r="D270">
+      <c r="E270">
+        <v>12.75</v>
+      </c>
+      <c r="F270">
         <v>263.6</v>
       </c>
-      <c r="E270" t="inlineStr">
+      <c r="G270">
+        <v>13.18</v>
+      </c>
+      <c r="H270" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5197,12 +7633,21 @@
         <v>240.2</v>
       </c>
       <c r="C271">
+        <v>12.01</v>
+      </c>
+      <c r="D271">
         <v>252.4</v>
       </c>
-      <c r="D271">
+      <c r="E271">
+        <v>12.62</v>
+      </c>
+      <c r="F271">
         <v>262.9</v>
       </c>
-      <c r="E271" t="inlineStr">
+      <c r="G271">
+        <v>13.14</v>
+      </c>
+      <c r="H271" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5216,12 +7661,21 @@
         <v>238.9</v>
       </c>
       <c r="C272">
+        <v>11.95</v>
+      </c>
+      <c r="D272">
         <v>251.2</v>
       </c>
-      <c r="D272">
+      <c r="E272">
+        <v>12.56</v>
+      </c>
+      <c r="F272">
         <v>259.0</v>
       </c>
-      <c r="E272" t="inlineStr">
+      <c r="G272">
+        <v>12.95</v>
+      </c>
+      <c r="H272" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5235,12 +7689,21 @@
         <v>238.3</v>
       </c>
       <c r="C273">
+        <v>11.92</v>
+      </c>
+      <c r="D273">
         <v>249.7</v>
       </c>
-      <c r="D273">
+      <c r="E273">
+        <v>12.48</v>
+      </c>
+      <c r="F273">
         <v>258.0</v>
       </c>
-      <c r="E273" t="inlineStr">
+      <c r="G273">
+        <v>12.9</v>
+      </c>
+      <c r="H273" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5254,12 +7717,21 @@
         <v>239.5</v>
       </c>
       <c r="C274">
+        <v>11.98</v>
+      </c>
+      <c r="D274">
         <v>247.1</v>
       </c>
-      <c r="D274">
+      <c r="E274">
+        <v>12.36</v>
+      </c>
+      <c r="F274">
         <v>256.7</v>
       </c>
-      <c r="E274" t="inlineStr">
+      <c r="G274">
+        <v>12.84</v>
+      </c>
+      <c r="H274" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5273,12 +7745,21 @@
         <v>239.0</v>
       </c>
       <c r="C275">
+        <v>11.95</v>
+      </c>
+      <c r="D275">
         <v>245.1</v>
       </c>
-      <c r="D275">
+      <c r="E275">
+        <v>12.26</v>
+      </c>
+      <c r="F275">
         <v>254.9</v>
       </c>
-      <c r="E275" t="inlineStr">
+      <c r="G275">
+        <v>12.75</v>
+      </c>
+      <c r="H275" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5292,12 +7773,21 @@
         <v>237.8</v>
       </c>
       <c r="C276">
+        <v>11.89</v>
+      </c>
+      <c r="D276">
         <v>243.7</v>
       </c>
-      <c r="D276">
+      <c r="E276">
+        <v>12.19</v>
+      </c>
+      <c r="F276">
         <v>252.4</v>
       </c>
-      <c r="E276" t="inlineStr">
+      <c r="G276">
+        <v>12.62</v>
+      </c>
+      <c r="H276" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5311,12 +7801,21 @@
         <v>238.6</v>
       </c>
       <c r="C277">
+        <v>11.93</v>
+      </c>
+      <c r="D277">
         <v>242.0</v>
       </c>
-      <c r="D277">
+      <c r="E277">
+        <v>12.1</v>
+      </c>
+      <c r="F277">
         <v>250.3</v>
       </c>
-      <c r="E277" t="inlineStr">
+      <c r="G277">
+        <v>12.52</v>
+      </c>
+      <c r="H277" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5330,12 +7829,21 @@
         <v>236.7</v>
       </c>
       <c r="C278">
+        <v>11.84</v>
+      </c>
+      <c r="D278">
         <v>240.3</v>
       </c>
-      <c r="D278">
+      <c r="E278">
+        <v>12.02</v>
+      </c>
+      <c r="F278">
         <v>248.2</v>
       </c>
-      <c r="E278" t="inlineStr">
+      <c r="G278">
+        <v>12.41</v>
+      </c>
+      <c r="H278" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5349,12 +7857,21 @@
         <v>238.0</v>
       </c>
       <c r="C279">
+        <v>11.9</v>
+      </c>
+      <c r="D279">
         <v>240.1</v>
       </c>
-      <c r="D279">
+      <c r="E279">
+        <v>12.01</v>
+      </c>
+      <c r="F279">
         <v>246.7</v>
       </c>
-      <c r="E279" t="inlineStr">
+      <c r="G279">
+        <v>12.34</v>
+      </c>
+      <c r="H279" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5368,12 +7885,21 @@
         <v>235.9</v>
       </c>
       <c r="C280">
+        <v>11.8</v>
+      </c>
+      <c r="D280">
         <v>238.5</v>
       </c>
-      <c r="D280">
+      <c r="E280">
+        <v>11.93</v>
+      </c>
+      <c r="F280">
         <v>244.3</v>
       </c>
-      <c r="E280" t="inlineStr">
+      <c r="G280">
+        <v>12.22</v>
+      </c>
+      <c r="H280" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5387,12 +7913,21 @@
         <v>234.8</v>
       </c>
       <c r="C281">
+        <v>11.74</v>
+      </c>
+      <c r="D281">
         <v>237.5</v>
       </c>
-      <c r="D281">
+      <c r="E281">
+        <v>11.88</v>
+      </c>
+      <c r="F281">
         <v>243.2</v>
       </c>
-      <c r="E281" t="inlineStr">
+      <c r="G281">
+        <v>12.16</v>
+      </c>
+      <c r="H281" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5406,12 +7941,21 @@
         <v>232.9</v>
       </c>
       <c r="C282">
+        <v>11.65</v>
+      </c>
+      <c r="D282">
         <v>235.1</v>
       </c>
-      <c r="D282">
+      <c r="E282">
+        <v>11.76</v>
+      </c>
+      <c r="F282">
         <v>240.2</v>
       </c>
-      <c r="E282" t="inlineStr">
+      <c r="G282">
+        <v>12.01</v>
+      </c>
+      <c r="H282" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5425,12 +7969,21 @@
         <v>231.0</v>
       </c>
       <c r="C283">
+        <v>11.55</v>
+      </c>
+      <c r="D283">
         <v>232.7</v>
       </c>
-      <c r="D283">
+      <c r="E283">
+        <v>11.63</v>
+      </c>
+      <c r="F283">
         <v>239.4</v>
       </c>
-      <c r="E283" t="inlineStr">
+      <c r="G283">
+        <v>11.97</v>
+      </c>
+      <c r="H283" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5444,12 +7997,21 @@
         <v>228.0</v>
       </c>
       <c r="C284">
+        <v>11.4</v>
+      </c>
+      <c r="D284">
         <v>233.4</v>
       </c>
-      <c r="D284">
+      <c r="E284">
+        <v>11.67</v>
+      </c>
+      <c r="F284">
         <v>236.2</v>
       </c>
-      <c r="E284" t="inlineStr">
+      <c r="G284">
+        <v>11.81</v>
+      </c>
+      <c r="H284" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5463,12 +8025,21 @@
         <v>228.3</v>
       </c>
       <c r="C285">
+        <v>11.42</v>
+      </c>
+      <c r="D285">
         <v>231.7</v>
       </c>
-      <c r="D285">
+      <c r="E285">
+        <v>11.59</v>
+      </c>
+      <c r="F285">
         <v>237.1</v>
       </c>
-      <c r="E285" t="inlineStr">
+      <c r="G285">
+        <v>11.86</v>
+      </c>
+      <c r="H285" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5482,12 +8053,21 @@
         <v>225.8</v>
       </c>
       <c r="C286">
+        <v>11.29</v>
+      </c>
+      <c r="D286">
         <v>229.5</v>
       </c>
-      <c r="D286">
+      <c r="E286">
+        <v>11.48</v>
+      </c>
+      <c r="F286">
         <v>234.0</v>
       </c>
-      <c r="E286" t="inlineStr">
+      <c r="G286">
+        <v>11.7</v>
+      </c>
+      <c r="H286" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5501,12 +8081,21 @@
         <v>225.6</v>
       </c>
       <c r="C287">
+        <v>11.28</v>
+      </c>
+      <c r="D287">
         <v>230.3</v>
       </c>
-      <c r="D287">
+      <c r="E287">
+        <v>11.52</v>
+      </c>
+      <c r="F287">
         <v>232.6</v>
       </c>
-      <c r="E287" t="inlineStr">
+      <c r="G287">
+        <v>11.63</v>
+      </c>
+      <c r="H287" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5520,12 +8109,21 @@
         <v>224.6</v>
       </c>
       <c r="C288">
+        <v>11.23</v>
+      </c>
+      <c r="D288">
         <v>229.1</v>
       </c>
-      <c r="D288">
+      <c r="E288">
+        <v>11.46</v>
+      </c>
+      <c r="F288">
         <v>228.7</v>
       </c>
-      <c r="E288" t="inlineStr">
+      <c r="G288">
+        <v>11.44</v>
+      </c>
+      <c r="H288" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5539,12 +8137,21 @@
         <v>221.9</v>
       </c>
       <c r="C289">
+        <v>11.1</v>
+      </c>
+      <c r="D289">
         <v>226.6</v>
       </c>
-      <c r="D289">
+      <c r="E289">
+        <v>11.33</v>
+      </c>
+      <c r="F289">
         <v>227.6</v>
       </c>
-      <c r="E289" t="inlineStr">
+      <c r="G289">
+        <v>11.38</v>
+      </c>
+      <c r="H289" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5558,12 +8165,21 @@
         <v>223.0</v>
       </c>
       <c r="C290">
+        <v>11.15</v>
+      </c>
+      <c r="D290">
         <v>228.0</v>
       </c>
-      <c r="D290">
+      <c r="E290">
+        <v>11.4</v>
+      </c>
+      <c r="F290">
         <v>225.8</v>
       </c>
-      <c r="E290" t="inlineStr">
+      <c r="G290">
+        <v>11.29</v>
+      </c>
+      <c r="H290" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5577,12 +8193,21 @@
         <v>221.0</v>
       </c>
       <c r="C291">
+        <v>11.05</v>
+      </c>
+      <c r="D291">
         <v>225.6</v>
       </c>
-      <c r="D291">
+      <c r="E291">
+        <v>11.28</v>
+      </c>
+      <c r="F291">
         <v>225.2</v>
       </c>
-      <c r="E291" t="inlineStr">
+      <c r="G291">
+        <v>11.26</v>
+      </c>
+      <c r="H291" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5596,12 +8221,21 @@
         <v>220.8</v>
       </c>
       <c r="C292">
+        <v>11.04</v>
+      </c>
+      <c r="D292">
         <v>224.8</v>
       </c>
-      <c r="D292">
+      <c r="E292">
+        <v>11.24</v>
+      </c>
+      <c r="F292">
         <v>223.3</v>
       </c>
-      <c r="E292" t="inlineStr">
+      <c r="G292">
+        <v>11.17</v>
+      </c>
+      <c r="H292" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5615,12 +8249,21 @@
         <v>220.4</v>
       </c>
       <c r="C293">
+        <v>11.02</v>
+      </c>
+      <c r="D293">
         <v>223.4</v>
       </c>
-      <c r="D293">
+      <c r="E293">
+        <v>11.17</v>
+      </c>
+      <c r="F293">
         <v>221.7</v>
       </c>
-      <c r="E293" t="inlineStr">
+      <c r="G293">
+        <v>11.09</v>
+      </c>
+      <c r="H293" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5634,12 +8277,21 @@
         <v>219.2</v>
       </c>
       <c r="C294">
+        <v>10.96</v>
+      </c>
+      <c r="D294">
         <v>223.0</v>
       </c>
-      <c r="D294">
+      <c r="E294">
+        <v>11.15</v>
+      </c>
+      <c r="F294">
         <v>220.3</v>
       </c>
-      <c r="E294" t="inlineStr">
+      <c r="G294">
+        <v>11.02</v>
+      </c>
+      <c r="H294" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5653,12 +8305,21 @@
         <v>220.5</v>
       </c>
       <c r="C295">
+        <v>11.03</v>
+      </c>
+      <c r="D295">
         <v>221.8</v>
       </c>
-      <c r="D295">
+      <c r="E295">
+        <v>11.09</v>
+      </c>
+      <c r="F295">
         <v>219.8</v>
       </c>
-      <c r="E295" t="inlineStr">
+      <c r="G295">
+        <v>10.99</v>
+      </c>
+      <c r="H295" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5672,12 +8333,21 @@
         <v>218.7</v>
       </c>
       <c r="C296">
+        <v>10.94</v>
+      </c>
+      <c r="D296">
         <v>219.8</v>
       </c>
-      <c r="D296">
+      <c r="E296">
+        <v>10.99</v>
+      </c>
+      <c r="F296">
         <v>219.1</v>
       </c>
-      <c r="E296" t="inlineStr">
+      <c r="G296">
+        <v>10.96</v>
+      </c>
+      <c r="H296" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5691,12 +8361,21 @@
         <v>215.5</v>
       </c>
       <c r="C297">
+        <v>10.78</v>
+      </c>
+      <c r="D297">
         <v>218.4</v>
       </c>
-      <c r="D297">
+      <c r="E297">
+        <v>10.92</v>
+      </c>
+      <c r="F297">
         <v>219.6</v>
       </c>
-      <c r="E297" t="inlineStr">
+      <c r="G297">
+        <v>10.98</v>
+      </c>
+      <c r="H297" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5710,12 +8389,21 @@
         <v>215.7</v>
       </c>
       <c r="C298">
+        <v>10.79</v>
+      </c>
+      <c r="D298">
         <v>218.0</v>
       </c>
-      <c r="D298">
+      <c r="E298">
+        <v>10.9</v>
+      </c>
+      <c r="F298">
         <v>218.4</v>
       </c>
-      <c r="E298" t="inlineStr">
+      <c r="G298">
+        <v>10.92</v>
+      </c>
+      <c r="H298" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5729,12 +8417,21 @@
         <v>216.8</v>
       </c>
       <c r="C299">
+        <v>10.84</v>
+      </c>
+      <c r="D299">
         <v>216.9</v>
       </c>
-      <c r="D299">
+      <c r="E299">
+        <v>10.85</v>
+      </c>
+      <c r="F299">
         <v>219.1</v>
       </c>
-      <c r="E299" t="inlineStr">
+      <c r="G299">
+        <v>10.96</v>
+      </c>
+      <c r="H299" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5748,12 +8445,21 @@
         <v>215.0</v>
       </c>
       <c r="C300">
+        <v>10.75</v>
+      </c>
+      <c r="D300">
         <v>215.2</v>
       </c>
-      <c r="D300">
+      <c r="E300">
+        <v>10.76</v>
+      </c>
+      <c r="F300">
         <v>218.4</v>
       </c>
-      <c r="E300" t="inlineStr">
+      <c r="G300">
+        <v>10.92</v>
+      </c>
+      <c r="H300" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5767,12 +8473,21 @@
         <v>215.8</v>
       </c>
       <c r="C301">
+        <v>10.79</v>
+      </c>
+      <c r="D301">
         <v>213.2</v>
       </c>
-      <c r="D301">
+      <c r="E301">
+        <v>10.66</v>
+      </c>
+      <c r="F301">
         <v>217.7</v>
       </c>
-      <c r="E301" t="inlineStr">
+      <c r="G301">
+        <v>10.88</v>
+      </c>
+      <c r="H301" t="inlineStr">
         <is>
           <t xml:space="preserve">HAZ</t>
         </is>
@@ -5786,12 +8501,21 @@
         <v>214.1</v>
       </c>
       <c r="C302">
+        <v>10.71</v>
+      </c>
+      <c r="D302">
         <v>213.4</v>
       </c>
-      <c r="D302">
+      <c r="E302">
+        <v>10.67</v>
+      </c>
+      <c r="F302">
         <v>215.8</v>
       </c>
-      <c r="E302" t="inlineStr">
+      <c r="G302">
+        <v>10.79</v>
+      </c>
+      <c r="H302" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -5805,12 +8529,21 @@
         <v>214.4</v>
       </c>
       <c r="C303">
+        <v>10.72</v>
+      </c>
+      <c r="D303">
         <v>213.7</v>
       </c>
-      <c r="D303">
+      <c r="E303">
+        <v>10.69</v>
+      </c>
+      <c r="F303">
         <v>216.1</v>
       </c>
-      <c r="E303" t="inlineStr">
+      <c r="G303">
+        <v>10.8</v>
+      </c>
+      <c r="H303" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -5824,12 +8557,21 @@
         <v>214.9</v>
       </c>
       <c r="C304">
+        <v>10.75</v>
+      </c>
+      <c r="D304">
         <v>216.1</v>
       </c>
-      <c r="D304">
+      <c r="E304">
+        <v>10.8</v>
+      </c>
+      <c r="F304">
         <v>217.0</v>
       </c>
-      <c r="E304" t="inlineStr">
+      <c r="G304">
+        <v>10.85</v>
+      </c>
+      <c r="H304" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -5843,12 +8585,21 @@
         <v>216.1</v>
       </c>
       <c r="C305">
+        <v>10.8</v>
+      </c>
+      <c r="D305">
         <v>212.7</v>
       </c>
-      <c r="D305">
+      <c r="E305">
+        <v>10.63</v>
+      </c>
+      <c r="F305">
         <v>217.9</v>
       </c>
-      <c r="E305" t="inlineStr">
+      <c r="G305">
+        <v>10.9</v>
+      </c>
+      <c r="H305" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -5862,12 +8613,21 @@
         <v>214.4</v>
       </c>
       <c r="C306">
+        <v>10.72</v>
+      </c>
+      <c r="D306">
         <v>211.4</v>
       </c>
-      <c r="D306">
+      <c r="E306">
+        <v>10.57</v>
+      </c>
+      <c r="F306">
         <v>217.6</v>
       </c>
-      <c r="E306" t="inlineStr">
+      <c r="G306">
+        <v>10.88</v>
+      </c>
+      <c r="H306" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -5881,12 +8641,21 @@
         <v>216.7</v>
       </c>
       <c r="C307">
+        <v>10.84</v>
+      </c>
+      <c r="D307">
         <v>213.4</v>
       </c>
-      <c r="D307">
+      <c r="E307">
+        <v>10.67</v>
+      </c>
+      <c r="F307">
         <v>217.5</v>
       </c>
-      <c r="E307" t="inlineStr">
+      <c r="G307">
+        <v>10.88</v>
+      </c>
+      <c r="H307" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -5900,12 +8669,21 @@
         <v>217.0</v>
       </c>
       <c r="C308">
+        <v>10.85</v>
+      </c>
+      <c r="D308">
         <v>212.8</v>
       </c>
-      <c r="D308">
+      <c r="E308">
+        <v>10.64</v>
+      </c>
+      <c r="F308">
         <v>217.6</v>
       </c>
-      <c r="E308" t="inlineStr">
+      <c r="G308">
+        <v>10.88</v>
+      </c>
+      <c r="H308" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -5919,12 +8697,21 @@
         <v>215.6</v>
       </c>
       <c r="C309">
+        <v>10.78</v>
+      </c>
+      <c r="D309">
         <v>211.8</v>
       </c>
-      <c r="D309">
+      <c r="E309">
+        <v>10.59</v>
+      </c>
+      <c r="F309">
         <v>215.8</v>
       </c>
-      <c r="E309" t="inlineStr">
+      <c r="G309">
+        <v>10.79</v>
+      </c>
+      <c r="H309" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -5938,12 +8725,21 @@
         <v>216.3</v>
       </c>
       <c r="C310">
+        <v>10.82</v>
+      </c>
+      <c r="D310">
         <v>213.1</v>
       </c>
-      <c r="D310">
+      <c r="E310">
+        <v>10.66</v>
+      </c>
+      <c r="F310">
         <v>215.9</v>
       </c>
-      <c r="E310" t="inlineStr">
+      <c r="G310">
+        <v>10.8</v>
+      </c>
+      <c r="H310" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -5957,12 +8753,21 @@
         <v>215.4</v>
       </c>
       <c r="C311">
+        <v>10.77</v>
+      </c>
+      <c r="D311">
         <v>213.0</v>
       </c>
-      <c r="D311">
+      <c r="E311">
+        <v>10.65</v>
+      </c>
+      <c r="F311">
         <v>215.3</v>
       </c>
-      <c r="E311" t="inlineStr">
+      <c r="G311">
+        <v>10.77</v>
+      </c>
+      <c r="H311" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -5976,12 +8781,21 @@
         <v>214.4</v>
       </c>
       <c r="C312">
+        <v>10.72</v>
+      </c>
+      <c r="D312">
         <v>213.4</v>
       </c>
-      <c r="D312">
+      <c r="E312">
+        <v>10.67</v>
+      </c>
+      <c r="F312">
         <v>215.9</v>
       </c>
-      <c r="E312" t="inlineStr">
+      <c r="G312">
+        <v>10.8</v>
+      </c>
+      <c r="H312" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -5995,12 +8809,21 @@
         <v>215.1</v>
       </c>
       <c r="C313">
+        <v>10.76</v>
+      </c>
+      <c r="D313">
         <v>213.7</v>
       </c>
-      <c r="D313">
+      <c r="E313">
+        <v>10.69</v>
+      </c>
+      <c r="F313">
         <v>216.2</v>
       </c>
-      <c r="E313" t="inlineStr">
+      <c r="G313">
+        <v>10.81</v>
+      </c>
+      <c r="H313" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -6014,12 +8837,21 @@
         <v>217.8</v>
       </c>
       <c r="C314">
+        <v>10.89</v>
+      </c>
+      <c r="D314">
         <v>213.6</v>
       </c>
-      <c r="D314">
+      <c r="E314">
+        <v>10.68</v>
+      </c>
+      <c r="F314">
         <v>214.4</v>
       </c>
-      <c r="E314" t="inlineStr">
+      <c r="G314">
+        <v>10.72</v>
+      </c>
+      <c r="H314" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -6033,12 +8865,21 @@
         <v>216.3</v>
       </c>
       <c r="C315">
+        <v>10.82</v>
+      </c>
+      <c r="D315">
         <v>214.8</v>
       </c>
-      <c r="D315">
+      <c r="E315">
+        <v>10.74</v>
+      </c>
+      <c r="F315">
         <v>214.6</v>
       </c>
-      <c r="E315" t="inlineStr">
+      <c r="G315">
+        <v>10.73</v>
+      </c>
+      <c r="H315" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -6052,12 +8893,21 @@
         <v>215.6</v>
       </c>
       <c r="C316">
+        <v>10.78</v>
+      </c>
+      <c r="D316">
         <v>213.7</v>
       </c>
-      <c r="D316">
+      <c r="E316">
+        <v>10.69</v>
+      </c>
+      <c r="F316">
         <v>215.7</v>
       </c>
-      <c r="E316" t="inlineStr">
+      <c r="G316">
+        <v>10.79</v>
+      </c>
+      <c r="H316" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -6071,12 +8921,21 @@
         <v>216.2</v>
       </c>
       <c r="C317">
+        <v>10.81</v>
+      </c>
+      <c r="D317">
         <v>216.0</v>
       </c>
-      <c r="D317">
+      <c r="E317">
+        <v>10.8</v>
+      </c>
+      <c r="F317">
         <v>216.2</v>
       </c>
-      <c r="E317" t="inlineStr">
+      <c r="G317">
+        <v>10.81</v>
+      </c>
+      <c r="H317" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -6090,12 +8949,21 @@
         <v>217.2</v>
       </c>
       <c r="C318">
+        <v>10.86</v>
+      </c>
+      <c r="D318">
         <v>215.2</v>
       </c>
-      <c r="D318">
+      <c r="E318">
+        <v>10.76</v>
+      </c>
+      <c r="F318">
         <v>215.1</v>
       </c>
-      <c r="E318" t="inlineStr">
+      <c r="G318">
+        <v>10.76</v>
+      </c>
+      <c r="H318" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -6109,12 +8977,21 @@
         <v>215.9</v>
       </c>
       <c r="C319">
+        <v>10.8</v>
+      </c>
+      <c r="D319">
         <v>214.0</v>
       </c>
-      <c r="D319">
+      <c r="E319">
+        <v>10.7</v>
+      </c>
+      <c r="F319">
         <v>217.2</v>
       </c>
-      <c r="E319" t="inlineStr">
+      <c r="G319">
+        <v>10.86</v>
+      </c>
+      <c r="H319" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -6128,12 +9005,21 @@
         <v>217.0</v>
       </c>
       <c r="C320">
+        <v>10.85</v>
+      </c>
+      <c r="D320">
         <v>215.0</v>
       </c>
-      <c r="D320">
+      <c r="E320">
+        <v>10.75</v>
+      </c>
+      <c r="F320">
         <v>217.2</v>
       </c>
-      <c r="E320" t="inlineStr">
+      <c r="G320">
+        <v>10.86</v>
+      </c>
+      <c r="H320" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -6147,12 +9033,21 @@
         <v>216.6</v>
       </c>
       <c r="C321">
+        <v>10.83</v>
+      </c>
+      <c r="D321">
         <v>216.6</v>
       </c>
-      <c r="D321">
+      <c r="E321">
+        <v>10.83</v>
+      </c>
+      <c r="F321">
         <v>217.5</v>
       </c>
-      <c r="E321" t="inlineStr">
+      <c r="G321">
+        <v>10.88</v>
+      </c>
+      <c r="H321" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -6166,12 +9061,21 @@
         <v>217.5</v>
       </c>
       <c r="C322">
+        <v>10.88</v>
+      </c>
+      <c r="D322">
         <v>216.2</v>
       </c>
-      <c r="D322">
+      <c r="E322">
+        <v>10.81</v>
+      </c>
+      <c r="F322">
         <v>219.1</v>
       </c>
-      <c r="E322" t="inlineStr">
+      <c r="G322">
+        <v>10.96</v>
+      </c>
+      <c r="H322" t="inlineStr">
         <is>
           <t xml:space="preserve">BM</t>
         </is>
@@ -6230,63 +9134,54 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Error bars</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SD = 5% of each HV value (see *_SD columns on Hardness Data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zone statistics (HV0.1): mean / min / max</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Zone statistics (HV0.1): mean / min / max</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Electrode</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Region</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mean</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Min</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Max</t>
         </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">E6018</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Base metal</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>214.9</v>
-      </c>
-      <c r="D8">
-        <v>211.1</v>
-      </c>
-      <c r="E8">
-        <v>217.8</v>
       </c>
     </row>
     <row r="9">
@@ -6297,17 +9192,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAZ</t>
+          <t xml:space="preserve">Base metal</t>
         </is>
       </c>
       <c r="C9">
-        <v>230.7</v>
+        <v>214.9</v>
       </c>
       <c r="D9">
-        <v>215.0</v>
+        <v>211.1</v>
       </c>
       <c r="E9">
-        <v>250.5</v>
+        <v>217.8</v>
       </c>
     </row>
     <row r="10">
@@ -6318,17 +9213,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fusion zone</t>
+          <t xml:space="preserve">HAZ</t>
         </is>
       </c>
       <c r="C10">
-        <v>208.0</v>
+        <v>230.7</v>
       </c>
       <c r="D10">
-        <v>201.7</v>
+        <v>215.0</v>
       </c>
       <c r="E10">
-        <v>218.5</v>
+        <v>250.5</v>
       </c>
     </row>
     <row r="11">
@@ -6339,42 +9234,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CGHAZ peak</t>
+          <t xml:space="preserve">Fusion zone</t>
         </is>
       </c>
       <c r="C11">
-        <v>250.5</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+        <v>208.0</v>
+      </c>
+      <c r="D11">
+        <v>201.7</v>
+      </c>
+      <c r="E11">
+        <v>218.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7018</t>
+          <t xml:space="preserve">E6018</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Base metal</t>
+          <t xml:space="preserve">CGHAZ peak</t>
         </is>
       </c>
       <c r="C12">
-        <v>213.5</v>
-      </c>
-      <c r="D12">
-        <v>208.8</v>
-      </c>
-      <c r="E12">
-        <v>216.6</v>
+        <v>250.5</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -6385,17 +9280,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAZ</t>
+          <t xml:space="preserve">Base metal</t>
         </is>
       </c>
       <c r="C13">
-        <v>237.0</v>
+        <v>213.5</v>
       </c>
       <c r="D13">
-        <v>213.2</v>
+        <v>208.8</v>
       </c>
       <c r="E13">
-        <v>261.2</v>
+        <v>216.6</v>
       </c>
     </row>
     <row r="14">
@@ -6406,17 +9301,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fusion zone</t>
+          <t xml:space="preserve">HAZ</t>
         </is>
       </c>
       <c r="C14">
-        <v>231.3</v>
+        <v>237.0</v>
       </c>
       <c r="D14">
-        <v>224.0</v>
+        <v>213.2</v>
       </c>
       <c r="E14">
-        <v>240.4</v>
+        <v>261.2</v>
       </c>
     </row>
     <row r="15">
@@ -6427,42 +9322,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CGHAZ peak</t>
+          <t xml:space="preserve">Fusion zone</t>
         </is>
       </c>
       <c r="C15">
-        <v>261.2</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+        <v>231.3</v>
+      </c>
+      <c r="D15">
+        <v>224.0</v>
+      </c>
+      <c r="E15">
+        <v>240.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9018</t>
+          <t xml:space="preserve">E7018</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Base metal</t>
+          <t xml:space="preserve">CGHAZ peak</t>
         </is>
       </c>
       <c r="C16">
-        <v>215.7</v>
-      </c>
-      <c r="D16">
-        <v>213.3</v>
-      </c>
-      <c r="E16">
-        <v>219.1</v>
+        <v>261.2</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -6473,17 +9368,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAZ</t>
+          <t xml:space="preserve">Base metal</t>
         </is>
       </c>
       <c r="C17">
-        <v>245.5</v>
+        <v>215.7</v>
       </c>
       <c r="D17">
-        <v>215.2</v>
+        <v>213.3</v>
       </c>
       <c r="E17">
-        <v>276.6</v>
+        <v>219.1</v>
       </c>
     </row>
     <row r="18">
@@ -6494,17 +9389,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fusion zone</t>
+          <t xml:space="preserve">HAZ</t>
         </is>
       </c>
       <c r="C18">
-        <v>258.4</v>
+        <v>245.5</v>
       </c>
       <c r="D18">
-        <v>249.2</v>
+        <v>215.2</v>
       </c>
       <c r="E18">
-        <v>265.2</v>
+        <v>276.6</v>
       </c>
     </row>
     <row r="19">
@@ -6515,177 +9410,198 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">CGHAZ peak</t>
+          <t xml:space="preserve">Fusion zone</t>
         </is>
       </c>
       <c r="C19">
-        <v>276.6</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+        <v>258.4</v>
+      </c>
+      <c r="D19">
+        <v>249.2</v>
+      </c>
+      <c r="E19">
+        <v>265.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t xml:space="preserve">E9018</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CGHAZ peak</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>276.6</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Literature basis (ranges reported for API X70 welds)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X70 base metal</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">~210-225 HV</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">CGHAZ peak</t>
+          <t xml:space="preserve">X70 base metal</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">up to ~234-253 HV at high cooling rate (bainitic)</t>
+          <t xml:space="preserve">~210-225 HV</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weld metal order</t>
+          <t xml:space="preserve">CGHAZ peak</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">E90 &gt; E70 &gt; E60 (rises with electrode strength)</t>
+          <t xml:space="preserve">up to ~234-253 HV at high cooling rate (bainitic)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Weld metal order</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E90 &gt; E70 &gt; E60 (rises with electrode strength)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SAW X70 hardness/tensile</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doi.org/10.1007/s00170-023-11070-4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">X70 CGHAZ CCT &amp; hardness</t>
+          <t xml:space="preserve">SAW X70 hardness/tensile</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">doi.org/10.1007/s12046-021-01623-2</t>
+          <t xml:space="preserve">doi.org/10.1007/s00170-023-11070-4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">sDSS/X70 GTA HAZ sub-zones</t>
+          <t xml:space="preserve">X70 CGHAZ CCT &amp; hardness</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">doi.org/10.1007/s10853-023-08723-w</t>
+          <t xml:space="preserve">doi.org/10.1007/s12046-021-01623-2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">SMAW E7018 vs E6013 weld hardness</t>
+          <t xml:space="preserve">sDSS/X70 GTA HAZ sub-zones</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">sapub.org 10.5923/j.materials.20190901.03</t>
+          <t xml:space="preserve">doi.org/10.1007/s10853-023-08723-w</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">GMAW/FCAW X70 cap-pass hardness</t>
+          <t xml:space="preserve">SMAW E7018 vs E6013 weld hardness</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">doi.org/10.1007/s00170-024-13859-3</t>
+          <t xml:space="preserve">sapub.org 10.5923/j.materials.20190901.03</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t xml:space="preserve">GMAW/FCAW X70 cap-pass hardness</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doi.org/10.1007/s00170-024-13859-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Values are a literature-grounded synthetic reconstruction of a realistic</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">traverse (CGHAZ peak, overlapping BM/HAZ, FZ fan-out, multi-pass scatter),</t>
+          <t xml:space="preserve">Values are a literature-grounded synthetic reconstruction of a realistic</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">traverse (CGHAZ peak, overlapping BM/HAZ, FZ fan-out, multi-pass scatter),</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t xml:space="preserve">not raw measured indentations.</t>
         </is>

--- a/hardness_profile.xlsx
+++ b/hardness_profile.xlsx
@@ -101,19 +101,19 @@
         <v>212.3</v>
       </c>
       <c r="C2">
-        <v>10.62</v>
+        <v>4.25</v>
       </c>
       <c r="D2">
         <v>208.8</v>
       </c>
       <c r="E2">
-        <v>10.44</v>
+        <v>4.18</v>
       </c>
       <c r="F2">
         <v>214.1</v>
       </c>
       <c r="G2">
-        <v>10.71</v>
+        <v>4.28</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -129,19 +129,19 @@
         <v>213.8</v>
       </c>
       <c r="C3">
-        <v>10.69</v>
+        <v>4.28</v>
       </c>
       <c r="D3">
         <v>211.1</v>
       </c>
       <c r="E3">
-        <v>10.55</v>
+        <v>4.22</v>
       </c>
       <c r="F3">
         <v>214.4</v>
       </c>
       <c r="G3">
-        <v>10.72</v>
+        <v>4.29</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -157,19 +157,19 @@
         <v>211.1</v>
       </c>
       <c r="C4">
-        <v>10.55</v>
+        <v>4.22</v>
       </c>
       <c r="D4">
         <v>211.2</v>
       </c>
       <c r="E4">
-        <v>10.56</v>
+        <v>4.22</v>
       </c>
       <c r="F4">
         <v>214.4</v>
       </c>
       <c r="G4">
-        <v>10.72</v>
+        <v>4.29</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -185,19 +185,19 @@
         <v>211.8</v>
       </c>
       <c r="C5">
-        <v>10.59</v>
+        <v>4.24</v>
       </c>
       <c r="D5">
         <v>212.6</v>
       </c>
       <c r="E5">
-        <v>10.63</v>
+        <v>4.25</v>
       </c>
       <c r="F5">
         <v>214.7</v>
       </c>
       <c r="G5">
-        <v>10.73</v>
+        <v>4.29</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -213,19 +213,19 @@
         <v>213.5</v>
       </c>
       <c r="C6">
-        <v>10.68</v>
+        <v>4.27</v>
       </c>
       <c r="D6">
         <v>212.7</v>
       </c>
       <c r="E6">
-        <v>10.63</v>
+        <v>4.25</v>
       </c>
       <c r="F6">
         <v>215.3</v>
       </c>
       <c r="G6">
-        <v>10.77</v>
+        <v>4.31</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -241,19 +241,19 @@
         <v>214.3</v>
       </c>
       <c r="C7">
-        <v>10.72</v>
+        <v>4.29</v>
       </c>
       <c r="D7">
         <v>214.0</v>
       </c>
       <c r="E7">
-        <v>10.7</v>
+        <v>4.28</v>
       </c>
       <c r="F7">
         <v>215.9</v>
       </c>
       <c r="G7">
-        <v>10.8</v>
+        <v>4.32</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -269,19 +269,19 @@
         <v>213.3</v>
       </c>
       <c r="C8">
-        <v>10.67</v>
+        <v>4.27</v>
       </c>
       <c r="D8">
         <v>213.3</v>
       </c>
       <c r="E8">
-        <v>10.67</v>
+        <v>4.27</v>
       </c>
       <c r="F8">
         <v>214.9</v>
       </c>
       <c r="G8">
-        <v>10.75</v>
+        <v>4.3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -297,19 +297,19 @@
         <v>213.9</v>
       </c>
       <c r="C9">
-        <v>10.7</v>
+        <v>4.28</v>
       </c>
       <c r="D9">
         <v>214.2</v>
       </c>
       <c r="E9">
-        <v>10.71</v>
+        <v>4.28</v>
       </c>
       <c r="F9">
         <v>215.8</v>
       </c>
       <c r="G9">
-        <v>10.79</v>
+        <v>4.32</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -325,19 +325,19 @@
         <v>214.4</v>
       </c>
       <c r="C10">
-        <v>10.72</v>
+        <v>4.29</v>
       </c>
       <c r="D10">
         <v>214.6</v>
       </c>
       <c r="E10">
-        <v>10.73</v>
+        <v>4.29</v>
       </c>
       <c r="F10">
         <v>216.3</v>
       </c>
       <c r="G10">
-        <v>10.82</v>
+        <v>4.33</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -353,19 +353,19 @@
         <v>213.4</v>
       </c>
       <c r="C11">
-        <v>10.67</v>
+        <v>4.27</v>
       </c>
       <c r="D11">
         <v>214.6</v>
       </c>
       <c r="E11">
-        <v>10.73</v>
+        <v>4.29</v>
       </c>
       <c r="F11">
         <v>214.7</v>
       </c>
       <c r="G11">
-        <v>10.73</v>
+        <v>4.29</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -381,19 +381,19 @@
         <v>215.0</v>
       </c>
       <c r="C12">
-        <v>10.75</v>
+        <v>4.3</v>
       </c>
       <c r="D12">
         <v>213.2</v>
       </c>
       <c r="E12">
-        <v>10.66</v>
+        <v>4.26</v>
       </c>
       <c r="F12">
         <v>214.3</v>
       </c>
       <c r="G12">
-        <v>10.72</v>
+        <v>4.29</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -409,19 +409,19 @@
         <v>216.4</v>
       </c>
       <c r="C13">
-        <v>10.82</v>
+        <v>4.33</v>
       </c>
       <c r="D13">
         <v>213.8</v>
       </c>
       <c r="E13">
-        <v>10.69</v>
+        <v>4.28</v>
       </c>
       <c r="F13">
         <v>215.9</v>
       </c>
       <c r="G13">
-        <v>10.8</v>
+        <v>4.32</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -437,19 +437,19 @@
         <v>214.0</v>
       </c>
       <c r="C14">
-        <v>10.7</v>
+        <v>4.28</v>
       </c>
       <c r="D14">
         <v>213.2</v>
       </c>
       <c r="E14">
-        <v>10.66</v>
+        <v>4.26</v>
       </c>
       <c r="F14">
         <v>214.5</v>
       </c>
       <c r="G14">
-        <v>10.73</v>
+        <v>4.29</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -465,19 +465,19 @@
         <v>214.0</v>
       </c>
       <c r="C15">
-        <v>10.7</v>
+        <v>4.28</v>
       </c>
       <c r="D15">
         <v>212.4</v>
       </c>
       <c r="E15">
-        <v>10.62</v>
+        <v>4.25</v>
       </c>
       <c r="F15">
         <v>213.9</v>
       </c>
       <c r="G15">
-        <v>10.7</v>
+        <v>4.28</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -493,19 +493,19 @@
         <v>213.5</v>
       </c>
       <c r="C16">
-        <v>10.68</v>
+        <v>4.27</v>
       </c>
       <c r="D16">
         <v>213.1</v>
       </c>
       <c r="E16">
-        <v>10.66</v>
+        <v>4.26</v>
       </c>
       <c r="F16">
         <v>213.3</v>
       </c>
       <c r="G16">
-        <v>10.67</v>
+        <v>4.27</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -521,19 +521,19 @@
         <v>215.1</v>
       </c>
       <c r="C17">
-        <v>10.76</v>
+        <v>4.3</v>
       </c>
       <c r="D17">
         <v>213.2</v>
       </c>
       <c r="E17">
-        <v>10.66</v>
+        <v>4.26</v>
       </c>
       <c r="F17">
         <v>215.5</v>
       </c>
       <c r="G17">
-        <v>10.78</v>
+        <v>4.31</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         <v>212.8</v>
       </c>
       <c r="C18">
-        <v>10.64</v>
+        <v>4.26</v>
       </c>
       <c r="D18">
         <v>213.1</v>
       </c>
       <c r="E18">
-        <v>10.66</v>
+        <v>4.26</v>
       </c>
       <c r="F18">
         <v>215.6</v>
       </c>
       <c r="G18">
-        <v>10.78</v>
+        <v>4.31</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -577,19 +577,19 @@
         <v>216.6</v>
       </c>
       <c r="C19">
-        <v>10.83</v>
+        <v>4.33</v>
       </c>
       <c r="D19">
         <v>212.8</v>
       </c>
       <c r="E19">
-        <v>10.64</v>
+        <v>4.26</v>
       </c>
       <c r="F19">
         <v>215.2</v>
       </c>
       <c r="G19">
-        <v>10.76</v>
+        <v>4.3</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -605,19 +605,19 @@
         <v>213.4</v>
       </c>
       <c r="C20">
-        <v>10.67</v>
+        <v>4.27</v>
       </c>
       <c r="D20">
         <v>213.4</v>
       </c>
       <c r="E20">
-        <v>10.67</v>
+        <v>4.27</v>
       </c>
       <c r="F20">
         <v>216.2</v>
       </c>
       <c r="G20">
-        <v>10.81</v>
+        <v>4.32</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -633,19 +633,19 @@
         <v>215.0</v>
       </c>
       <c r="C21">
-        <v>10.75</v>
+        <v>4.3</v>
       </c>
       <c r="D21">
         <v>213.6</v>
       </c>
       <c r="E21">
-        <v>10.68</v>
+        <v>4.27</v>
       </c>
       <c r="F21">
         <v>214.7</v>
       </c>
       <c r="G21">
-        <v>10.73</v>
+        <v>4.29</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -661,19 +661,19 @@
         <v>214.8</v>
       </c>
       <c r="C22">
-        <v>10.74</v>
+        <v>4.3</v>
       </c>
       <c r="D22">
         <v>215.7</v>
       </c>
       <c r="E22">
-        <v>10.79</v>
+        <v>4.31</v>
       </c>
       <c r="F22">
         <v>215.7</v>
       </c>
       <c r="G22">
-        <v>10.79</v>
+        <v>4.31</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -689,19 +689,19 @@
         <v>215.6</v>
       </c>
       <c r="C23">
-        <v>10.78</v>
+        <v>4.31</v>
       </c>
       <c r="D23">
         <v>215.7</v>
       </c>
       <c r="E23">
-        <v>10.79</v>
+        <v>4.31</v>
       </c>
       <c r="F23">
         <v>215.2</v>
       </c>
       <c r="G23">
-        <v>10.76</v>
+        <v>4.3</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -717,19 +717,19 @@
         <v>216.6</v>
       </c>
       <c r="C24">
-        <v>10.83</v>
+        <v>4.33</v>
       </c>
       <c r="D24">
         <v>215.6</v>
       </c>
       <c r="E24">
-        <v>10.78</v>
+        <v>4.31</v>
       </c>
       <c r="F24">
         <v>216.2</v>
       </c>
       <c r="G24">
-        <v>10.81</v>
+        <v>4.32</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -745,19 +745,19 @@
         <v>217.2</v>
       </c>
       <c r="C25">
-        <v>10.86</v>
+        <v>4.34</v>
       </c>
       <c r="D25">
         <v>217.1</v>
       </c>
       <c r="E25">
-        <v>10.86</v>
+        <v>4.34</v>
       </c>
       <c r="F25">
         <v>218.3</v>
       </c>
       <c r="G25">
-        <v>10.92</v>
+        <v>4.37</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -773,19 +773,19 @@
         <v>217.4</v>
       </c>
       <c r="C26">
-        <v>10.87</v>
+        <v>4.35</v>
       </c>
       <c r="D26">
         <v>217.3</v>
       </c>
       <c r="E26">
-        <v>10.87</v>
+        <v>4.35</v>
       </c>
       <c r="F26">
         <v>219.4</v>
       </c>
       <c r="G26">
-        <v>10.97</v>
+        <v>4.39</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         <v>217.9</v>
       </c>
       <c r="C27">
-        <v>10.9</v>
+        <v>4.36</v>
       </c>
       <c r="D27">
         <v>219.4</v>
       </c>
       <c r="E27">
-        <v>10.97</v>
+        <v>4.39</v>
       </c>
       <c r="F27">
         <v>222.0</v>
       </c>
       <c r="G27">
-        <v>11.1</v>
+        <v>4.44</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -829,19 +829,19 @@
         <v>218.2</v>
       </c>
       <c r="C28">
-        <v>10.91</v>
+        <v>4.36</v>
       </c>
       <c r="D28">
         <v>219.9</v>
       </c>
       <c r="E28">
-        <v>11.0</v>
+        <v>4.4</v>
       </c>
       <c r="F28">
         <v>222.4</v>
       </c>
       <c r="G28">
-        <v>11.12</v>
+        <v>4.45</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -857,19 +857,19 @@
         <v>221.0</v>
       </c>
       <c r="C29">
-        <v>11.05</v>
+        <v>4.42</v>
       </c>
       <c r="D29">
         <v>222.5</v>
       </c>
       <c r="E29">
-        <v>11.12</v>
+        <v>4.45</v>
       </c>
       <c r="F29">
         <v>222.6</v>
       </c>
       <c r="G29">
-        <v>11.13</v>
+        <v>4.45</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -885,19 +885,19 @@
         <v>220.1</v>
       </c>
       <c r="C30">
-        <v>11.01</v>
+        <v>4.4</v>
       </c>
       <c r="D30">
         <v>223.5</v>
       </c>
       <c r="E30">
-        <v>11.18</v>
+        <v>4.47</v>
       </c>
       <c r="F30">
         <v>227.0</v>
       </c>
       <c r="G30">
-        <v>11.35</v>
+        <v>4.54</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -913,19 +913,19 @@
         <v>220.0</v>
       </c>
       <c r="C31">
-        <v>11.0</v>
+        <v>4.4</v>
       </c>
       <c r="D31">
         <v>223.3</v>
       </c>
       <c r="E31">
-        <v>11.17</v>
+        <v>4.47</v>
       </c>
       <c r="F31">
         <v>229.2</v>
       </c>
       <c r="G31">
-        <v>11.46</v>
+        <v>4.58</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -941,19 +941,19 @@
         <v>218.6</v>
       </c>
       <c r="C32">
-        <v>10.93</v>
+        <v>4.37</v>
       </c>
       <c r="D32">
         <v>226.2</v>
       </c>
       <c r="E32">
-        <v>11.31</v>
+        <v>4.52</v>
       </c>
       <c r="F32">
         <v>231.8</v>
       </c>
       <c r="G32">
-        <v>11.59</v>
+        <v>4.64</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -969,19 +969,19 @@
         <v>220.7</v>
       </c>
       <c r="C33">
-        <v>11.04</v>
+        <v>4.41</v>
       </c>
       <c r="D33">
         <v>224.8</v>
       </c>
       <c r="E33">
-        <v>11.24</v>
+        <v>4.5</v>
       </c>
       <c r="F33">
         <v>233.1</v>
       </c>
       <c r="G33">
-        <v>11.66</v>
+        <v>4.66</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -997,19 +997,19 @@
         <v>219.8</v>
       </c>
       <c r="C34">
-        <v>10.99</v>
+        <v>4.4</v>
       </c>
       <c r="D34">
         <v>226.3</v>
       </c>
       <c r="E34">
-        <v>11.32</v>
+        <v>4.53</v>
       </c>
       <c r="F34">
         <v>235.6</v>
       </c>
       <c r="G34">
-        <v>11.78</v>
+        <v>4.71</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1025,19 +1025,19 @@
         <v>221.5</v>
       </c>
       <c r="C35">
-        <v>11.08</v>
+        <v>4.43</v>
       </c>
       <c r="D35">
         <v>229.1</v>
       </c>
       <c r="E35">
-        <v>11.46</v>
+        <v>4.58</v>
       </c>
       <c r="F35">
         <v>238.3</v>
       </c>
       <c r="G35">
-        <v>11.92</v>
+        <v>4.77</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1053,19 +1053,19 @@
         <v>221.6</v>
       </c>
       <c r="C36">
-        <v>11.08</v>
+        <v>4.43</v>
       </c>
       <c r="D36">
         <v>231.5</v>
       </c>
       <c r="E36">
-        <v>11.58</v>
+        <v>4.63</v>
       </c>
       <c r="F36">
         <v>237.8</v>
       </c>
       <c r="G36">
-        <v>11.89</v>
+        <v>4.76</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1081,19 +1081,19 @@
         <v>223.3</v>
       </c>
       <c r="C37">
-        <v>11.17</v>
+        <v>4.47</v>
       </c>
       <c r="D37">
         <v>232.1</v>
       </c>
       <c r="E37">
-        <v>11.61</v>
+        <v>4.64</v>
       </c>
       <c r="F37">
         <v>239.9</v>
       </c>
       <c r="G37">
-        <v>12.0</v>
+        <v>4.8</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1109,19 +1109,19 @@
         <v>224.5</v>
       </c>
       <c r="C38">
-        <v>11.23</v>
+        <v>4.49</v>
       </c>
       <c r="D38">
         <v>232.3</v>
       </c>
       <c r="E38">
-        <v>11.62</v>
+        <v>4.65</v>
       </c>
       <c r="F38">
         <v>242.1</v>
       </c>
       <c r="G38">
-        <v>12.11</v>
+        <v>4.84</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         <v>226.9</v>
       </c>
       <c r="C39">
-        <v>11.35</v>
+        <v>4.54</v>
       </c>
       <c r="D39">
         <v>233.7</v>
       </c>
       <c r="E39">
-        <v>11.69</v>
+        <v>4.67</v>
       </c>
       <c r="F39">
         <v>243.8</v>
       </c>
       <c r="G39">
-        <v>12.19</v>
+        <v>4.88</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1165,19 +1165,19 @@
         <v>228.4</v>
       </c>
       <c r="C40">
-        <v>11.42</v>
+        <v>4.57</v>
       </c>
       <c r="D40">
         <v>236.9</v>
       </c>
       <c r="E40">
-        <v>11.85</v>
+        <v>4.74</v>
       </c>
       <c r="F40">
         <v>246.3</v>
       </c>
       <c r="G40">
-        <v>12.32</v>
+        <v>4.93</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1193,19 +1193,19 @@
         <v>230.7</v>
       </c>
       <c r="C41">
-        <v>11.54</v>
+        <v>4.61</v>
       </c>
       <c r="D41">
         <v>237.9</v>
       </c>
       <c r="E41">
-        <v>11.9</v>
+        <v>4.76</v>
       </c>
       <c r="F41">
         <v>248.5</v>
       </c>
       <c r="G41">
-        <v>12.43</v>
+        <v>4.97</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1221,19 +1221,19 @@
         <v>231.2</v>
       </c>
       <c r="C42">
-        <v>11.56</v>
+        <v>4.62</v>
       </c>
       <c r="D42">
         <v>240.7</v>
       </c>
       <c r="E42">
-        <v>12.04</v>
+        <v>4.81</v>
       </c>
       <c r="F42">
         <v>248.6</v>
       </c>
       <c r="G42">
-        <v>12.43</v>
+        <v>4.97</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1249,19 +1249,19 @@
         <v>231.9</v>
       </c>
       <c r="C43">
-        <v>11.6</v>
+        <v>4.64</v>
       </c>
       <c r="D43">
         <v>239.0</v>
       </c>
       <c r="E43">
-        <v>11.95</v>
+        <v>4.78</v>
       </c>
       <c r="F43">
         <v>251.8</v>
       </c>
       <c r="G43">
-        <v>12.59</v>
+        <v>5.04</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1277,19 +1277,19 @@
         <v>234.6</v>
       </c>
       <c r="C44">
-        <v>11.73</v>
+        <v>4.69</v>
       </c>
       <c r="D44">
         <v>239.7</v>
       </c>
       <c r="E44">
-        <v>11.98</v>
+        <v>4.79</v>
       </c>
       <c r="F44">
         <v>251.0</v>
       </c>
       <c r="G44">
-        <v>12.55</v>
+        <v>5.02</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1305,19 +1305,19 @@
         <v>236.5</v>
       </c>
       <c r="C45">
-        <v>11.83</v>
+        <v>4.73</v>
       </c>
       <c r="D45">
         <v>242.7</v>
       </c>
       <c r="E45">
-        <v>12.13</v>
+        <v>4.85</v>
       </c>
       <c r="F45">
         <v>256.3</v>
       </c>
       <c r="G45">
-        <v>12.82</v>
+        <v>5.13</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1333,19 +1333,19 @@
         <v>236.9</v>
       </c>
       <c r="C46">
-        <v>11.85</v>
+        <v>4.74</v>
       </c>
       <c r="D46">
         <v>243.5</v>
       </c>
       <c r="E46">
-        <v>12.18</v>
+        <v>4.87</v>
       </c>
       <c r="F46">
         <v>255.0</v>
       </c>
       <c r="G46">
-        <v>12.75</v>
+        <v>5.1</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -1361,19 +1361,19 @@
         <v>237.8</v>
       </c>
       <c r="C47">
-        <v>11.89</v>
+        <v>4.76</v>
       </c>
       <c r="D47">
         <v>243.9</v>
       </c>
       <c r="E47">
-        <v>12.2</v>
+        <v>4.88</v>
       </c>
       <c r="F47">
         <v>257.1</v>
       </c>
       <c r="G47">
-        <v>12.86</v>
+        <v>5.14</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -1389,19 +1389,19 @@
         <v>240.6</v>
       </c>
       <c r="C48">
-        <v>12.03</v>
+        <v>4.81</v>
       </c>
       <c r="D48">
         <v>242.9</v>
       </c>
       <c r="E48">
-        <v>12.15</v>
+        <v>4.86</v>
       </c>
       <c r="F48">
         <v>258.1</v>
       </c>
       <c r="G48">
-        <v>12.91</v>
+        <v>5.16</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -1417,19 +1417,19 @@
         <v>240.0</v>
       </c>
       <c r="C49">
-        <v>12.0</v>
+        <v>4.8</v>
       </c>
       <c r="D49">
         <v>245.3</v>
       </c>
       <c r="E49">
-        <v>12.27</v>
+        <v>4.91</v>
       </c>
       <c r="F49">
         <v>261.0</v>
       </c>
       <c r="G49">
-        <v>13.05</v>
+        <v>5.22</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -1445,19 +1445,19 @@
         <v>243.1</v>
       </c>
       <c r="C50">
-        <v>12.16</v>
+        <v>4.86</v>
       </c>
       <c r="D50">
         <v>247.7</v>
       </c>
       <c r="E50">
-        <v>12.38</v>
+        <v>4.95</v>
       </c>
       <c r="F50">
         <v>262.7</v>
       </c>
       <c r="G50">
-        <v>13.13</v>
+        <v>5.25</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -1473,19 +1473,19 @@
         <v>243.3</v>
       </c>
       <c r="C51">
-        <v>12.17</v>
+        <v>4.87</v>
       </c>
       <c r="D51">
         <v>248.9</v>
       </c>
       <c r="E51">
-        <v>12.45</v>
+        <v>4.98</v>
       </c>
       <c r="F51">
         <v>263.0</v>
       </c>
       <c r="G51">
-        <v>13.15</v>
+        <v>5.26</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -1501,19 +1501,19 @@
         <v>244.6</v>
       </c>
       <c r="C52">
-        <v>12.23</v>
+        <v>4.89</v>
       </c>
       <c r="D52">
         <v>249.8</v>
       </c>
       <c r="E52">
-        <v>12.49</v>
+        <v>5.0</v>
       </c>
       <c r="F52">
         <v>265.3</v>
       </c>
       <c r="G52">
-        <v>13.27</v>
+        <v>5.31</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -1529,19 +1529,19 @@
         <v>247.4</v>
       </c>
       <c r="C53">
-        <v>12.37</v>
+        <v>4.95</v>
       </c>
       <c r="D53">
         <v>251.0</v>
       </c>
       <c r="E53">
-        <v>12.55</v>
+        <v>5.02</v>
       </c>
       <c r="F53">
         <v>265.8</v>
       </c>
       <c r="G53">
-        <v>13.29</v>
+        <v>5.32</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -1557,19 +1557,19 @@
         <v>248.1</v>
       </c>
       <c r="C54">
-        <v>12.41</v>
+        <v>4.96</v>
       </c>
       <c r="D54">
         <v>251.7</v>
       </c>
       <c r="E54">
-        <v>12.59</v>
+        <v>5.03</v>
       </c>
       <c r="F54">
         <v>269.3</v>
       </c>
       <c r="G54">
-        <v>13.47</v>
+        <v>5.39</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -1585,19 +1585,19 @@
         <v>249.1</v>
       </c>
       <c r="C55">
-        <v>12.46</v>
+        <v>4.98</v>
       </c>
       <c r="D55">
         <v>253.7</v>
       </c>
       <c r="E55">
-        <v>12.69</v>
+        <v>5.07</v>
       </c>
       <c r="F55">
         <v>271.6</v>
       </c>
       <c r="G55">
-        <v>13.58</v>
+        <v>5.43</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -1613,19 +1613,19 @@
         <v>249.8</v>
       </c>
       <c r="C56">
-        <v>12.49</v>
+        <v>5.0</v>
       </c>
       <c r="D56">
         <v>255.6</v>
       </c>
       <c r="E56">
-        <v>12.78</v>
+        <v>5.11</v>
       </c>
       <c r="F56">
         <v>272.9</v>
       </c>
       <c r="G56">
-        <v>13.64</v>
+        <v>5.46</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -1641,19 +1641,19 @@
         <v>250.5</v>
       </c>
       <c r="C57">
-        <v>12.53</v>
+        <v>5.01</v>
       </c>
       <c r="D57">
         <v>256.7</v>
       </c>
       <c r="E57">
-        <v>12.84</v>
+        <v>5.13</v>
       </c>
       <c r="F57">
         <v>276.6</v>
       </c>
       <c r="G57">
-        <v>13.83</v>
+        <v>5.53</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -1669,19 +1669,19 @@
         <v>248.6</v>
       </c>
       <c r="C58">
-        <v>12.43</v>
+        <v>4.97</v>
       </c>
       <c r="D58">
         <v>255.7</v>
       </c>
       <c r="E58">
-        <v>12.79</v>
+        <v>5.11</v>
       </c>
       <c r="F58">
         <v>274.7</v>
       </c>
       <c r="G58">
-        <v>13.73</v>
+        <v>5.49</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -1697,19 +1697,19 @@
         <v>245.4</v>
       </c>
       <c r="C59">
-        <v>12.27</v>
+        <v>4.91</v>
       </c>
       <c r="D59">
         <v>253.5</v>
       </c>
       <c r="E59">
-        <v>12.68</v>
+        <v>5.07</v>
       </c>
       <c r="F59">
         <v>272.8</v>
       </c>
       <c r="G59">
-        <v>13.64</v>
+        <v>5.46</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -1725,19 +1725,19 @@
         <v>243.1</v>
       </c>
       <c r="C60">
-        <v>12.16</v>
+        <v>4.86</v>
       </c>
       <c r="D60">
         <v>251.8</v>
       </c>
       <c r="E60">
-        <v>12.59</v>
+        <v>5.04</v>
       </c>
       <c r="F60">
         <v>272.4</v>
       </c>
       <c r="G60">
-        <v>13.62</v>
+        <v>5.45</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -1753,19 +1753,19 @@
         <v>235.4</v>
       </c>
       <c r="C61">
-        <v>11.77</v>
+        <v>4.71</v>
       </c>
       <c r="D61">
         <v>246.8</v>
       </c>
       <c r="E61">
-        <v>12.34</v>
+        <v>4.94</v>
       </c>
       <c r="F61">
         <v>270.2</v>
       </c>
       <c r="G61">
-        <v>13.51</v>
+        <v>5.4</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -1781,19 +1781,19 @@
         <v>227.0</v>
       </c>
       <c r="C62">
-        <v>11.35</v>
+        <v>4.54</v>
       </c>
       <c r="D62">
         <v>241.7</v>
       </c>
       <c r="E62">
-        <v>12.09</v>
+        <v>4.83</v>
       </c>
       <c r="F62">
         <v>266.6</v>
       </c>
       <c r="G62">
-        <v>13.33</v>
+        <v>5.33</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -1809,19 +1809,19 @@
         <v>218.5</v>
       </c>
       <c r="C63">
-        <v>10.93</v>
+        <v>4.37</v>
       </c>
       <c r="D63">
         <v>238.4</v>
       </c>
       <c r="E63">
-        <v>11.92</v>
+        <v>4.77</v>
       </c>
       <c r="F63">
         <v>265.2</v>
       </c>
       <c r="G63">
-        <v>13.26</v>
+        <v>5.3</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -1837,19 +1837,19 @@
         <v>210.2</v>
       </c>
       <c r="C64">
-        <v>10.51</v>
+        <v>4.2</v>
       </c>
       <c r="D64">
         <v>232.2</v>
       </c>
       <c r="E64">
-        <v>11.61</v>
+        <v>4.64</v>
       </c>
       <c r="F64">
         <v>262.5</v>
       </c>
       <c r="G64">
-        <v>13.12</v>
+        <v>5.25</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -1865,19 +1865,19 @@
         <v>207.8</v>
       </c>
       <c r="C65">
-        <v>10.39</v>
+        <v>4.16</v>
       </c>
       <c r="D65">
         <v>232.5</v>
       </c>
       <c r="E65">
-        <v>11.62</v>
+        <v>4.65</v>
       </c>
       <c r="F65">
         <v>264.3</v>
       </c>
       <c r="G65">
-        <v>13.22</v>
+        <v>5.29</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -1893,19 +1893,19 @@
         <v>207.0</v>
       </c>
       <c r="C66">
-        <v>10.35</v>
+        <v>4.14</v>
       </c>
       <c r="D66">
         <v>231.0</v>
       </c>
       <c r="E66">
-        <v>11.55</v>
+        <v>4.62</v>
       </c>
       <c r="F66">
         <v>264.5</v>
       </c>
       <c r="G66">
-        <v>13.23</v>
+        <v>5.29</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -1921,19 +1921,19 @@
         <v>206.5</v>
       </c>
       <c r="C67">
-        <v>10.33</v>
+        <v>4.13</v>
       </c>
       <c r="D67">
         <v>230.1</v>
       </c>
       <c r="E67">
-        <v>11.51</v>
+        <v>4.6</v>
       </c>
       <c r="F67">
         <v>262.7</v>
       </c>
       <c r="G67">
-        <v>13.13</v>
+        <v>5.25</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -1949,19 +1949,19 @@
         <v>206.4</v>
       </c>
       <c r="C68">
-        <v>10.32</v>
+        <v>4.13</v>
       </c>
       <c r="D68">
         <v>230.0</v>
       </c>
       <c r="E68">
-        <v>11.5</v>
+        <v>4.6</v>
       </c>
       <c r="F68">
         <v>263.3</v>
       </c>
       <c r="G68">
-        <v>13.17</v>
+        <v>5.27</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -1977,19 +1977,19 @@
         <v>205.1</v>
       </c>
       <c r="C69">
-        <v>10.26</v>
+        <v>4.1</v>
       </c>
       <c r="D69">
         <v>229.1</v>
       </c>
       <c r="E69">
-        <v>11.46</v>
+        <v>4.58</v>
       </c>
       <c r="F69">
         <v>264.2</v>
       </c>
       <c r="G69">
-        <v>13.21</v>
+        <v>5.28</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2005,19 +2005,19 @@
         <v>205.6</v>
       </c>
       <c r="C70">
-        <v>10.28</v>
+        <v>4.11</v>
       </c>
       <c r="D70">
         <v>228.4</v>
       </c>
       <c r="E70">
-        <v>11.42</v>
+        <v>4.57</v>
       </c>
       <c r="F70">
         <v>262.2</v>
       </c>
       <c r="G70">
-        <v>13.11</v>
+        <v>5.24</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -2033,19 +2033,19 @@
         <v>204.9</v>
       </c>
       <c r="C71">
-        <v>10.25</v>
+        <v>4.1</v>
       </c>
       <c r="D71">
         <v>227.6</v>
       </c>
       <c r="E71">
-        <v>11.38</v>
+        <v>4.55</v>
       </c>
       <c r="F71">
         <v>262.8</v>
       </c>
       <c r="G71">
-        <v>13.14</v>
+        <v>5.26</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -2061,19 +2061,19 @@
         <v>206.0</v>
       </c>
       <c r="C72">
-        <v>10.3</v>
+        <v>4.12</v>
       </c>
       <c r="D72">
         <v>225.9</v>
       </c>
       <c r="E72">
-        <v>11.3</v>
+        <v>4.52</v>
       </c>
       <c r="F72">
         <v>260.5</v>
       </c>
       <c r="G72">
-        <v>13.03</v>
+        <v>5.21</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -2089,19 +2089,19 @@
         <v>205.1</v>
       </c>
       <c r="C73">
-        <v>10.26</v>
+        <v>4.1</v>
       </c>
       <c r="D73">
         <v>226.2</v>
       </c>
       <c r="E73">
-        <v>11.31</v>
+        <v>4.52</v>
       </c>
       <c r="F73">
         <v>261.4</v>
       </c>
       <c r="G73">
-        <v>13.07</v>
+        <v>5.23</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -2117,19 +2117,19 @@
         <v>204.9</v>
       </c>
       <c r="C74">
-        <v>10.25</v>
+        <v>4.1</v>
       </c>
       <c r="D74">
         <v>224.8</v>
       </c>
       <c r="E74">
-        <v>11.24</v>
+        <v>4.5</v>
       </c>
       <c r="F74">
         <v>262.5</v>
       </c>
       <c r="G74">
-        <v>13.12</v>
+        <v>5.25</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -2145,19 +2145,19 @@
         <v>204.9</v>
       </c>
       <c r="C75">
-        <v>10.25</v>
+        <v>4.1</v>
       </c>
       <c r="D75">
         <v>227.0</v>
       </c>
       <c r="E75">
-        <v>11.35</v>
+        <v>4.54</v>
       </c>
       <c r="F75">
         <v>260.8</v>
       </c>
       <c r="G75">
-        <v>13.04</v>
+        <v>5.22</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -2173,19 +2173,19 @@
         <v>205.2</v>
       </c>
       <c r="C76">
-        <v>10.26</v>
+        <v>4.1</v>
       </c>
       <c r="D76">
         <v>225.6</v>
       </c>
       <c r="E76">
-        <v>11.28</v>
+        <v>4.51</v>
       </c>
       <c r="F76">
         <v>262.0</v>
       </c>
       <c r="G76">
-        <v>13.1</v>
+        <v>5.24</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -2201,19 +2201,19 @@
         <v>203.6</v>
       </c>
       <c r="C77">
-        <v>10.18</v>
+        <v>4.07</v>
       </c>
       <c r="D77">
         <v>226.6</v>
       </c>
       <c r="E77">
-        <v>11.33</v>
+        <v>4.53</v>
       </c>
       <c r="F77">
         <v>260.8</v>
       </c>
       <c r="G77">
-        <v>13.04</v>
+        <v>5.22</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -2229,19 +2229,19 @@
         <v>205.3</v>
       </c>
       <c r="C78">
-        <v>10.27</v>
+        <v>4.11</v>
       </c>
       <c r="D78">
         <v>228.9</v>
       </c>
       <c r="E78">
-        <v>11.45</v>
+        <v>4.58</v>
       </c>
       <c r="F78">
         <v>260.6</v>
       </c>
       <c r="G78">
-        <v>13.03</v>
+        <v>5.21</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -2257,19 +2257,19 @@
         <v>206.2</v>
       </c>
       <c r="C79">
-        <v>10.31</v>
+        <v>4.12</v>
       </c>
       <c r="D79">
         <v>229.0</v>
       </c>
       <c r="E79">
-        <v>11.45</v>
+        <v>4.58</v>
       </c>
       <c r="F79">
         <v>259.2</v>
       </c>
       <c r="G79">
-        <v>12.96</v>
+        <v>5.18</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -2285,19 +2285,19 @@
         <v>207.2</v>
       </c>
       <c r="C80">
-        <v>10.36</v>
+        <v>4.14</v>
       </c>
       <c r="D80">
         <v>228.8</v>
       </c>
       <c r="E80">
-        <v>11.44</v>
+        <v>4.58</v>
       </c>
       <c r="F80">
         <v>258.3</v>
       </c>
       <c r="G80">
-        <v>12.92</v>
+        <v>5.17</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -2313,19 +2313,19 @@
         <v>206.6</v>
       </c>
       <c r="C81">
-        <v>10.33</v>
+        <v>4.13</v>
       </c>
       <c r="D81">
         <v>230.5</v>
       </c>
       <c r="E81">
-        <v>11.53</v>
+        <v>4.61</v>
       </c>
       <c r="F81">
         <v>258.8</v>
       </c>
       <c r="G81">
-        <v>12.94</v>
+        <v>5.18</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -2341,19 +2341,19 @@
         <v>207.1</v>
       </c>
       <c r="C82">
-        <v>10.36</v>
+        <v>4.14</v>
       </c>
       <c r="D82">
         <v>231.7</v>
       </c>
       <c r="E82">
-        <v>11.59</v>
+        <v>4.63</v>
       </c>
       <c r="F82">
         <v>259.6</v>
       </c>
       <c r="G82">
-        <v>12.98</v>
+        <v>5.19</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -2369,19 +2369,19 @@
         <v>206.6</v>
       </c>
       <c r="C83">
-        <v>10.33</v>
+        <v>4.13</v>
       </c>
       <c r="D83">
         <v>231.5</v>
       </c>
       <c r="E83">
-        <v>11.58</v>
+        <v>4.63</v>
       </c>
       <c r="F83">
         <v>259.4</v>
       </c>
       <c r="G83">
-        <v>12.97</v>
+        <v>5.19</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -2397,19 +2397,19 @@
         <v>209.0</v>
       </c>
       <c r="C84">
-        <v>10.45</v>
+        <v>4.18</v>
       </c>
       <c r="D84">
         <v>232.9</v>
       </c>
       <c r="E84">
-        <v>11.65</v>
+        <v>4.66</v>
       </c>
       <c r="F84">
         <v>257.6</v>
       </c>
       <c r="G84">
-        <v>12.88</v>
+        <v>5.15</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -2425,19 +2425,19 @@
         <v>208.0</v>
       </c>
       <c r="C85">
-        <v>10.4</v>
+        <v>4.16</v>
       </c>
       <c r="D85">
         <v>232.1</v>
       </c>
       <c r="E85">
-        <v>11.61</v>
+        <v>4.64</v>
       </c>
       <c r="F85">
         <v>260.0</v>
       </c>
       <c r="G85">
-        <v>13.0</v>
+        <v>5.2</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -2453,19 +2453,19 @@
         <v>208.6</v>
       </c>
       <c r="C86">
-        <v>10.43</v>
+        <v>4.17</v>
       </c>
       <c r="D86">
         <v>233.5</v>
       </c>
       <c r="E86">
-        <v>11.68</v>
+        <v>4.67</v>
       </c>
       <c r="F86">
         <v>260.8</v>
       </c>
       <c r="G86">
-        <v>13.04</v>
+        <v>5.22</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -2481,19 +2481,19 @@
         <v>209.2</v>
       </c>
       <c r="C87">
-        <v>10.46</v>
+        <v>4.18</v>
       </c>
       <c r="D87">
         <v>233.7</v>
       </c>
       <c r="E87">
-        <v>11.69</v>
+        <v>4.67</v>
       </c>
       <c r="F87">
         <v>261.9</v>
       </c>
       <c r="G87">
-        <v>13.09</v>
+        <v>5.24</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -2509,19 +2509,19 @@
         <v>209.8</v>
       </c>
       <c r="C88">
-        <v>10.49</v>
+        <v>4.2</v>
       </c>
       <c r="D88">
         <v>232.9</v>
       </c>
       <c r="E88">
-        <v>11.65</v>
+        <v>4.66</v>
       </c>
       <c r="F88">
         <v>261.3</v>
       </c>
       <c r="G88">
-        <v>13.07</v>
+        <v>5.23</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -2537,19 +2537,19 @@
         <v>210.5</v>
       </c>
       <c r="C89">
-        <v>10.53</v>
+        <v>4.21</v>
       </c>
       <c r="D89">
         <v>233.2</v>
       </c>
       <c r="E89">
-        <v>11.66</v>
+        <v>4.66</v>
       </c>
       <c r="F89">
         <v>262.6</v>
       </c>
       <c r="G89">
-        <v>13.13</v>
+        <v>5.25</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -2565,19 +2565,19 @@
         <v>212.0</v>
       </c>
       <c r="C90">
-        <v>10.6</v>
+        <v>4.24</v>
       </c>
       <c r="D90">
         <v>234.6</v>
       </c>
       <c r="E90">
-        <v>11.73</v>
+        <v>4.69</v>
       </c>
       <c r="F90">
         <v>263.5</v>
       </c>
       <c r="G90">
-        <v>13.18</v>
+        <v>5.27</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -2593,19 +2593,19 @@
         <v>211.6</v>
       </c>
       <c r="C91">
-        <v>10.58</v>
+        <v>4.23</v>
       </c>
       <c r="D91">
         <v>233.3</v>
       </c>
       <c r="E91">
-        <v>11.67</v>
+        <v>4.67</v>
       </c>
       <c r="F91">
         <v>263.5</v>
       </c>
       <c r="G91">
-        <v>13.18</v>
+        <v>5.27</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -2621,19 +2621,19 @@
         <v>214.6</v>
       </c>
       <c r="C92">
-        <v>10.73</v>
+        <v>4.29</v>
       </c>
       <c r="D92">
         <v>231.8</v>
       </c>
       <c r="E92">
-        <v>11.59</v>
+        <v>4.64</v>
       </c>
       <c r="F92">
         <v>260.9</v>
       </c>
       <c r="G92">
-        <v>13.04</v>
+        <v>5.22</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -2649,19 +2649,19 @@
         <v>212.8</v>
       </c>
       <c r="C93">
-        <v>10.64</v>
+        <v>4.26</v>
       </c>
       <c r="D93">
         <v>233.4</v>
       </c>
       <c r="E93">
-        <v>11.67</v>
+        <v>4.67</v>
       </c>
       <c r="F93">
         <v>264.6</v>
       </c>
       <c r="G93">
-        <v>13.23</v>
+        <v>5.29</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -2677,19 +2677,19 @@
         <v>213.0</v>
       </c>
       <c r="C94">
-        <v>10.65</v>
+        <v>4.26</v>
       </c>
       <c r="D94">
         <v>231.8</v>
       </c>
       <c r="E94">
-        <v>11.59</v>
+        <v>4.64</v>
       </c>
       <c r="F94">
         <v>263.1</v>
       </c>
       <c r="G94">
-        <v>13.16</v>
+        <v>5.26</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -2705,19 +2705,19 @@
         <v>213.8</v>
       </c>
       <c r="C95">
-        <v>10.69</v>
+        <v>4.28</v>
       </c>
       <c r="D95">
         <v>232.6</v>
       </c>
       <c r="E95">
-        <v>11.63</v>
+        <v>4.65</v>
       </c>
       <c r="F95">
         <v>263.2</v>
       </c>
       <c r="G95">
-        <v>13.16</v>
+        <v>5.26</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -2733,19 +2733,19 @@
         <v>212.8</v>
       </c>
       <c r="C96">
-        <v>10.64</v>
+        <v>4.26</v>
       </c>
       <c r="D96">
         <v>231.4</v>
       </c>
       <c r="E96">
-        <v>11.57</v>
+        <v>4.63</v>
       </c>
       <c r="F96">
         <v>262.2</v>
       </c>
       <c r="G96">
-        <v>13.11</v>
+        <v>5.24</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -2761,19 +2761,19 @@
         <v>213.4</v>
       </c>
       <c r="C97">
-        <v>10.67</v>
+        <v>4.27</v>
       </c>
       <c r="D97">
         <v>230.4</v>
       </c>
       <c r="E97">
-        <v>11.52</v>
+        <v>4.61</v>
       </c>
       <c r="F97">
         <v>261.6</v>
       </c>
       <c r="G97">
-        <v>13.08</v>
+        <v>5.23</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -2789,19 +2789,19 @@
         <v>213.3</v>
       </c>
       <c r="C98">
-        <v>10.67</v>
+        <v>4.27</v>
       </c>
       <c r="D98">
         <v>228.9</v>
       </c>
       <c r="E98">
-        <v>11.45</v>
+        <v>4.58</v>
       </c>
       <c r="F98">
         <v>261.5</v>
       </c>
       <c r="G98">
-        <v>13.08</v>
+        <v>5.23</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -2817,19 +2817,19 @@
         <v>213.0</v>
       </c>
       <c r="C99">
-        <v>10.65</v>
+        <v>4.26</v>
       </c>
       <c r="D99">
         <v>229.1</v>
       </c>
       <c r="E99">
-        <v>11.46</v>
+        <v>4.58</v>
       </c>
       <c r="F99">
         <v>261.7</v>
       </c>
       <c r="G99">
-        <v>13.09</v>
+        <v>5.23</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -2845,19 +2845,19 @@
         <v>211.2</v>
       </c>
       <c r="C100">
-        <v>10.56</v>
+        <v>4.22</v>
       </c>
       <c r="D100">
         <v>229.1</v>
       </c>
       <c r="E100">
-        <v>11.46</v>
+        <v>4.58</v>
       </c>
       <c r="F100">
         <v>259.6</v>
       </c>
       <c r="G100">
-        <v>12.98</v>
+        <v>5.19</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -2873,19 +2873,19 @@
         <v>209.6</v>
       </c>
       <c r="C101">
-        <v>10.48</v>
+        <v>4.19</v>
       </c>
       <c r="D101">
         <v>230.1</v>
       </c>
       <c r="E101">
-        <v>11.51</v>
+        <v>4.6</v>
       </c>
       <c r="F101">
         <v>256.5</v>
       </c>
       <c r="G101">
-        <v>12.83</v>
+        <v>5.13</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -2901,19 +2901,19 @@
         <v>207.1</v>
       </c>
       <c r="C102">
-        <v>10.36</v>
+        <v>4.14</v>
       </c>
       <c r="D102">
         <v>228.9</v>
       </c>
       <c r="E102">
-        <v>11.45</v>
+        <v>4.58</v>
       </c>
       <c r="F102">
         <v>257.5</v>
       </c>
       <c r="G102">
-        <v>12.88</v>
+        <v>5.15</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -2929,19 +2929,19 @@
         <v>207.8</v>
       </c>
       <c r="C103">
-        <v>10.39</v>
+        <v>4.16</v>
       </c>
       <c r="D103">
         <v>229.4</v>
       </c>
       <c r="E103">
-        <v>11.47</v>
+        <v>4.59</v>
       </c>
       <c r="F103">
         <v>257.1</v>
       </c>
       <c r="G103">
-        <v>12.86</v>
+        <v>5.14</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -2957,19 +2957,19 @@
         <v>207.2</v>
       </c>
       <c r="C104">
-        <v>10.36</v>
+        <v>4.14</v>
       </c>
       <c r="D104">
         <v>227.9</v>
       </c>
       <c r="E104">
-        <v>11.4</v>
+        <v>4.56</v>
       </c>
       <c r="F104">
         <v>255.2</v>
       </c>
       <c r="G104">
-        <v>12.76</v>
+        <v>5.1</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -2985,19 +2985,19 @@
         <v>206.9</v>
       </c>
       <c r="C105">
-        <v>10.35</v>
+        <v>4.14</v>
       </c>
       <c r="D105">
         <v>230.8</v>
       </c>
       <c r="E105">
-        <v>11.54</v>
+        <v>4.62</v>
       </c>
       <c r="F105">
         <v>254.2</v>
       </c>
       <c r="G105">
-        <v>12.71</v>
+        <v>5.08</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -3013,19 +3013,19 @@
         <v>205.5</v>
       </c>
       <c r="C106">
-        <v>10.28</v>
+        <v>4.11</v>
       </c>
       <c r="D106">
         <v>228.1</v>
       </c>
       <c r="E106">
-        <v>11.41</v>
+        <v>4.56</v>
       </c>
       <c r="F106">
         <v>252.3</v>
       </c>
       <c r="G106">
-        <v>12.62</v>
+        <v>5.05</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -3041,19 +3041,19 @@
         <v>206.1</v>
       </c>
       <c r="C107">
-        <v>10.3</v>
+        <v>4.12</v>
       </c>
       <c r="D107">
         <v>227.3</v>
       </c>
       <c r="E107">
-        <v>11.37</v>
+        <v>4.55</v>
       </c>
       <c r="F107">
         <v>250.4</v>
       </c>
       <c r="G107">
-        <v>12.52</v>
+        <v>5.01</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -3069,19 +3069,19 @@
         <v>205.7</v>
       </c>
       <c r="C108">
-        <v>10.29</v>
+        <v>4.11</v>
       </c>
       <c r="D108">
         <v>226.8</v>
       </c>
       <c r="E108">
-        <v>11.34</v>
+        <v>4.54</v>
       </c>
       <c r="F108">
         <v>251.4</v>
       </c>
       <c r="G108">
-        <v>12.57</v>
+        <v>5.03</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -3097,19 +3097,19 @@
         <v>207.3</v>
       </c>
       <c r="C109">
-        <v>10.37</v>
+        <v>4.15</v>
       </c>
       <c r="D109">
         <v>226.6</v>
       </c>
       <c r="E109">
-        <v>11.33</v>
+        <v>4.53</v>
       </c>
       <c r="F109">
         <v>250.2</v>
       </c>
       <c r="G109">
-        <v>12.51</v>
+        <v>5.0</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -3125,19 +3125,19 @@
         <v>207.0</v>
       </c>
       <c r="C110">
-        <v>10.35</v>
+        <v>4.14</v>
       </c>
       <c r="D110">
         <v>226.2</v>
       </c>
       <c r="E110">
-        <v>11.31</v>
+        <v>4.52</v>
       </c>
       <c r="F110">
         <v>250.2</v>
       </c>
       <c r="G110">
-        <v>12.51</v>
+        <v>5.0</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -3153,19 +3153,19 @@
         <v>206.5</v>
       </c>
       <c r="C111">
-        <v>10.33</v>
+        <v>4.13</v>
       </c>
       <c r="D111">
         <v>224.0</v>
       </c>
       <c r="E111">
-        <v>11.2</v>
+        <v>4.48</v>
       </c>
       <c r="F111">
         <v>249.2</v>
       </c>
       <c r="G111">
-        <v>12.46</v>
+        <v>4.98</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -3181,19 +3181,19 @@
         <v>206.4</v>
       </c>
       <c r="C112">
-        <v>10.32</v>
+        <v>4.13</v>
       </c>
       <c r="D112">
         <v>224.3</v>
       </c>
       <c r="E112">
-        <v>11.22</v>
+        <v>4.49</v>
       </c>
       <c r="F112">
         <v>251.0</v>
       </c>
       <c r="G112">
-        <v>12.55</v>
+        <v>5.02</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -3209,19 +3209,19 @@
         <v>206.7</v>
       </c>
       <c r="C113">
-        <v>10.34</v>
+        <v>4.13</v>
       </c>
       <c r="D113">
         <v>224.2</v>
       </c>
       <c r="E113">
-        <v>11.21</v>
+        <v>4.48</v>
       </c>
       <c r="F113">
         <v>251.1</v>
       </c>
       <c r="G113">
-        <v>12.55</v>
+        <v>5.02</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -3237,19 +3237,19 @@
         <v>207.4</v>
       </c>
       <c r="C114">
-        <v>10.37</v>
+        <v>4.15</v>
       </c>
       <c r="D114">
         <v>226.4</v>
       </c>
       <c r="E114">
-        <v>11.32</v>
+        <v>4.53</v>
       </c>
       <c r="F114">
         <v>252.3</v>
       </c>
       <c r="G114">
-        <v>12.62</v>
+        <v>5.05</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -3265,19 +3265,19 @@
         <v>206.8</v>
       </c>
       <c r="C115">
-        <v>10.34</v>
+        <v>4.14</v>
       </c>
       <c r="D115">
         <v>226.4</v>
       </c>
       <c r="E115">
-        <v>11.32</v>
+        <v>4.53</v>
       </c>
       <c r="F115">
         <v>254.3</v>
       </c>
       <c r="G115">
-        <v>12.72</v>
+        <v>5.09</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -3293,19 +3293,19 @@
         <v>206.8</v>
       </c>
       <c r="C116">
-        <v>10.34</v>
+        <v>4.14</v>
       </c>
       <c r="D116">
         <v>227.6</v>
       </c>
       <c r="E116">
-        <v>11.38</v>
+        <v>4.55</v>
       </c>
       <c r="F116">
         <v>254.4</v>
       </c>
       <c r="G116">
-        <v>12.72</v>
+        <v>5.09</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -3321,19 +3321,19 @@
         <v>208.8</v>
       </c>
       <c r="C117">
-        <v>10.44</v>
+        <v>4.18</v>
       </c>
       <c r="D117">
         <v>228.9</v>
       </c>
       <c r="E117">
-        <v>11.45</v>
+        <v>4.58</v>
       </c>
       <c r="F117">
         <v>254.3</v>
       </c>
       <c r="G117">
-        <v>12.72</v>
+        <v>5.09</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -3349,19 +3349,19 @@
         <v>206.2</v>
       </c>
       <c r="C118">
-        <v>10.31</v>
+        <v>4.12</v>
       </c>
       <c r="D118">
         <v>230.1</v>
       </c>
       <c r="E118">
-        <v>11.51</v>
+        <v>4.6</v>
       </c>
       <c r="F118">
         <v>256.8</v>
       </c>
       <c r="G118">
-        <v>12.84</v>
+        <v>5.14</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -3377,19 +3377,19 @@
         <v>208.2</v>
       </c>
       <c r="C119">
-        <v>10.41</v>
+        <v>4.16</v>
       </c>
       <c r="D119">
         <v>230.7</v>
       </c>
       <c r="E119">
-        <v>11.54</v>
+        <v>4.61</v>
       </c>
       <c r="F119">
         <v>257.9</v>
       </c>
       <c r="G119">
-        <v>12.89</v>
+        <v>5.16</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -3405,19 +3405,19 @@
         <v>207.9</v>
       </c>
       <c r="C120">
-        <v>10.4</v>
+        <v>4.16</v>
       </c>
       <c r="D120">
         <v>231.4</v>
       </c>
       <c r="E120">
-        <v>11.57</v>
+        <v>4.63</v>
       </c>
       <c r="F120">
         <v>257.2</v>
       </c>
       <c r="G120">
-        <v>12.86</v>
+        <v>5.14</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -3433,19 +3433,19 @@
         <v>207.1</v>
       </c>
       <c r="C121">
-        <v>10.36</v>
+        <v>4.14</v>
       </c>
       <c r="D121">
         <v>233.7</v>
       </c>
       <c r="E121">
-        <v>11.69</v>
+        <v>4.67</v>
       </c>
       <c r="F121">
         <v>258.0</v>
       </c>
       <c r="G121">
-        <v>12.9</v>
+        <v>5.16</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -3461,19 +3461,19 @@
         <v>208.3</v>
       </c>
       <c r="C122">
-        <v>10.42</v>
+        <v>4.17</v>
       </c>
       <c r="D122">
         <v>234.0</v>
       </c>
       <c r="E122">
-        <v>11.7</v>
+        <v>4.68</v>
       </c>
       <c r="F122">
         <v>257.4</v>
       </c>
       <c r="G122">
-        <v>12.87</v>
+        <v>5.15</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -3489,19 +3489,19 @@
         <v>206.0</v>
       </c>
       <c r="C123">
-        <v>10.3</v>
+        <v>4.12</v>
       </c>
       <c r="D123">
         <v>234.4</v>
       </c>
       <c r="E123">
-        <v>11.72</v>
+        <v>4.69</v>
       </c>
       <c r="F123">
         <v>259.5</v>
       </c>
       <c r="G123">
-        <v>12.98</v>
+        <v>5.19</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -3517,19 +3517,19 @@
         <v>206.8</v>
       </c>
       <c r="C124">
-        <v>10.34</v>
+        <v>4.14</v>
       </c>
       <c r="D124">
         <v>234.9</v>
       </c>
       <c r="E124">
-        <v>11.75</v>
+        <v>4.7</v>
       </c>
       <c r="F124">
         <v>259.7</v>
       </c>
       <c r="G124">
-        <v>12.98</v>
+        <v>5.19</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -3545,19 +3545,19 @@
         <v>207.1</v>
       </c>
       <c r="C125">
-        <v>10.36</v>
+        <v>4.14</v>
       </c>
       <c r="D125">
         <v>235.3</v>
       </c>
       <c r="E125">
-        <v>11.77</v>
+        <v>4.71</v>
       </c>
       <c r="F125">
         <v>258.0</v>
       </c>
       <c r="G125">
-        <v>12.9</v>
+        <v>5.16</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -3573,19 +3573,19 @@
         <v>209.6</v>
       </c>
       <c r="C126">
-        <v>10.48</v>
+        <v>4.19</v>
       </c>
       <c r="D126">
         <v>234.8</v>
       </c>
       <c r="E126">
-        <v>11.74</v>
+        <v>4.7</v>
       </c>
       <c r="F126">
         <v>259.7</v>
       </c>
       <c r="G126">
-        <v>12.98</v>
+        <v>5.19</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -3601,19 +3601,19 @@
         <v>206.5</v>
       </c>
       <c r="C127">
-        <v>10.33</v>
+        <v>4.13</v>
       </c>
       <c r="D127">
         <v>233.3</v>
       </c>
       <c r="E127">
-        <v>11.67</v>
+        <v>4.67</v>
       </c>
       <c r="F127">
         <v>260.6</v>
       </c>
       <c r="G127">
-        <v>13.03</v>
+        <v>5.21</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -3629,19 +3629,19 @@
         <v>209.9</v>
       </c>
       <c r="C128">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="D128">
         <v>234.7</v>
       </c>
       <c r="E128">
-        <v>11.73</v>
+        <v>4.69</v>
       </c>
       <c r="F128">
         <v>259.3</v>
       </c>
       <c r="G128">
-        <v>12.97</v>
+        <v>5.19</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -3657,19 +3657,19 @@
         <v>210.2</v>
       </c>
       <c r="C129">
-        <v>10.51</v>
+        <v>4.2</v>
       </c>
       <c r="D129">
         <v>234.6</v>
       </c>
       <c r="E129">
-        <v>11.73</v>
+        <v>4.69</v>
       </c>
       <c r="F129">
         <v>261.7</v>
       </c>
       <c r="G129">
-        <v>13.09</v>
+        <v>5.23</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -3685,19 +3685,19 @@
         <v>209.5</v>
       </c>
       <c r="C130">
-        <v>10.48</v>
+        <v>4.19</v>
       </c>
       <c r="D130">
         <v>233.6</v>
       </c>
       <c r="E130">
-        <v>11.68</v>
+        <v>4.67</v>
       </c>
       <c r="F130">
         <v>261.2</v>
       </c>
       <c r="G130">
-        <v>13.06</v>
+        <v>5.22</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -3713,19 +3713,19 @@
         <v>209.8</v>
       </c>
       <c r="C131">
-        <v>10.49</v>
+        <v>4.2</v>
       </c>
       <c r="D131">
         <v>234.6</v>
       </c>
       <c r="E131">
-        <v>11.73</v>
+        <v>4.69</v>
       </c>
       <c r="F131">
         <v>262.3</v>
       </c>
       <c r="G131">
-        <v>13.12</v>
+        <v>5.25</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -3741,19 +3741,19 @@
         <v>211.9</v>
       </c>
       <c r="C132">
-        <v>10.6</v>
+        <v>4.24</v>
       </c>
       <c r="D132">
         <v>236.1</v>
       </c>
       <c r="E132">
-        <v>11.8</v>
+        <v>4.72</v>
       </c>
       <c r="F132">
         <v>262.5</v>
       </c>
       <c r="G132">
-        <v>13.12</v>
+        <v>5.25</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -3769,19 +3769,19 @@
         <v>211.6</v>
       </c>
       <c r="C133">
-        <v>10.58</v>
+        <v>4.23</v>
       </c>
       <c r="D133">
         <v>236.9</v>
       </c>
       <c r="E133">
-        <v>11.85</v>
+        <v>4.74</v>
       </c>
       <c r="F133">
         <v>261.9</v>
       </c>
       <c r="G133">
-        <v>13.09</v>
+        <v>5.24</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -3797,19 +3797,19 @@
         <v>213.1</v>
       </c>
       <c r="C134">
-        <v>10.66</v>
+        <v>4.26</v>
       </c>
       <c r="D134">
         <v>236.5</v>
       </c>
       <c r="E134">
-        <v>11.83</v>
+        <v>4.73</v>
       </c>
       <c r="F134">
         <v>262.1</v>
       </c>
       <c r="G134">
-        <v>13.11</v>
+        <v>5.24</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -3825,19 +3825,19 @@
         <v>211.8</v>
       </c>
       <c r="C135">
-        <v>10.59</v>
+        <v>4.24</v>
       </c>
       <c r="D135">
         <v>236.4</v>
       </c>
       <c r="E135">
-        <v>11.82</v>
+        <v>4.73</v>
       </c>
       <c r="F135">
         <v>261.0</v>
       </c>
       <c r="G135">
-        <v>13.05</v>
+        <v>5.22</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -3853,19 +3853,19 @@
         <v>211.5</v>
       </c>
       <c r="C136">
-        <v>10.58</v>
+        <v>4.23</v>
       </c>
       <c r="D136">
         <v>237.7</v>
       </c>
       <c r="E136">
-        <v>11.88</v>
+        <v>4.75</v>
       </c>
       <c r="F136">
         <v>261.0</v>
       </c>
       <c r="G136">
-        <v>13.05</v>
+        <v>5.22</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -3881,19 +3881,19 @@
         <v>211.3</v>
       </c>
       <c r="C137">
-        <v>10.57</v>
+        <v>4.23</v>
       </c>
       <c r="D137">
         <v>238.3</v>
       </c>
       <c r="E137">
-        <v>11.92</v>
+        <v>4.77</v>
       </c>
       <c r="F137">
         <v>259.8</v>
       </c>
       <c r="G137">
-        <v>12.99</v>
+        <v>5.2</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -3909,19 +3909,19 @@
         <v>209.9</v>
       </c>
       <c r="C138">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="D138">
         <v>238.5</v>
       </c>
       <c r="E138">
-        <v>11.93</v>
+        <v>4.77</v>
       </c>
       <c r="F138">
         <v>259.4</v>
       </c>
       <c r="G138">
-        <v>12.97</v>
+        <v>5.19</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -3937,19 +3937,19 @@
         <v>211.4</v>
       </c>
       <c r="C139">
-        <v>10.57</v>
+        <v>4.23</v>
       </c>
       <c r="D139">
         <v>238.3</v>
       </c>
       <c r="E139">
-        <v>11.92</v>
+        <v>4.77</v>
       </c>
       <c r="F139">
         <v>257.9</v>
       </c>
       <c r="G139">
-        <v>12.89</v>
+        <v>5.16</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -3965,19 +3965,19 @@
         <v>208.8</v>
       </c>
       <c r="C140">
-        <v>10.44</v>
+        <v>4.18</v>
       </c>
       <c r="D140">
         <v>238.9</v>
       </c>
       <c r="E140">
-        <v>11.95</v>
+        <v>4.78</v>
       </c>
       <c r="F140">
         <v>257.8</v>
       </c>
       <c r="G140">
-        <v>12.89</v>
+        <v>5.16</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -3993,19 +3993,19 @@
         <v>210.0</v>
       </c>
       <c r="C141">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="D141">
         <v>237.3</v>
       </c>
       <c r="E141">
-        <v>11.87</v>
+        <v>4.75</v>
       </c>
       <c r="F141">
         <v>257.0</v>
       </c>
       <c r="G141">
-        <v>12.85</v>
+        <v>5.14</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -4021,19 +4021,19 @@
         <v>210.4</v>
       </c>
       <c r="C142">
-        <v>10.52</v>
+        <v>4.21</v>
       </c>
       <c r="D142">
         <v>240.4</v>
       </c>
       <c r="E142">
-        <v>12.02</v>
+        <v>4.81</v>
       </c>
       <c r="F142">
         <v>256.8</v>
       </c>
       <c r="G142">
-        <v>12.84</v>
+        <v>5.14</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -4049,19 +4049,19 @@
         <v>209.2</v>
       </c>
       <c r="C143">
-        <v>10.46</v>
+        <v>4.18</v>
       </c>
       <c r="D143">
         <v>237.9</v>
       </c>
       <c r="E143">
-        <v>11.9</v>
+        <v>4.76</v>
       </c>
       <c r="F143">
         <v>257.2</v>
       </c>
       <c r="G143">
-        <v>12.86</v>
+        <v>5.14</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -4077,19 +4077,19 @@
         <v>210.9</v>
       </c>
       <c r="C144">
-        <v>10.55</v>
+        <v>4.22</v>
       </c>
       <c r="D144">
         <v>237.6</v>
       </c>
       <c r="E144">
-        <v>11.88</v>
+        <v>4.75</v>
       </c>
       <c r="F144">
         <v>254.9</v>
       </c>
       <c r="G144">
-        <v>12.75</v>
+        <v>5.1</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -4105,19 +4105,19 @@
         <v>209.4</v>
       </c>
       <c r="C145">
-        <v>10.47</v>
+        <v>4.19</v>
       </c>
       <c r="D145">
         <v>237.7</v>
       </c>
       <c r="E145">
-        <v>11.88</v>
+        <v>4.75</v>
       </c>
       <c r="F145">
         <v>255.3</v>
       </c>
       <c r="G145">
-        <v>12.77</v>
+        <v>5.11</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -4133,19 +4133,19 @@
         <v>209.0</v>
       </c>
       <c r="C146">
-        <v>10.45</v>
+        <v>4.18</v>
       </c>
       <c r="D146">
         <v>238.6</v>
       </c>
       <c r="E146">
-        <v>11.93</v>
+        <v>4.77</v>
       </c>
       <c r="F146">
         <v>254.5</v>
       </c>
       <c r="G146">
-        <v>12.73</v>
+        <v>5.09</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -4161,19 +4161,19 @@
         <v>210.2</v>
       </c>
       <c r="C147">
-        <v>10.51</v>
+        <v>4.2</v>
       </c>
       <c r="D147">
         <v>238.1</v>
       </c>
       <c r="E147">
-        <v>11.91</v>
+        <v>4.76</v>
       </c>
       <c r="F147">
         <v>256.4</v>
       </c>
       <c r="G147">
-        <v>12.82</v>
+        <v>5.13</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -4189,19 +4189,19 @@
         <v>209.9</v>
       </c>
       <c r="C148">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="D148">
         <v>235.2</v>
       </c>
       <c r="E148">
-        <v>11.76</v>
+        <v>4.7</v>
       </c>
       <c r="F148">
         <v>254.6</v>
       </c>
       <c r="G148">
-        <v>12.73</v>
+        <v>5.09</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -4217,19 +4217,19 @@
         <v>210.2</v>
       </c>
       <c r="C149">
-        <v>10.51</v>
+        <v>4.2</v>
       </c>
       <c r="D149">
         <v>236.2</v>
       </c>
       <c r="E149">
-        <v>11.81</v>
+        <v>4.72</v>
       </c>
       <c r="F149">
         <v>256.0</v>
       </c>
       <c r="G149">
-        <v>12.8</v>
+        <v>5.12</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -4245,19 +4245,19 @@
         <v>209.5</v>
       </c>
       <c r="C150">
-        <v>10.48</v>
+        <v>4.19</v>
       </c>
       <c r="D150">
         <v>235.5</v>
       </c>
       <c r="E150">
-        <v>11.78</v>
+        <v>4.71</v>
       </c>
       <c r="F150">
         <v>254.1</v>
       </c>
       <c r="G150">
-        <v>12.71</v>
+        <v>5.08</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -4273,19 +4273,19 @@
         <v>210.7</v>
       </c>
       <c r="C151">
-        <v>10.54</v>
+        <v>4.21</v>
       </c>
       <c r="D151">
         <v>235.6</v>
       </c>
       <c r="E151">
-        <v>11.78</v>
+        <v>4.71</v>
       </c>
       <c r="F151">
         <v>255.2</v>
       </c>
       <c r="G151">
-        <v>12.76</v>
+        <v>5.1</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -4301,19 +4301,19 @@
         <v>210.8</v>
       </c>
       <c r="C152">
-        <v>10.54</v>
+        <v>4.22</v>
       </c>
       <c r="D152">
         <v>233.8</v>
       </c>
       <c r="E152">
-        <v>11.69</v>
+        <v>4.68</v>
       </c>
       <c r="F152">
         <v>257.7</v>
       </c>
       <c r="G152">
-        <v>12.88</v>
+        <v>5.15</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -4329,19 +4329,19 @@
         <v>209.3</v>
       </c>
       <c r="C153">
-        <v>10.47</v>
+        <v>4.19</v>
       </c>
       <c r="D153">
         <v>233.5</v>
       </c>
       <c r="E153">
-        <v>11.68</v>
+        <v>4.67</v>
       </c>
       <c r="F153">
         <v>255.8</v>
       </c>
       <c r="G153">
-        <v>12.79</v>
+        <v>5.12</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -4357,19 +4357,19 @@
         <v>209.6</v>
       </c>
       <c r="C154">
-        <v>10.48</v>
+        <v>4.19</v>
       </c>
       <c r="D154">
         <v>232.8</v>
       </c>
       <c r="E154">
-        <v>11.64</v>
+        <v>4.66</v>
       </c>
       <c r="F154">
         <v>255.8</v>
       </c>
       <c r="G154">
-        <v>12.79</v>
+        <v>5.12</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -4385,19 +4385,19 @@
         <v>208.9</v>
       </c>
       <c r="C155">
-        <v>10.45</v>
+        <v>4.18</v>
       </c>
       <c r="D155">
         <v>232.9</v>
       </c>
       <c r="E155">
-        <v>11.65</v>
+        <v>4.66</v>
       </c>
       <c r="F155">
         <v>255.5</v>
       </c>
       <c r="G155">
-        <v>12.78</v>
+        <v>5.11</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -4413,19 +4413,19 @@
         <v>211.2</v>
       </c>
       <c r="C156">
-        <v>10.56</v>
+        <v>4.22</v>
       </c>
       <c r="D156">
         <v>231.8</v>
       </c>
       <c r="E156">
-        <v>11.59</v>
+        <v>4.64</v>
       </c>
       <c r="F156">
         <v>255.4</v>
       </c>
       <c r="G156">
-        <v>12.77</v>
+        <v>5.11</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -4441,19 +4441,19 @@
         <v>210.9</v>
       </c>
       <c r="C157">
-        <v>10.55</v>
+        <v>4.22</v>
       </c>
       <c r="D157">
         <v>231.5</v>
       </c>
       <c r="E157">
-        <v>11.58</v>
+        <v>4.63</v>
       </c>
       <c r="F157">
         <v>256.6</v>
       </c>
       <c r="G157">
-        <v>12.83</v>
+        <v>5.13</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -4469,19 +4469,19 @@
         <v>209.8</v>
       </c>
       <c r="C158">
-        <v>10.49</v>
+        <v>4.2</v>
       </c>
       <c r="D158">
         <v>231.0</v>
       </c>
       <c r="E158">
-        <v>11.55</v>
+        <v>4.62</v>
       </c>
       <c r="F158">
         <v>256.1</v>
       </c>
       <c r="G158">
-        <v>12.81</v>
+        <v>5.12</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -4497,19 +4497,19 @@
         <v>212.9</v>
       </c>
       <c r="C159">
-        <v>10.65</v>
+        <v>4.26</v>
       </c>
       <c r="D159">
         <v>230.2</v>
       </c>
       <c r="E159">
-        <v>11.51</v>
+        <v>4.6</v>
       </c>
       <c r="F159">
         <v>258.3</v>
       </c>
       <c r="G159">
-        <v>12.92</v>
+        <v>5.17</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -4525,19 +4525,19 @@
         <v>212.0</v>
       </c>
       <c r="C160">
-        <v>10.6</v>
+        <v>4.24</v>
       </c>
       <c r="D160">
         <v>230.8</v>
       </c>
       <c r="E160">
-        <v>11.54</v>
+        <v>4.62</v>
       </c>
       <c r="F160">
         <v>258.2</v>
       </c>
       <c r="G160">
-        <v>12.91</v>
+        <v>5.16</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -4553,19 +4553,19 @@
         <v>211.2</v>
       </c>
       <c r="C161">
-        <v>10.56</v>
+        <v>4.22</v>
       </c>
       <c r="D161">
         <v>229.6</v>
       </c>
       <c r="E161">
-        <v>11.48</v>
+        <v>4.59</v>
       </c>
       <c r="F161">
         <v>258.4</v>
       </c>
       <c r="G161">
-        <v>12.92</v>
+        <v>5.17</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -4581,19 +4581,19 @@
         <v>211.8</v>
       </c>
       <c r="C162">
-        <v>10.59</v>
+        <v>4.24</v>
       </c>
       <c r="D162">
         <v>229.8</v>
       </c>
       <c r="E162">
-        <v>11.49</v>
+        <v>4.6</v>
       </c>
       <c r="F162">
         <v>257.3</v>
       </c>
       <c r="G162">
-        <v>12.87</v>
+        <v>5.15</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -4609,19 +4609,19 @@
         <v>212.1</v>
       </c>
       <c r="C163">
-        <v>10.61</v>
+        <v>4.24</v>
       </c>
       <c r="D163">
         <v>229.4</v>
       </c>
       <c r="E163">
-        <v>11.47</v>
+        <v>4.59</v>
       </c>
       <c r="F163">
         <v>258.0</v>
       </c>
       <c r="G163">
-        <v>12.9</v>
+        <v>5.16</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -4637,19 +4637,19 @@
         <v>211.5</v>
       </c>
       <c r="C164">
-        <v>10.58</v>
+        <v>4.23</v>
       </c>
       <c r="D164">
         <v>229.6</v>
       </c>
       <c r="E164">
-        <v>11.48</v>
+        <v>4.59</v>
       </c>
       <c r="F164">
         <v>257.4</v>
       </c>
       <c r="G164">
-        <v>12.87</v>
+        <v>5.15</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -4665,19 +4665,19 @@
         <v>210.5</v>
       </c>
       <c r="C165">
-        <v>10.53</v>
+        <v>4.21</v>
       </c>
       <c r="D165">
         <v>229.8</v>
       </c>
       <c r="E165">
-        <v>11.49</v>
+        <v>4.6</v>
       </c>
       <c r="F165">
         <v>260.2</v>
       </c>
       <c r="G165">
-        <v>13.01</v>
+        <v>5.2</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -4693,19 +4693,19 @@
         <v>210.5</v>
       </c>
       <c r="C166">
-        <v>10.53</v>
+        <v>4.21</v>
       </c>
       <c r="D166">
         <v>229.4</v>
       </c>
       <c r="E166">
-        <v>11.47</v>
+        <v>4.59</v>
       </c>
       <c r="F166">
         <v>258.5</v>
       </c>
       <c r="G166">
-        <v>12.93</v>
+        <v>5.17</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -4721,19 +4721,19 @@
         <v>208.8</v>
       </c>
       <c r="C167">
-        <v>10.44</v>
+        <v>4.18</v>
       </c>
       <c r="D167">
         <v>230.9</v>
       </c>
       <c r="E167">
-        <v>11.55</v>
+        <v>4.62</v>
       </c>
       <c r="F167">
         <v>260.8</v>
       </c>
       <c r="G167">
-        <v>13.04</v>
+        <v>5.22</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -4749,19 +4749,19 @@
         <v>207.5</v>
       </c>
       <c r="C168">
-        <v>10.38</v>
+        <v>4.15</v>
       </c>
       <c r="D168">
         <v>231.7</v>
       </c>
       <c r="E168">
-        <v>11.59</v>
+        <v>4.63</v>
       </c>
       <c r="F168">
         <v>259.9</v>
       </c>
       <c r="G168">
-        <v>12.99</v>
+        <v>5.2</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -4777,19 +4777,19 @@
         <v>205.3</v>
       </c>
       <c r="C169">
-        <v>10.27</v>
+        <v>4.11</v>
       </c>
       <c r="D169">
         <v>232.0</v>
       </c>
       <c r="E169">
-        <v>11.6</v>
+        <v>4.64</v>
       </c>
       <c r="F169">
         <v>259.5</v>
       </c>
       <c r="G169">
-        <v>12.98</v>
+        <v>5.19</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -4805,19 +4805,19 @@
         <v>205.4</v>
       </c>
       <c r="C170">
-        <v>10.27</v>
+        <v>4.11</v>
       </c>
       <c r="D170">
         <v>231.5</v>
       </c>
       <c r="E170">
-        <v>11.58</v>
+        <v>4.63</v>
       </c>
       <c r="F170">
         <v>259.8</v>
       </c>
       <c r="G170">
-        <v>12.99</v>
+        <v>5.2</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -4833,19 +4833,19 @@
         <v>204.7</v>
       </c>
       <c r="C171">
-        <v>10.23</v>
+        <v>4.09</v>
       </c>
       <c r="D171">
         <v>231.4</v>
       </c>
       <c r="E171">
-        <v>11.57</v>
+        <v>4.63</v>
       </c>
       <c r="F171">
         <v>259.8</v>
       </c>
       <c r="G171">
-        <v>12.99</v>
+        <v>5.2</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -4861,19 +4861,19 @@
         <v>204.9</v>
       </c>
       <c r="C172">
-        <v>10.25</v>
+        <v>4.1</v>
       </c>
       <c r="D172">
         <v>232.3</v>
       </c>
       <c r="E172">
-        <v>11.62</v>
+        <v>4.65</v>
       </c>
       <c r="F172">
         <v>258.4</v>
       </c>
       <c r="G172">
-        <v>12.92</v>
+        <v>5.17</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -4889,19 +4889,19 @@
         <v>203.7</v>
       </c>
       <c r="C173">
-        <v>10.19</v>
+        <v>4.07</v>
       </c>
       <c r="D173">
         <v>232.4</v>
       </c>
       <c r="E173">
-        <v>11.62</v>
+        <v>4.65</v>
       </c>
       <c r="F173">
         <v>257.5</v>
       </c>
       <c r="G173">
-        <v>12.88</v>
+        <v>5.15</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -4917,19 +4917,19 @@
         <v>205.4</v>
       </c>
       <c r="C174">
-        <v>10.27</v>
+        <v>4.11</v>
       </c>
       <c r="D174">
         <v>233.1</v>
       </c>
       <c r="E174">
-        <v>11.66</v>
+        <v>4.66</v>
       </c>
       <c r="F174">
         <v>258.4</v>
       </c>
       <c r="G174">
-        <v>12.92</v>
+        <v>5.17</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -4945,19 +4945,19 @@
         <v>206.5</v>
       </c>
       <c r="C175">
-        <v>10.33</v>
+        <v>4.13</v>
       </c>
       <c r="D175">
         <v>233.8</v>
       </c>
       <c r="E175">
-        <v>11.69</v>
+        <v>4.68</v>
       </c>
       <c r="F175">
         <v>258.6</v>
       </c>
       <c r="G175">
-        <v>12.93</v>
+        <v>5.17</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -4973,19 +4973,19 @@
         <v>204.4</v>
       </c>
       <c r="C176">
-        <v>10.22</v>
+        <v>4.09</v>
       </c>
       <c r="D176">
         <v>233.2</v>
       </c>
       <c r="E176">
-        <v>11.66</v>
+        <v>4.66</v>
       </c>
       <c r="F176">
         <v>258.4</v>
       </c>
       <c r="G176">
-        <v>12.92</v>
+        <v>5.17</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -5001,19 +5001,19 @@
         <v>205.8</v>
       </c>
       <c r="C177">
-        <v>10.29</v>
+        <v>4.12</v>
       </c>
       <c r="D177">
         <v>235.0</v>
       </c>
       <c r="E177">
-        <v>11.75</v>
+        <v>4.7</v>
       </c>
       <c r="F177">
         <v>257.9</v>
       </c>
       <c r="G177">
-        <v>12.89</v>
+        <v>5.16</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -5029,19 +5029,19 @@
         <v>205.5</v>
       </c>
       <c r="C178">
-        <v>10.28</v>
+        <v>4.11</v>
       </c>
       <c r="D178">
         <v>234.1</v>
       </c>
       <c r="E178">
-        <v>11.71</v>
+        <v>4.68</v>
       </c>
       <c r="F178">
         <v>260.1</v>
       </c>
       <c r="G178">
-        <v>13.01</v>
+        <v>5.2</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -5057,19 +5057,19 @@
         <v>206.5</v>
       </c>
       <c r="C179">
-        <v>10.33</v>
+        <v>4.13</v>
       </c>
       <c r="D179">
         <v>232.4</v>
       </c>
       <c r="E179">
-        <v>11.62</v>
+        <v>4.65</v>
       </c>
       <c r="F179">
         <v>260.8</v>
       </c>
       <c r="G179">
-        <v>13.04</v>
+        <v>5.22</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -5085,19 +5085,19 @@
         <v>207.4</v>
       </c>
       <c r="C180">
-        <v>10.37</v>
+        <v>4.15</v>
       </c>
       <c r="D180">
         <v>235.0</v>
       </c>
       <c r="E180">
-        <v>11.75</v>
+        <v>4.7</v>
       </c>
       <c r="F180">
         <v>260.6</v>
       </c>
       <c r="G180">
-        <v>13.03</v>
+        <v>5.21</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -5113,19 +5113,19 @@
         <v>205.8</v>
       </c>
       <c r="C181">
-        <v>10.29</v>
+        <v>4.12</v>
       </c>
       <c r="D181">
         <v>233.8</v>
       </c>
       <c r="E181">
-        <v>11.69</v>
+        <v>4.68</v>
       </c>
       <c r="F181">
         <v>258.6</v>
       </c>
       <c r="G181">
-        <v>12.93</v>
+        <v>5.17</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -5141,19 +5141,19 @@
         <v>205.8</v>
       </c>
       <c r="C182">
-        <v>10.29</v>
+        <v>4.12</v>
       </c>
       <c r="D182">
         <v>233.5</v>
       </c>
       <c r="E182">
-        <v>11.68</v>
+        <v>4.67</v>
       </c>
       <c r="F182">
         <v>259.2</v>
       </c>
       <c r="G182">
-        <v>12.96</v>
+        <v>5.18</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -5169,19 +5169,19 @@
         <v>206.1</v>
       </c>
       <c r="C183">
-        <v>10.3</v>
+        <v>4.12</v>
       </c>
       <c r="D183">
         <v>231.5</v>
       </c>
       <c r="E183">
-        <v>11.58</v>
+        <v>4.63</v>
       </c>
       <c r="F183">
         <v>259.3</v>
       </c>
       <c r="G183">
-        <v>12.97</v>
+        <v>5.19</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -5197,19 +5197,19 @@
         <v>205.8</v>
       </c>
       <c r="C184">
-        <v>10.29</v>
+        <v>4.12</v>
       </c>
       <c r="D184">
         <v>232.6</v>
       </c>
       <c r="E184">
-        <v>11.63</v>
+        <v>4.65</v>
       </c>
       <c r="F184">
         <v>260.8</v>
       </c>
       <c r="G184">
-        <v>13.04</v>
+        <v>5.22</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -5225,19 +5225,19 @@
         <v>204.3</v>
       </c>
       <c r="C185">
-        <v>10.22</v>
+        <v>4.09</v>
       </c>
       <c r="D185">
         <v>231.6</v>
       </c>
       <c r="E185">
-        <v>11.58</v>
+        <v>4.63</v>
       </c>
       <c r="F185">
         <v>261.7</v>
       </c>
       <c r="G185">
-        <v>13.09</v>
+        <v>5.23</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -5253,19 +5253,19 @@
         <v>204.3</v>
       </c>
       <c r="C186">
-        <v>10.22</v>
+        <v>4.09</v>
       </c>
       <c r="D186">
         <v>229.1</v>
       </c>
       <c r="E186">
-        <v>11.46</v>
+        <v>4.58</v>
       </c>
       <c r="F186">
         <v>261.5</v>
       </c>
       <c r="G186">
-        <v>13.08</v>
+        <v>5.23</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -5281,19 +5281,19 @@
         <v>205.6</v>
       </c>
       <c r="C187">
-        <v>10.28</v>
+        <v>4.11</v>
       </c>
       <c r="D187">
         <v>229.7</v>
       </c>
       <c r="E187">
-        <v>11.48</v>
+        <v>4.59</v>
       </c>
       <c r="F187">
         <v>259.7</v>
       </c>
       <c r="G187">
-        <v>12.98</v>
+        <v>5.19</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -5309,19 +5309,19 @@
         <v>205.2</v>
       </c>
       <c r="C188">
-        <v>10.26</v>
+        <v>4.1</v>
       </c>
       <c r="D188">
         <v>226.9</v>
       </c>
       <c r="E188">
-        <v>11.35</v>
+        <v>4.54</v>
       </c>
       <c r="F188">
         <v>260.4</v>
       </c>
       <c r="G188">
-        <v>13.02</v>
+        <v>5.21</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -5337,19 +5337,19 @@
         <v>204.8</v>
       </c>
       <c r="C189">
-        <v>10.24</v>
+        <v>4.1</v>
       </c>
       <c r="D189">
         <v>228.9</v>
       </c>
       <c r="E189">
-        <v>11.45</v>
+        <v>4.58</v>
       </c>
       <c r="F189">
         <v>260.5</v>
       </c>
       <c r="G189">
-        <v>13.03</v>
+        <v>5.21</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -5365,19 +5365,19 @@
         <v>204.9</v>
       </c>
       <c r="C190">
-        <v>10.25</v>
+        <v>4.1</v>
       </c>
       <c r="D190">
         <v>227.4</v>
       </c>
       <c r="E190">
-        <v>11.37</v>
+        <v>4.55</v>
       </c>
       <c r="F190">
         <v>260.7</v>
       </c>
       <c r="G190">
-        <v>13.04</v>
+        <v>5.21</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -5393,19 +5393,19 @@
         <v>204.7</v>
       </c>
       <c r="C191">
-        <v>10.23</v>
+        <v>4.09</v>
       </c>
       <c r="D191">
         <v>226.9</v>
       </c>
       <c r="E191">
-        <v>11.35</v>
+        <v>4.54</v>
       </c>
       <c r="F191">
         <v>260.3</v>
       </c>
       <c r="G191">
-        <v>13.02</v>
+        <v>5.21</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -5421,19 +5421,19 @@
         <v>205.0</v>
       </c>
       <c r="C192">
-        <v>10.25</v>
+        <v>4.1</v>
       </c>
       <c r="D192">
         <v>227.1</v>
       </c>
       <c r="E192">
-        <v>11.36</v>
+        <v>4.54</v>
       </c>
       <c r="F192">
         <v>260.8</v>
       </c>
       <c r="G192">
-        <v>13.04</v>
+        <v>5.22</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -5449,19 +5449,19 @@
         <v>203.7</v>
       </c>
       <c r="C193">
-        <v>10.19</v>
+        <v>4.07</v>
       </c>
       <c r="D193">
         <v>226.7</v>
       </c>
       <c r="E193">
-        <v>11.34</v>
+        <v>4.53</v>
       </c>
       <c r="F193">
         <v>260.9</v>
       </c>
       <c r="G193">
-        <v>13.04</v>
+        <v>5.22</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -5477,19 +5477,19 @@
         <v>205.6</v>
       </c>
       <c r="C194">
-        <v>10.28</v>
+        <v>4.11</v>
       </c>
       <c r="D194">
         <v>225.0</v>
       </c>
       <c r="E194">
-        <v>11.25</v>
+        <v>4.5</v>
       </c>
       <c r="F194">
         <v>258.9</v>
       </c>
       <c r="G194">
-        <v>12.95</v>
+        <v>5.18</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -5505,19 +5505,19 @@
         <v>203.7</v>
       </c>
       <c r="C195">
-        <v>10.19</v>
+        <v>4.07</v>
       </c>
       <c r="D195">
         <v>225.9</v>
       </c>
       <c r="E195">
-        <v>11.3</v>
+        <v>4.52</v>
       </c>
       <c r="F195">
         <v>257.3</v>
       </c>
       <c r="G195">
-        <v>12.87</v>
+        <v>5.15</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -5533,19 +5533,19 @@
         <v>202.9</v>
       </c>
       <c r="C196">
-        <v>10.15</v>
+        <v>4.06</v>
       </c>
       <c r="D196">
         <v>227.2</v>
       </c>
       <c r="E196">
-        <v>11.36</v>
+        <v>4.54</v>
       </c>
       <c r="F196">
         <v>256.8</v>
       </c>
       <c r="G196">
-        <v>12.84</v>
+        <v>5.14</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -5561,19 +5561,19 @@
         <v>201.7</v>
       </c>
       <c r="C197">
-        <v>10.09</v>
+        <v>4.03</v>
       </c>
       <c r="D197">
         <v>228.1</v>
       </c>
       <c r="E197">
-        <v>11.41</v>
+        <v>4.56</v>
       </c>
       <c r="F197">
         <v>255.8</v>
       </c>
       <c r="G197">
-        <v>12.79</v>
+        <v>5.12</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -5589,19 +5589,19 @@
         <v>204.4</v>
       </c>
       <c r="C198">
-        <v>10.22</v>
+        <v>4.09</v>
       </c>
       <c r="D198">
         <v>227.5</v>
       </c>
       <c r="E198">
-        <v>11.38</v>
+        <v>4.55</v>
       </c>
       <c r="F198">
         <v>254.8</v>
       </c>
       <c r="G198">
-        <v>12.74</v>
+        <v>5.1</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -5617,19 +5617,19 @@
         <v>203.7</v>
       </c>
       <c r="C199">
-        <v>10.19</v>
+        <v>4.07</v>
       </c>
       <c r="D199">
         <v>227.9</v>
       </c>
       <c r="E199">
-        <v>11.4</v>
+        <v>4.56</v>
       </c>
       <c r="F199">
         <v>251.5</v>
       </c>
       <c r="G199">
-        <v>12.58</v>
+        <v>5.03</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -5645,19 +5645,19 @@
         <v>202.8</v>
       </c>
       <c r="C200">
-        <v>10.14</v>
+        <v>4.06</v>
       </c>
       <c r="D200">
         <v>229.3</v>
       </c>
       <c r="E200">
-        <v>11.47</v>
+        <v>4.59</v>
       </c>
       <c r="F200">
         <v>252.7</v>
       </c>
       <c r="G200">
-        <v>12.63</v>
+        <v>5.05</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -5673,19 +5673,19 @@
         <v>203.9</v>
       </c>
       <c r="C201">
-        <v>10.2</v>
+        <v>4.08</v>
       </c>
       <c r="D201">
         <v>230.8</v>
       </c>
       <c r="E201">
-        <v>11.54</v>
+        <v>4.62</v>
       </c>
       <c r="F201">
         <v>250.7</v>
       </c>
       <c r="G201">
-        <v>12.54</v>
+        <v>5.01</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -5701,19 +5701,19 @@
         <v>203.2</v>
       </c>
       <c r="C202">
-        <v>10.16</v>
+        <v>4.06</v>
       </c>
       <c r="D202">
         <v>231.0</v>
       </c>
       <c r="E202">
-        <v>11.55</v>
+        <v>4.62</v>
       </c>
       <c r="F202">
         <v>251.0</v>
       </c>
       <c r="G202">
-        <v>12.55</v>
+        <v>5.02</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -5729,19 +5729,19 @@
         <v>202.8</v>
       </c>
       <c r="C203">
-        <v>10.14</v>
+        <v>4.06</v>
       </c>
       <c r="D203">
         <v>231.0</v>
       </c>
       <c r="E203">
-        <v>11.55</v>
+        <v>4.62</v>
       </c>
       <c r="F203">
         <v>251.3</v>
       </c>
       <c r="G203">
-        <v>12.57</v>
+        <v>5.03</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -5757,19 +5757,19 @@
         <v>204.1</v>
       </c>
       <c r="C204">
-        <v>10.21</v>
+        <v>4.08</v>
       </c>
       <c r="D204">
         <v>229.2</v>
       </c>
       <c r="E204">
-        <v>11.46</v>
+        <v>4.58</v>
       </c>
       <c r="F204">
         <v>251.9</v>
       </c>
       <c r="G204">
-        <v>12.6</v>
+        <v>5.04</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -5785,19 +5785,19 @@
         <v>204.1</v>
       </c>
       <c r="C205">
-        <v>10.21</v>
+        <v>4.08</v>
       </c>
       <c r="D205">
         <v>229.3</v>
       </c>
       <c r="E205">
-        <v>11.47</v>
+        <v>4.59</v>
       </c>
       <c r="F205">
         <v>253.5</v>
       </c>
       <c r="G205">
-        <v>12.68</v>
+        <v>5.07</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -5813,19 +5813,19 @@
         <v>205.6</v>
       </c>
       <c r="C206">
-        <v>10.28</v>
+        <v>4.11</v>
       </c>
       <c r="D206">
         <v>227.9</v>
       </c>
       <c r="E206">
-        <v>11.4</v>
+        <v>4.56</v>
       </c>
       <c r="F206">
         <v>254.4</v>
       </c>
       <c r="G206">
-        <v>12.72</v>
+        <v>5.09</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -5841,19 +5841,19 @@
         <v>204.7</v>
       </c>
       <c r="C207">
-        <v>10.23</v>
+        <v>4.09</v>
       </c>
       <c r="D207">
         <v>229.5</v>
       </c>
       <c r="E207">
-        <v>11.48</v>
+        <v>4.59</v>
       </c>
       <c r="F207">
         <v>254.3</v>
       </c>
       <c r="G207">
-        <v>12.72</v>
+        <v>5.09</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -5869,19 +5869,19 @@
         <v>202.8</v>
       </c>
       <c r="C208">
-        <v>10.14</v>
+        <v>4.06</v>
       </c>
       <c r="D208">
         <v>227.1</v>
       </c>
       <c r="E208">
-        <v>11.36</v>
+        <v>4.54</v>
       </c>
       <c r="F208">
         <v>253.3</v>
       </c>
       <c r="G208">
-        <v>12.67</v>
+        <v>5.07</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -5897,19 +5897,19 @@
         <v>205.6</v>
       </c>
       <c r="C209">
-        <v>10.28</v>
+        <v>4.11</v>
       </c>
       <c r="D209">
         <v>227.6</v>
       </c>
       <c r="E209">
-        <v>11.38</v>
+        <v>4.55</v>
       </c>
       <c r="F209">
         <v>254.7</v>
       </c>
       <c r="G209">
-        <v>12.73</v>
+        <v>5.09</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -5925,19 +5925,19 @@
         <v>204.8</v>
       </c>
       <c r="C210">
-        <v>10.24</v>
+        <v>4.1</v>
       </c>
       <c r="D210">
         <v>226.1</v>
       </c>
       <c r="E210">
-        <v>11.3</v>
+        <v>4.52</v>
       </c>
       <c r="F210">
         <v>253.4</v>
       </c>
       <c r="G210">
-        <v>12.67</v>
+        <v>5.07</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -5953,19 +5953,19 @@
         <v>205.9</v>
       </c>
       <c r="C211">
-        <v>10.3</v>
+        <v>4.12</v>
       </c>
       <c r="D211">
         <v>225.6</v>
       </c>
       <c r="E211">
-        <v>11.28</v>
+        <v>4.51</v>
       </c>
       <c r="F211">
         <v>253.8</v>
       </c>
       <c r="G211">
-        <v>12.69</v>
+        <v>5.08</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -5981,19 +5981,19 @@
         <v>205.2</v>
       </c>
       <c r="C212">
-        <v>10.26</v>
+        <v>4.1</v>
       </c>
       <c r="D212">
         <v>225.6</v>
       </c>
       <c r="E212">
-        <v>11.28</v>
+        <v>4.51</v>
       </c>
       <c r="F212">
         <v>254.4</v>
       </c>
       <c r="G212">
-        <v>12.72</v>
+        <v>5.09</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -6009,19 +6009,19 @@
         <v>206.1</v>
       </c>
       <c r="C213">
-        <v>10.3</v>
+        <v>4.12</v>
       </c>
       <c r="D213">
         <v>226.1</v>
       </c>
       <c r="E213">
-        <v>11.3</v>
+        <v>4.52</v>
       </c>
       <c r="F213">
         <v>254.8</v>
       </c>
       <c r="G213">
-        <v>12.74</v>
+        <v>5.1</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -6037,19 +6037,19 @@
         <v>206.5</v>
       </c>
       <c r="C214">
-        <v>10.33</v>
+        <v>4.13</v>
       </c>
       <c r="D214">
         <v>227.0</v>
       </c>
       <c r="E214">
-        <v>11.35</v>
+        <v>4.54</v>
       </c>
       <c r="F214">
         <v>255.1</v>
       </c>
       <c r="G214">
-        <v>12.76</v>
+        <v>5.1</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -6065,19 +6065,19 @@
         <v>207.5</v>
       </c>
       <c r="C215">
-        <v>10.38</v>
+        <v>4.15</v>
       </c>
       <c r="D215">
         <v>227.2</v>
       </c>
       <c r="E215">
-        <v>11.36</v>
+        <v>4.54</v>
       </c>
       <c r="F215">
         <v>254.7</v>
       </c>
       <c r="G215">
-        <v>12.73</v>
+        <v>5.09</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -6093,19 +6093,19 @@
         <v>207.3</v>
       </c>
       <c r="C216">
-        <v>10.37</v>
+        <v>4.15</v>
       </c>
       <c r="D216">
         <v>227.6</v>
       </c>
       <c r="E216">
-        <v>11.38</v>
+        <v>4.55</v>
       </c>
       <c r="F216">
         <v>256.0</v>
       </c>
       <c r="G216">
-        <v>12.8</v>
+        <v>5.12</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -6121,19 +6121,19 @@
         <v>207.1</v>
       </c>
       <c r="C217">
-        <v>10.36</v>
+        <v>4.14</v>
       </c>
       <c r="D217">
         <v>228.2</v>
       </c>
       <c r="E217">
-        <v>11.41</v>
+        <v>4.56</v>
       </c>
       <c r="F217">
         <v>256.2</v>
       </c>
       <c r="G217">
-        <v>12.81</v>
+        <v>5.12</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -6149,19 +6149,19 @@
         <v>207.9</v>
       </c>
       <c r="C218">
-        <v>10.4</v>
+        <v>4.16</v>
       </c>
       <c r="D218">
         <v>227.6</v>
       </c>
       <c r="E218">
-        <v>11.38</v>
+        <v>4.55</v>
       </c>
       <c r="F218">
         <v>254.8</v>
       </c>
       <c r="G218">
-        <v>12.74</v>
+        <v>5.1</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -6177,19 +6177,19 @@
         <v>208.0</v>
       </c>
       <c r="C219">
-        <v>10.4</v>
+        <v>4.16</v>
       </c>
       <c r="D219">
         <v>226.8</v>
       </c>
       <c r="E219">
-        <v>11.34</v>
+        <v>4.54</v>
       </c>
       <c r="F219">
         <v>254.8</v>
       </c>
       <c r="G219">
-        <v>12.74</v>
+        <v>5.1</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -6205,19 +6205,19 @@
         <v>207.7</v>
       </c>
       <c r="C220">
-        <v>10.38</v>
+        <v>4.15</v>
       </c>
       <c r="D220">
         <v>228.7</v>
       </c>
       <c r="E220">
-        <v>11.44</v>
+        <v>4.57</v>
       </c>
       <c r="F220">
         <v>256.7</v>
       </c>
       <c r="G220">
-        <v>12.84</v>
+        <v>5.13</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -6233,19 +6233,19 @@
         <v>208.1</v>
       </c>
       <c r="C221">
-        <v>10.41</v>
+        <v>4.16</v>
       </c>
       <c r="D221">
         <v>228.4</v>
       </c>
       <c r="E221">
-        <v>11.42</v>
+        <v>4.57</v>
       </c>
       <c r="F221">
         <v>258.2</v>
       </c>
       <c r="G221">
-        <v>12.91</v>
+        <v>5.16</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -6261,19 +6261,19 @@
         <v>208.2</v>
       </c>
       <c r="C222">
-        <v>10.41</v>
+        <v>4.16</v>
       </c>
       <c r="D222">
         <v>228.3</v>
       </c>
       <c r="E222">
-        <v>11.42</v>
+        <v>4.57</v>
       </c>
       <c r="F222">
         <v>257.7</v>
       </c>
       <c r="G222">
-        <v>12.88</v>
+        <v>5.15</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -6289,19 +6289,19 @@
         <v>206.3</v>
       </c>
       <c r="C223">
-        <v>10.32</v>
+        <v>4.13</v>
       </c>
       <c r="D223">
         <v>230.0</v>
       </c>
       <c r="E223">
-        <v>11.5</v>
+        <v>4.6</v>
       </c>
       <c r="F223">
         <v>257.8</v>
       </c>
       <c r="G223">
-        <v>12.89</v>
+        <v>5.16</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -6317,19 +6317,19 @@
         <v>207.1</v>
       </c>
       <c r="C224">
-        <v>10.36</v>
+        <v>4.14</v>
       </c>
       <c r="D224">
         <v>229.8</v>
       </c>
       <c r="E224">
-        <v>11.49</v>
+        <v>4.6</v>
       </c>
       <c r="F224">
         <v>259.2</v>
       </c>
       <c r="G224">
-        <v>12.96</v>
+        <v>5.18</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -6345,19 +6345,19 @@
         <v>207.7</v>
       </c>
       <c r="C225">
-        <v>10.38</v>
+        <v>4.15</v>
       </c>
       <c r="D225">
         <v>229.9</v>
       </c>
       <c r="E225">
-        <v>11.5</v>
+        <v>4.6</v>
       </c>
       <c r="F225">
         <v>259.0</v>
       </c>
       <c r="G225">
-        <v>12.95</v>
+        <v>5.18</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -6373,19 +6373,19 @@
         <v>207.5</v>
       </c>
       <c r="C226">
-        <v>10.38</v>
+        <v>4.15</v>
       </c>
       <c r="D226">
         <v>231.6</v>
       </c>
       <c r="E226">
-        <v>11.58</v>
+        <v>4.63</v>
       </c>
       <c r="F226">
         <v>261.3</v>
       </c>
       <c r="G226">
-        <v>13.07</v>
+        <v>5.23</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -6401,19 +6401,19 @@
         <v>207.9</v>
       </c>
       <c r="C227">
-        <v>10.4</v>
+        <v>4.16</v>
       </c>
       <c r="D227">
         <v>232.2</v>
       </c>
       <c r="E227">
-        <v>11.61</v>
+        <v>4.64</v>
       </c>
       <c r="F227">
         <v>260.9</v>
       </c>
       <c r="G227">
-        <v>13.04</v>
+        <v>5.22</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -6429,19 +6429,19 @@
         <v>209.0</v>
       </c>
       <c r="C228">
-        <v>10.45</v>
+        <v>4.18</v>
       </c>
       <c r="D228">
         <v>233.7</v>
       </c>
       <c r="E228">
-        <v>11.69</v>
+        <v>4.67</v>
       </c>
       <c r="F228">
         <v>261.6</v>
       </c>
       <c r="G228">
-        <v>13.08</v>
+        <v>5.23</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -6457,19 +6457,19 @@
         <v>209.1</v>
       </c>
       <c r="C229">
-        <v>10.46</v>
+        <v>4.18</v>
       </c>
       <c r="D229">
         <v>235.7</v>
       </c>
       <c r="E229">
-        <v>11.79</v>
+        <v>4.71</v>
       </c>
       <c r="F229">
         <v>263.0</v>
       </c>
       <c r="G229">
-        <v>13.15</v>
+        <v>5.26</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -6485,19 +6485,19 @@
         <v>209.7</v>
       </c>
       <c r="C230">
-        <v>10.48</v>
+        <v>4.19</v>
       </c>
       <c r="D230">
         <v>234.9</v>
       </c>
       <c r="E230">
-        <v>11.75</v>
+        <v>4.7</v>
       </c>
       <c r="F230">
         <v>263.8</v>
       </c>
       <c r="G230">
-        <v>13.19</v>
+        <v>5.28</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -6513,19 +6513,19 @@
         <v>210.9</v>
       </c>
       <c r="C231">
-        <v>10.55</v>
+        <v>4.22</v>
       </c>
       <c r="D231">
         <v>235.8</v>
       </c>
       <c r="E231">
-        <v>11.79</v>
+        <v>4.72</v>
       </c>
       <c r="F231">
         <v>264.2</v>
       </c>
       <c r="G231">
-        <v>13.21</v>
+        <v>5.28</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -6541,19 +6541,19 @@
         <v>211.4</v>
       </c>
       <c r="C232">
-        <v>10.57</v>
+        <v>4.23</v>
       </c>
       <c r="D232">
         <v>236.9</v>
       </c>
       <c r="E232">
-        <v>11.85</v>
+        <v>4.74</v>
       </c>
       <c r="F232">
         <v>265.2</v>
       </c>
       <c r="G232">
-        <v>13.26</v>
+        <v>5.3</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -6569,19 +6569,19 @@
         <v>210.2</v>
       </c>
       <c r="C233">
-        <v>10.51</v>
+        <v>4.2</v>
       </c>
       <c r="D233">
         <v>237.0</v>
       </c>
       <c r="E233">
-        <v>11.85</v>
+        <v>4.74</v>
       </c>
       <c r="F233">
         <v>264.1</v>
       </c>
       <c r="G233">
-        <v>13.21</v>
+        <v>5.28</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -6597,19 +6597,19 @@
         <v>210.5</v>
       </c>
       <c r="C234">
-        <v>10.53</v>
+        <v>4.21</v>
       </c>
       <c r="D234">
         <v>235.5</v>
       </c>
       <c r="E234">
-        <v>11.78</v>
+        <v>4.71</v>
       </c>
       <c r="F234">
         <v>265.1</v>
       </c>
       <c r="G234">
-        <v>13.26</v>
+        <v>5.3</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -6625,19 +6625,19 @@
         <v>208.8</v>
       </c>
       <c r="C235">
-        <v>10.44</v>
+        <v>4.18</v>
       </c>
       <c r="D235">
         <v>234.4</v>
       </c>
       <c r="E235">
-        <v>11.72</v>
+        <v>4.69</v>
       </c>
       <c r="F235">
         <v>263.5</v>
       </c>
       <c r="G235">
-        <v>13.18</v>
+        <v>5.27</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -6653,19 +6653,19 @@
         <v>209.8</v>
       </c>
       <c r="C236">
-        <v>10.49</v>
+        <v>4.2</v>
       </c>
       <c r="D236">
         <v>234.6</v>
       </c>
       <c r="E236">
-        <v>11.73</v>
+        <v>4.69</v>
       </c>
       <c r="F236">
         <v>262.8</v>
       </c>
       <c r="G236">
-        <v>13.14</v>
+        <v>5.26</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -6681,19 +6681,19 @@
         <v>209.1</v>
       </c>
       <c r="C237">
-        <v>10.46</v>
+        <v>4.18</v>
       </c>
       <c r="D237">
         <v>233.8</v>
       </c>
       <c r="E237">
-        <v>11.69</v>
+        <v>4.68</v>
       </c>
       <c r="F237">
         <v>262.3</v>
       </c>
       <c r="G237">
-        <v>13.12</v>
+        <v>5.25</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -6709,19 +6709,19 @@
         <v>209.2</v>
       </c>
       <c r="C238">
-        <v>10.46</v>
+        <v>4.18</v>
       </c>
       <c r="D238">
         <v>232.9</v>
       </c>
       <c r="E238">
-        <v>11.65</v>
+        <v>4.66</v>
       </c>
       <c r="F238">
         <v>261.9</v>
       </c>
       <c r="G238">
-        <v>13.09</v>
+        <v>5.24</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -6737,19 +6737,19 @@
         <v>209.6</v>
       </c>
       <c r="C239">
-        <v>10.48</v>
+        <v>4.19</v>
       </c>
       <c r="D239">
         <v>231.5</v>
       </c>
       <c r="E239">
-        <v>11.58</v>
+        <v>4.63</v>
       </c>
       <c r="F239">
         <v>261.7</v>
       </c>
       <c r="G239">
-        <v>13.09</v>
+        <v>5.23</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -6765,19 +6765,19 @@
         <v>210.0</v>
       </c>
       <c r="C240">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="D240">
         <v>233.0</v>
       </c>
       <c r="E240">
-        <v>11.65</v>
+        <v>4.66</v>
       </c>
       <c r="F240">
         <v>260.9</v>
       </c>
       <c r="G240">
-        <v>13.04</v>
+        <v>5.22</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -6793,19 +6793,19 @@
         <v>208.9</v>
       </c>
       <c r="C241">
-        <v>10.45</v>
+        <v>4.18</v>
       </c>
       <c r="D241">
         <v>233.8</v>
       </c>
       <c r="E241">
-        <v>11.69</v>
+        <v>4.68</v>
       </c>
       <c r="F241">
         <v>261.9</v>
       </c>
       <c r="G241">
-        <v>13.09</v>
+        <v>5.24</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -6821,19 +6821,19 @@
         <v>210.5</v>
       </c>
       <c r="C242">
-        <v>10.53</v>
+        <v>4.21</v>
       </c>
       <c r="D242">
         <v>231.4</v>
       </c>
       <c r="E242">
-        <v>11.57</v>
+        <v>4.63</v>
       </c>
       <c r="F242">
         <v>259.0</v>
       </c>
       <c r="G242">
-        <v>12.95</v>
+        <v>5.18</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -6849,19 +6849,19 @@
         <v>208.8</v>
       </c>
       <c r="C243">
-        <v>10.44</v>
+        <v>4.18</v>
       </c>
       <c r="D243">
         <v>230.8</v>
       </c>
       <c r="E243">
-        <v>11.54</v>
+        <v>4.62</v>
       </c>
       <c r="F243">
         <v>259.3</v>
       </c>
       <c r="G243">
-        <v>12.97</v>
+        <v>5.19</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -6877,19 +6877,19 @@
         <v>208.6</v>
       </c>
       <c r="C244">
-        <v>10.43</v>
+        <v>4.17</v>
       </c>
       <c r="D244">
         <v>230.6</v>
       </c>
       <c r="E244">
-        <v>11.53</v>
+        <v>4.61</v>
       </c>
       <c r="F244">
         <v>257.8</v>
       </c>
       <c r="G244">
-        <v>12.89</v>
+        <v>5.16</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -6905,19 +6905,19 @@
         <v>209.7</v>
       </c>
       <c r="C245">
-        <v>10.48</v>
+        <v>4.19</v>
       </c>
       <c r="D245">
         <v>230.1</v>
       </c>
       <c r="E245">
-        <v>11.51</v>
+        <v>4.6</v>
       </c>
       <c r="F245">
         <v>256.5</v>
       </c>
       <c r="G245">
-        <v>12.83</v>
+        <v>5.13</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -6933,19 +6933,19 @@
         <v>208.9</v>
       </c>
       <c r="C246">
-        <v>10.45</v>
+        <v>4.18</v>
       </c>
       <c r="D246">
         <v>231.2</v>
       </c>
       <c r="E246">
-        <v>11.56</v>
+        <v>4.62</v>
       </c>
       <c r="F246">
         <v>256.2</v>
       </c>
       <c r="G246">
-        <v>12.81</v>
+        <v>5.12</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -6961,19 +6961,19 @@
         <v>207.7</v>
       </c>
       <c r="C247">
-        <v>10.38</v>
+        <v>4.15</v>
       </c>
       <c r="D247">
         <v>229.8</v>
       </c>
       <c r="E247">
-        <v>11.49</v>
+        <v>4.6</v>
       </c>
       <c r="F247">
         <v>256.6</v>
       </c>
       <c r="G247">
-        <v>12.83</v>
+        <v>5.13</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -6989,19 +6989,19 @@
         <v>209.3</v>
       </c>
       <c r="C248">
-        <v>10.47</v>
+        <v>4.19</v>
       </c>
       <c r="D248">
         <v>229.9</v>
       </c>
       <c r="E248">
-        <v>11.5</v>
+        <v>4.6</v>
       </c>
       <c r="F248">
         <v>256.7</v>
       </c>
       <c r="G248">
-        <v>12.84</v>
+        <v>5.13</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -7017,19 +7017,19 @@
         <v>209.8</v>
       </c>
       <c r="C249">
-        <v>10.49</v>
+        <v>4.2</v>
       </c>
       <c r="D249">
         <v>230.3</v>
       </c>
       <c r="E249">
-        <v>11.52</v>
+        <v>4.61</v>
       </c>
       <c r="F249">
         <v>256.4</v>
       </c>
       <c r="G249">
-        <v>12.82</v>
+        <v>5.13</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -7045,19 +7045,19 @@
         <v>207.6</v>
       </c>
       <c r="C250">
-        <v>10.38</v>
+        <v>4.15</v>
       </c>
       <c r="D250">
         <v>230.8</v>
       </c>
       <c r="E250">
-        <v>11.54</v>
+        <v>4.62</v>
       </c>
       <c r="F250">
         <v>254.6</v>
       </c>
       <c r="G250">
-        <v>12.73</v>
+        <v>5.09</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -7073,19 +7073,19 @@
         <v>209.1</v>
       </c>
       <c r="C251">
-        <v>10.46</v>
+        <v>4.18</v>
       </c>
       <c r="D251">
         <v>230.0</v>
       </c>
       <c r="E251">
-        <v>11.5</v>
+        <v>4.6</v>
       </c>
       <c r="F251">
         <v>256.4</v>
       </c>
       <c r="G251">
-        <v>12.82</v>
+        <v>5.13</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -7101,19 +7101,19 @@
         <v>208.2</v>
       </c>
       <c r="C252">
-        <v>10.41</v>
+        <v>4.16</v>
       </c>
       <c r="D252">
         <v>231.1</v>
       </c>
       <c r="E252">
-        <v>11.55</v>
+        <v>4.62</v>
       </c>
       <c r="F252">
         <v>256.4</v>
       </c>
       <c r="G252">
-        <v>12.82</v>
+        <v>5.13</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -7129,19 +7129,19 @@
         <v>207.6</v>
       </c>
       <c r="C253">
-        <v>10.38</v>
+        <v>4.15</v>
       </c>
       <c r="D253">
         <v>230.3</v>
       </c>
       <c r="E253">
-        <v>11.52</v>
+        <v>4.61</v>
       </c>
       <c r="F253">
         <v>255.9</v>
       </c>
       <c r="G253">
-        <v>12.8</v>
+        <v>5.12</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -7157,19 +7157,19 @@
         <v>208.5</v>
       </c>
       <c r="C254">
-        <v>10.43</v>
+        <v>4.17</v>
       </c>
       <c r="D254">
         <v>230.8</v>
       </c>
       <c r="E254">
-        <v>11.54</v>
+        <v>4.62</v>
       </c>
       <c r="F254">
         <v>257.5</v>
       </c>
       <c r="G254">
-        <v>12.88</v>
+        <v>5.15</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -7185,19 +7185,19 @@
         <v>208.8</v>
       </c>
       <c r="C255">
-        <v>10.44</v>
+        <v>4.18</v>
       </c>
       <c r="D255">
         <v>231.8</v>
       </c>
       <c r="E255">
-        <v>11.59</v>
+        <v>4.64</v>
       </c>
       <c r="F255">
         <v>257.7</v>
       </c>
       <c r="G255">
-        <v>12.88</v>
+        <v>5.15</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -7213,19 +7213,19 @@
         <v>208.6</v>
       </c>
       <c r="C256">
-        <v>10.43</v>
+        <v>4.17</v>
       </c>
       <c r="D256">
         <v>232.4</v>
       </c>
       <c r="E256">
-        <v>11.62</v>
+        <v>4.65</v>
       </c>
       <c r="F256">
         <v>258.2</v>
       </c>
       <c r="G256">
-        <v>12.91</v>
+        <v>5.16</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -7241,19 +7241,19 @@
         <v>209.8</v>
       </c>
       <c r="C257">
-        <v>10.49</v>
+        <v>4.2</v>
       </c>
       <c r="D257">
         <v>234.5</v>
       </c>
       <c r="E257">
-        <v>11.73</v>
+        <v>4.69</v>
       </c>
       <c r="F257">
         <v>260.6</v>
       </c>
       <c r="G257">
-        <v>13.03</v>
+        <v>5.21</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -7269,19 +7269,19 @@
         <v>209.7</v>
       </c>
       <c r="C258">
-        <v>10.48</v>
+        <v>4.19</v>
       </c>
       <c r="D258">
         <v>234.9</v>
       </c>
       <c r="E258">
-        <v>11.75</v>
+        <v>4.7</v>
       </c>
       <c r="F258">
         <v>259.6</v>
       </c>
       <c r="G258">
-        <v>12.98</v>
+        <v>5.19</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -7297,19 +7297,19 @@
         <v>207.7</v>
       </c>
       <c r="C259">
-        <v>10.38</v>
+        <v>4.15</v>
       </c>
       <c r="D259">
         <v>235.3</v>
       </c>
       <c r="E259">
-        <v>11.77</v>
+        <v>4.71</v>
       </c>
       <c r="F259">
         <v>260.4</v>
       </c>
       <c r="G259">
-        <v>13.02</v>
+        <v>5.21</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -7325,19 +7325,19 @@
         <v>207.7</v>
       </c>
       <c r="C260">
-        <v>10.38</v>
+        <v>4.15</v>
       </c>
       <c r="D260">
         <v>233.8</v>
       </c>
       <c r="E260">
-        <v>11.69</v>
+        <v>4.68</v>
       </c>
       <c r="F260">
         <v>261.8</v>
       </c>
       <c r="G260">
-        <v>13.09</v>
+        <v>5.24</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -7353,19 +7353,19 @@
         <v>215.9</v>
       </c>
       <c r="C261">
-        <v>10.8</v>
+        <v>4.32</v>
       </c>
       <c r="D261">
         <v>240.0</v>
       </c>
       <c r="E261">
-        <v>12.0</v>
+        <v>4.8</v>
       </c>
       <c r="F261">
         <v>262.9</v>
       </c>
       <c r="G261">
-        <v>13.14</v>
+        <v>5.26</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -7381,19 +7381,19 @@
         <v>222.8</v>
       </c>
       <c r="C262">
-        <v>11.14</v>
+        <v>4.46</v>
       </c>
       <c r="D262">
         <v>243.9</v>
       </c>
       <c r="E262">
-        <v>12.2</v>
+        <v>4.88</v>
       </c>
       <c r="F262">
         <v>265.6</v>
       </c>
       <c r="G262">
-        <v>13.28</v>
+        <v>5.31</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -7409,19 +7409,19 @@
         <v>230.1</v>
       </c>
       <c r="C263">
-        <v>11.51</v>
+        <v>4.6</v>
       </c>
       <c r="D263">
         <v>249.9</v>
       </c>
       <c r="E263">
-        <v>12.5</v>
+        <v>5.0</v>
       </c>
       <c r="F263">
         <v>266.2</v>
       </c>
       <c r="G263">
-        <v>13.31</v>
+        <v>5.32</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -7437,19 +7437,19 @@
         <v>237.7</v>
       </c>
       <c r="C264">
-        <v>11.88</v>
+        <v>4.75</v>
       </c>
       <c r="D264">
         <v>254.3</v>
       </c>
       <c r="E264">
-        <v>12.72</v>
+        <v>5.09</v>
       </c>
       <c r="F264">
         <v>268.9</v>
       </c>
       <c r="G264">
-        <v>13.45</v>
+        <v>5.38</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -7465,19 +7465,19 @@
         <v>239.2</v>
       </c>
       <c r="C265">
-        <v>11.96</v>
+        <v>4.78</v>
       </c>
       <c r="D265">
         <v>255.6</v>
       </c>
       <c r="E265">
-        <v>12.78</v>
+        <v>5.11</v>
       </c>
       <c r="F265">
         <v>269.5</v>
       </c>
       <c r="G265">
-        <v>13.48</v>
+        <v>5.39</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -7493,19 +7493,19 @@
         <v>240.6</v>
       </c>
       <c r="C266">
-        <v>12.03</v>
+        <v>4.81</v>
       </c>
       <c r="D266">
         <v>257.0</v>
       </c>
       <c r="E266">
-        <v>12.85</v>
+        <v>5.14</v>
       </c>
       <c r="F266">
         <v>271.4</v>
       </c>
       <c r="G266">
-        <v>13.57</v>
+        <v>5.43</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -7521,19 +7521,19 @@
         <v>243.1</v>
       </c>
       <c r="C267">
-        <v>12.16</v>
+        <v>4.86</v>
       </c>
       <c r="D267">
         <v>261.2</v>
       </c>
       <c r="E267">
-        <v>13.06</v>
+        <v>5.22</v>
       </c>
       <c r="F267">
         <v>271.0</v>
       </c>
       <c r="G267">
-        <v>13.55</v>
+        <v>5.42</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -7549,19 +7549,19 @@
         <v>241.1</v>
       </c>
       <c r="C268">
-        <v>12.05</v>
+        <v>4.82</v>
       </c>
       <c r="D268">
         <v>258.7</v>
       </c>
       <c r="E268">
-        <v>12.94</v>
+        <v>5.17</v>
       </c>
       <c r="F268">
         <v>268.0</v>
       </c>
       <c r="G268">
-        <v>13.4</v>
+        <v>5.36</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -7577,19 +7577,19 @@
         <v>240.8</v>
       </c>
       <c r="C269">
-        <v>12.04</v>
+        <v>4.82</v>
       </c>
       <c r="D269">
         <v>256.5</v>
       </c>
       <c r="E269">
-        <v>12.83</v>
+        <v>5.13</v>
       </c>
       <c r="F269">
         <v>266.5</v>
       </c>
       <c r="G269">
-        <v>13.33</v>
+        <v>5.33</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -7605,19 +7605,19 @@
         <v>239.3</v>
       </c>
       <c r="C270">
-        <v>11.97</v>
+        <v>4.79</v>
       </c>
       <c r="D270">
         <v>255.0</v>
       </c>
       <c r="E270">
-        <v>12.75</v>
+        <v>5.1</v>
       </c>
       <c r="F270">
         <v>263.6</v>
       </c>
       <c r="G270">
-        <v>13.18</v>
+        <v>5.27</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -7633,19 +7633,19 @@
         <v>240.2</v>
       </c>
       <c r="C271">
-        <v>12.01</v>
+        <v>4.8</v>
       </c>
       <c r="D271">
         <v>252.4</v>
       </c>
       <c r="E271">
-        <v>12.62</v>
+        <v>5.05</v>
       </c>
       <c r="F271">
         <v>262.9</v>
       </c>
       <c r="G271">
-        <v>13.14</v>
+        <v>5.26</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -7661,19 +7661,19 @@
         <v>238.9</v>
       </c>
       <c r="C272">
-        <v>11.95</v>
+        <v>4.78</v>
       </c>
       <c r="D272">
         <v>251.2</v>
       </c>
       <c r="E272">
-        <v>12.56</v>
+        <v>5.02</v>
       </c>
       <c r="F272">
         <v>259.0</v>
       </c>
       <c r="G272">
-        <v>12.95</v>
+        <v>5.18</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -7689,19 +7689,19 @@
         <v>238.3</v>
       </c>
       <c r="C273">
-        <v>11.92</v>
+        <v>4.77</v>
       </c>
       <c r="D273">
         <v>249.7</v>
       </c>
       <c r="E273">
-        <v>12.48</v>
+        <v>4.99</v>
       </c>
       <c r="F273">
         <v>258.0</v>
       </c>
       <c r="G273">
-        <v>12.9</v>
+        <v>5.16</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -7717,19 +7717,19 @@
         <v>239.5</v>
       </c>
       <c r="C274">
-        <v>11.98</v>
+        <v>4.79</v>
       </c>
       <c r="D274">
         <v>247.1</v>
       </c>
       <c r="E274">
-        <v>12.36</v>
+        <v>4.94</v>
       </c>
       <c r="F274">
         <v>256.7</v>
       </c>
       <c r="G274">
-        <v>12.84</v>
+        <v>5.13</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -7745,19 +7745,19 @@
         <v>239.0</v>
       </c>
       <c r="C275">
-        <v>11.95</v>
+        <v>4.78</v>
       </c>
       <c r="D275">
         <v>245.1</v>
       </c>
       <c r="E275">
-        <v>12.26</v>
+        <v>4.9</v>
       </c>
       <c r="F275">
         <v>254.9</v>
       </c>
       <c r="G275">
-        <v>12.75</v>
+        <v>5.1</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -7773,19 +7773,19 @@
         <v>237.8</v>
       </c>
       <c r="C276">
-        <v>11.89</v>
+        <v>4.76</v>
       </c>
       <c r="D276">
         <v>243.7</v>
       </c>
       <c r="E276">
-        <v>12.19</v>
+        <v>4.87</v>
       </c>
       <c r="F276">
         <v>252.4</v>
       </c>
       <c r="G276">
-        <v>12.62</v>
+        <v>5.05</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -7801,19 +7801,19 @@
         <v>238.6</v>
       </c>
       <c r="C277">
-        <v>11.93</v>
+        <v>4.77</v>
       </c>
       <c r="D277">
         <v>242.0</v>
       </c>
       <c r="E277">
-        <v>12.1</v>
+        <v>4.84</v>
       </c>
       <c r="F277">
         <v>250.3</v>
       </c>
       <c r="G277">
-        <v>12.52</v>
+        <v>5.01</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -7829,19 +7829,19 @@
         <v>236.7</v>
       </c>
       <c r="C278">
-        <v>11.84</v>
+        <v>4.73</v>
       </c>
       <c r="D278">
         <v>240.3</v>
       </c>
       <c r="E278">
-        <v>12.02</v>
+        <v>4.81</v>
       </c>
       <c r="F278">
         <v>248.2</v>
       </c>
       <c r="G278">
-        <v>12.41</v>
+        <v>4.96</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -7857,19 +7857,19 @@
         <v>238.0</v>
       </c>
       <c r="C279">
-        <v>11.9</v>
+        <v>4.76</v>
       </c>
       <c r="D279">
         <v>240.1</v>
       </c>
       <c r="E279">
-        <v>12.01</v>
+        <v>4.8</v>
       </c>
       <c r="F279">
         <v>246.7</v>
       </c>
       <c r="G279">
-        <v>12.34</v>
+        <v>4.93</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -7885,19 +7885,19 @@
         <v>235.9</v>
       </c>
       <c r="C280">
-        <v>11.8</v>
+        <v>4.72</v>
       </c>
       <c r="D280">
         <v>238.5</v>
       </c>
       <c r="E280">
-        <v>11.93</v>
+        <v>4.77</v>
       </c>
       <c r="F280">
         <v>244.3</v>
       </c>
       <c r="G280">
-        <v>12.22</v>
+        <v>4.89</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -7913,19 +7913,19 @@
         <v>234.8</v>
       </c>
       <c r="C281">
-        <v>11.74</v>
+        <v>4.7</v>
       </c>
       <c r="D281">
         <v>237.5</v>
       </c>
       <c r="E281">
-        <v>11.88</v>
+        <v>4.75</v>
       </c>
       <c r="F281">
         <v>243.2</v>
       </c>
       <c r="G281">
-        <v>12.16</v>
+        <v>4.86</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -7941,19 +7941,19 @@
         <v>232.9</v>
       </c>
       <c r="C282">
-        <v>11.65</v>
+        <v>4.66</v>
       </c>
       <c r="D282">
         <v>235.1</v>
       </c>
       <c r="E282">
-        <v>11.76</v>
+        <v>4.7</v>
       </c>
       <c r="F282">
         <v>240.2</v>
       </c>
       <c r="G282">
-        <v>12.01</v>
+        <v>4.8</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -7969,19 +7969,19 @@
         <v>231.0</v>
       </c>
       <c r="C283">
-        <v>11.55</v>
+        <v>4.62</v>
       </c>
       <c r="D283">
         <v>232.7</v>
       </c>
       <c r="E283">
-        <v>11.63</v>
+        <v>4.65</v>
       </c>
       <c r="F283">
         <v>239.4</v>
       </c>
       <c r="G283">
-        <v>11.97</v>
+        <v>4.79</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -7997,19 +7997,19 @@
         <v>228.0</v>
       </c>
       <c r="C284">
-        <v>11.4</v>
+        <v>4.56</v>
       </c>
       <c r="D284">
         <v>233.4</v>
       </c>
       <c r="E284">
-        <v>11.67</v>
+        <v>4.67</v>
       </c>
       <c r="F284">
         <v>236.2</v>
       </c>
       <c r="G284">
-        <v>11.81</v>
+        <v>4.72</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -8025,19 +8025,19 @@
         <v>228.3</v>
       </c>
       <c r="C285">
-        <v>11.42</v>
+        <v>4.57</v>
       </c>
       <c r="D285">
         <v>231.7</v>
       </c>
       <c r="E285">
-        <v>11.59</v>
+        <v>4.63</v>
       </c>
       <c r="F285">
         <v>237.1</v>
       </c>
       <c r="G285">
-        <v>11.86</v>
+        <v>4.74</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -8053,19 +8053,19 @@
         <v>225.8</v>
       </c>
       <c r="C286">
-        <v>11.29</v>
+        <v>4.52</v>
       </c>
       <c r="D286">
         <v>229.5</v>
       </c>
       <c r="E286">
-        <v>11.48</v>
+        <v>4.59</v>
       </c>
       <c r="F286">
         <v>234.0</v>
       </c>
       <c r="G286">
-        <v>11.7</v>
+        <v>4.68</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -8081,19 +8081,19 @@
         <v>225.6</v>
       </c>
       <c r="C287">
-        <v>11.28</v>
+        <v>4.51</v>
       </c>
       <c r="D287">
         <v>230.3</v>
       </c>
       <c r="E287">
-        <v>11.52</v>
+        <v>4.61</v>
       </c>
       <c r="F287">
         <v>232.6</v>
       </c>
       <c r="G287">
-        <v>11.63</v>
+        <v>4.65</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -8109,19 +8109,19 @@
         <v>224.6</v>
       </c>
       <c r="C288">
-        <v>11.23</v>
+        <v>4.49</v>
       </c>
       <c r="D288">
         <v>229.1</v>
       </c>
       <c r="E288">
-        <v>11.46</v>
+        <v>4.58</v>
       </c>
       <c r="F288">
         <v>228.7</v>
       </c>
       <c r="G288">
-        <v>11.44</v>
+        <v>4.57</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -8137,19 +8137,19 @@
         <v>221.9</v>
       </c>
       <c r="C289">
-        <v>11.1</v>
+        <v>4.44</v>
       </c>
       <c r="D289">
         <v>226.6</v>
       </c>
       <c r="E289">
-        <v>11.33</v>
+        <v>4.53</v>
       </c>
       <c r="F289">
         <v>227.6</v>
       </c>
       <c r="G289">
-        <v>11.38</v>
+        <v>4.55</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -8165,19 +8165,19 @@
         <v>223.0</v>
       </c>
       <c r="C290">
-        <v>11.15</v>
+        <v>4.46</v>
       </c>
       <c r="D290">
         <v>228.0</v>
       </c>
       <c r="E290">
-        <v>11.4</v>
+        <v>4.56</v>
       </c>
       <c r="F290">
         <v>225.8</v>
       </c>
       <c r="G290">
-        <v>11.29</v>
+        <v>4.52</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -8193,19 +8193,19 @@
         <v>221.0</v>
       </c>
       <c r="C291">
-        <v>11.05</v>
+        <v>4.42</v>
       </c>
       <c r="D291">
         <v>225.6</v>
       </c>
       <c r="E291">
-        <v>11.28</v>
+        <v>4.51</v>
       </c>
       <c r="F291">
         <v>225.2</v>
       </c>
       <c r="G291">
-        <v>11.26</v>
+        <v>4.5</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -8221,19 +8221,19 @@
         <v>220.8</v>
       </c>
       <c r="C292">
-        <v>11.04</v>
+        <v>4.42</v>
       </c>
       <c r="D292">
         <v>224.8</v>
       </c>
       <c r="E292">
-        <v>11.24</v>
+        <v>4.5</v>
       </c>
       <c r="F292">
         <v>223.3</v>
       </c>
       <c r="G292">
-        <v>11.17</v>
+        <v>4.47</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -8249,19 +8249,19 @@
         <v>220.4</v>
       </c>
       <c r="C293">
-        <v>11.02</v>
+        <v>4.41</v>
       </c>
       <c r="D293">
         <v>223.4</v>
       </c>
       <c r="E293">
-        <v>11.17</v>
+        <v>4.47</v>
       </c>
       <c r="F293">
         <v>221.7</v>
       </c>
       <c r="G293">
-        <v>11.09</v>
+        <v>4.43</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -8277,19 +8277,19 @@
         <v>219.2</v>
       </c>
       <c r="C294">
-        <v>10.96</v>
+        <v>4.38</v>
       </c>
       <c r="D294">
         <v>223.0</v>
       </c>
       <c r="E294">
-        <v>11.15</v>
+        <v>4.46</v>
       </c>
       <c r="F294">
         <v>220.3</v>
       </c>
       <c r="G294">
-        <v>11.02</v>
+        <v>4.41</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -8305,19 +8305,19 @@
         <v>220.5</v>
       </c>
       <c r="C295">
-        <v>11.03</v>
+        <v>4.41</v>
       </c>
       <c r="D295">
         <v>221.8</v>
       </c>
       <c r="E295">
-        <v>11.09</v>
+        <v>4.44</v>
       </c>
       <c r="F295">
         <v>219.8</v>
       </c>
       <c r="G295">
-        <v>10.99</v>
+        <v>4.4</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -8333,19 +8333,19 @@
         <v>218.7</v>
       </c>
       <c r="C296">
-        <v>10.94</v>
+        <v>4.37</v>
       </c>
       <c r="D296">
         <v>219.8</v>
       </c>
       <c r="E296">
-        <v>10.99</v>
+        <v>4.4</v>
       </c>
       <c r="F296">
         <v>219.1</v>
       </c>
       <c r="G296">
-        <v>10.96</v>
+        <v>4.38</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -8361,19 +8361,19 @@
         <v>215.5</v>
       </c>
       <c r="C297">
-        <v>10.78</v>
+        <v>4.31</v>
       </c>
       <c r="D297">
         <v>218.4</v>
       </c>
       <c r="E297">
-        <v>10.92</v>
+        <v>4.37</v>
       </c>
       <c r="F297">
         <v>219.6</v>
       </c>
       <c r="G297">
-        <v>10.98</v>
+        <v>4.39</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -8389,19 +8389,19 @@
         <v>215.7</v>
       </c>
       <c r="C298">
-        <v>10.79</v>
+        <v>4.31</v>
       </c>
       <c r="D298">
         <v>218.0</v>
       </c>
       <c r="E298">
-        <v>10.9</v>
+        <v>4.36</v>
       </c>
       <c r="F298">
         <v>218.4</v>
       </c>
       <c r="G298">
-        <v>10.92</v>
+        <v>4.37</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -8417,19 +8417,19 @@
         <v>216.8</v>
       </c>
       <c r="C299">
-        <v>10.84</v>
+        <v>4.34</v>
       </c>
       <c r="D299">
         <v>216.9</v>
       </c>
       <c r="E299">
-        <v>10.85</v>
+        <v>4.34</v>
       </c>
       <c r="F299">
         <v>219.1</v>
       </c>
       <c r="G299">
-        <v>10.96</v>
+        <v>4.38</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -8445,19 +8445,19 @@
         <v>215.0</v>
       </c>
       <c r="C300">
-        <v>10.75</v>
+        <v>4.3</v>
       </c>
       <c r="D300">
         <v>215.2</v>
       </c>
       <c r="E300">
-        <v>10.76</v>
+        <v>4.3</v>
       </c>
       <c r="F300">
         <v>218.4</v>
       </c>
       <c r="G300">
-        <v>10.92</v>
+        <v>4.37</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -8473,19 +8473,19 @@
         <v>215.8</v>
       </c>
       <c r="C301">
-        <v>10.79</v>
+        <v>4.32</v>
       </c>
       <c r="D301">
         <v>213.2</v>
       </c>
       <c r="E301">
-        <v>10.66</v>
+        <v>4.26</v>
       </c>
       <c r="F301">
         <v>217.7</v>
       </c>
       <c r="G301">
-        <v>10.88</v>
+        <v>4.35</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
@@ -8501,19 +8501,19 @@
         <v>214.1</v>
       </c>
       <c r="C302">
-        <v>10.71</v>
+        <v>4.28</v>
       </c>
       <c r="D302">
         <v>213.4</v>
       </c>
       <c r="E302">
-        <v>10.67</v>
+        <v>4.27</v>
       </c>
       <c r="F302">
         <v>215.8</v>
       </c>
       <c r="G302">
-        <v>10.79</v>
+        <v>4.32</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
@@ -8529,19 +8529,19 @@
         <v>214.4</v>
       </c>
       <c r="C303">
-        <v>10.72</v>
+        <v>4.29</v>
       </c>
       <c r="D303">
         <v>213.7</v>
       </c>
       <c r="E303">
-        <v>10.69</v>
+        <v>4.27</v>
       </c>
       <c r="F303">
         <v>216.1</v>
       </c>
       <c r="G303">
-        <v>10.8</v>
+        <v>4.32</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
@@ -8557,19 +8557,19 @@
         <v>214.9</v>
       </c>
       <c r="C304">
-        <v>10.75</v>
+        <v>4.3</v>
       </c>
       <c r="D304">
         <v>216.1</v>
       </c>
       <c r="E304">
-        <v>10.8</v>
+        <v>4.32</v>
       </c>
       <c r="F304">
         <v>217.0</v>
       </c>
       <c r="G304">
-        <v>10.85</v>
+        <v>4.34</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
@@ -8585,19 +8585,19 @@
         <v>216.1</v>
       </c>
       <c r="C305">
-        <v>10.8</v>
+        <v>4.32</v>
       </c>
       <c r="D305">
         <v>212.7</v>
       </c>
       <c r="E305">
-        <v>10.63</v>
+        <v>4.25</v>
       </c>
       <c r="F305">
         <v>217.9</v>
       </c>
       <c r="G305">
-        <v>10.9</v>
+        <v>4.36</v>
       </c>
       <c r="H305" t="inlineStr">
         <is>
@@ -8613,19 +8613,19 @@
         <v>214.4</v>
       </c>
       <c r="C306">
-        <v>10.72</v>
+        <v>4.29</v>
       </c>
       <c r="D306">
         <v>211.4</v>
       </c>
       <c r="E306">
-        <v>10.57</v>
+        <v>4.23</v>
       </c>
       <c r="F306">
         <v>217.6</v>
       </c>
       <c r="G306">
-        <v>10.88</v>
+        <v>4.35</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
@@ -8641,19 +8641,19 @@
         <v>216.7</v>
       </c>
       <c r="C307">
-        <v>10.84</v>
+        <v>4.33</v>
       </c>
       <c r="D307">
         <v>213.4</v>
       </c>
       <c r="E307">
-        <v>10.67</v>
+        <v>4.27</v>
       </c>
       <c r="F307">
         <v>217.5</v>
       </c>
       <c r="G307">
-        <v>10.88</v>
+        <v>4.35</v>
       </c>
       <c r="H307" t="inlineStr">
         <is>
@@ -8669,19 +8669,19 @@
         <v>217.0</v>
       </c>
       <c r="C308">
-        <v>10.85</v>
+        <v>4.34</v>
       </c>
       <c r="D308">
         <v>212.8</v>
       </c>
       <c r="E308">
-        <v>10.64</v>
+        <v>4.26</v>
       </c>
       <c r="F308">
         <v>217.6</v>
       </c>
       <c r="G308">
-        <v>10.88</v>
+        <v>4.35</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
@@ -8697,19 +8697,19 @@
         <v>215.6</v>
       </c>
       <c r="C309">
-        <v>10.78</v>
+        <v>4.31</v>
       </c>
       <c r="D309">
         <v>211.8</v>
       </c>
       <c r="E309">
-        <v>10.59</v>
+        <v>4.24</v>
       </c>
       <c r="F309">
         <v>215.8</v>
       </c>
       <c r="G309">
-        <v>10.79</v>
+        <v>4.32</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
@@ -8725,19 +8725,19 @@
         <v>216.3</v>
       </c>
       <c r="C310">
-        <v>10.82</v>
+        <v>4.33</v>
       </c>
       <c r="D310">
         <v>213.1</v>
       </c>
       <c r="E310">
-        <v>10.66</v>
+        <v>4.26</v>
       </c>
       <c r="F310">
         <v>215.9</v>
       </c>
       <c r="G310">
-        <v>10.8</v>
+        <v>4.32</v>
       </c>
       <c r="H310" t="inlineStr">
         <is>
@@ -8753,19 +8753,19 @@
         <v>215.4</v>
       </c>
       <c r="C311">
-        <v>10.77</v>
+        <v>4.31</v>
       </c>
       <c r="D311">
         <v>213.0</v>
       </c>
       <c r="E311">
-        <v>10.65</v>
+        <v>4.26</v>
       </c>
       <c r="F311">
         <v>215.3</v>
       </c>
       <c r="G311">
-        <v>10.77</v>
+        <v>4.31</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
@@ -8781,19 +8781,19 @@
         <v>214.4</v>
       </c>
       <c r="C312">
-        <v>10.72</v>
+        <v>4.29</v>
       </c>
       <c r="D312">
         <v>213.4</v>
       </c>
       <c r="E312">
-        <v>10.67</v>
+        <v>4.27</v>
       </c>
       <c r="F312">
         <v>215.9</v>
       </c>
       <c r="G312">
-        <v>10.8</v>
+        <v>4.32</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
@@ -8809,19 +8809,19 @@
         <v>215.1</v>
       </c>
       <c r="C313">
-        <v>10.76</v>
+        <v>4.3</v>
       </c>
       <c r="D313">
         <v>213.7</v>
       </c>
       <c r="E313">
-        <v>10.69</v>
+        <v>4.27</v>
       </c>
       <c r="F313">
         <v>216.2</v>
       </c>
       <c r="G313">
-        <v>10.81</v>
+        <v>4.32</v>
       </c>
       <c r="H313" t="inlineStr">
         <is>
@@ -8837,19 +8837,19 @@
         <v>217.8</v>
       </c>
       <c r="C314">
-        <v>10.89</v>
+        <v>4.36</v>
       </c>
       <c r="D314">
         <v>213.6</v>
       </c>
       <c r="E314">
-        <v>10.68</v>
+        <v>4.27</v>
       </c>
       <c r="F314">
         <v>214.4</v>
       </c>
       <c r="G314">
-        <v>10.72</v>
+        <v>4.29</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
@@ -8865,19 +8865,19 @@
         <v>216.3</v>
       </c>
       <c r="C315">
-        <v>10.82</v>
+        <v>4.33</v>
       </c>
       <c r="D315">
         <v>214.8</v>
       </c>
       <c r="E315">
-        <v>10.74</v>
+        <v>4.3</v>
       </c>
       <c r="F315">
         <v>214.6</v>
       </c>
       <c r="G315">
-        <v>10.73</v>
+        <v>4.29</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
@@ -8893,19 +8893,19 @@
         <v>215.6</v>
       </c>
       <c r="C316">
-        <v>10.78</v>
+        <v>4.31</v>
       </c>
       <c r="D316">
         <v>213.7</v>
       </c>
       <c r="E316">
-        <v>10.69</v>
+        <v>4.27</v>
       </c>
       <c r="F316">
         <v>215.7</v>
       </c>
       <c r="G316">
-        <v>10.79</v>
+        <v>4.31</v>
       </c>
       <c r="H316" t="inlineStr">
         <is>
@@ -8921,19 +8921,19 @@
         <v>216.2</v>
       </c>
       <c r="C317">
-        <v>10.81</v>
+        <v>4.32</v>
       </c>
       <c r="D317">
         <v>216.0</v>
       </c>
       <c r="E317">
-        <v>10.8</v>
+        <v>4.32</v>
       </c>
       <c r="F317">
         <v>216.2</v>
       </c>
       <c r="G317">
-        <v>10.81</v>
+        <v>4.32</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
@@ -8949,19 +8949,19 @@
         <v>217.2</v>
       </c>
       <c r="C318">
-        <v>10.86</v>
+        <v>4.34</v>
       </c>
       <c r="D318">
         <v>215.2</v>
       </c>
       <c r="E318">
-        <v>10.76</v>
+        <v>4.3</v>
       </c>
       <c r="F318">
         <v>215.1</v>
       </c>
       <c r="G318">
-        <v>10.76</v>
+        <v>4.3</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
@@ -8977,19 +8977,19 @@
         <v>215.9</v>
       </c>
       <c r="C319">
-        <v>10.8</v>
+        <v>4.32</v>
       </c>
       <c r="D319">
         <v>214.0</v>
       </c>
       <c r="E319">
-        <v>10.7</v>
+        <v>4.28</v>
       </c>
       <c r="F319">
         <v>217.2</v>
       </c>
       <c r="G319">
-        <v>10.86</v>
+        <v>4.34</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
@@ -9005,19 +9005,19 @@
         <v>217.0</v>
       </c>
       <c r="C320">
-        <v>10.85</v>
+        <v>4.34</v>
       </c>
       <c r="D320">
         <v>215.0</v>
       </c>
       <c r="E320">
-        <v>10.75</v>
+        <v>4.3</v>
       </c>
       <c r="F320">
         <v>217.2</v>
       </c>
       <c r="G320">
-        <v>10.86</v>
+        <v>4.34</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
@@ -9033,19 +9033,19 @@
         <v>216.6</v>
       </c>
       <c r="C321">
-        <v>10.83</v>
+        <v>4.33</v>
       </c>
       <c r="D321">
         <v>216.6</v>
       </c>
       <c r="E321">
-        <v>10.83</v>
+        <v>4.33</v>
       </c>
       <c r="F321">
         <v>217.5</v>
       </c>
       <c r="G321">
-        <v>10.88</v>
+        <v>4.35</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
@@ -9061,19 +9061,19 @@
         <v>217.5</v>
       </c>
       <c r="C322">
-        <v>10.88</v>
+        <v>4.35</v>
       </c>
       <c r="D322">
         <v>216.2</v>
       </c>
       <c r="E322">
-        <v>10.81</v>
+        <v>4.32</v>
       </c>
       <c r="F322">
         <v>219.1</v>
       </c>
       <c r="G322">
-        <v>10.96</v>
+        <v>4.38</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SD = 5% of each HV value (see *_SD columns on Hardness Data)</t>
+          <t xml:space="preserve">SD = 2% of each HV value (see *_SD columns on Hardness Data)</t>
         </is>
       </c>
     </row>
